--- a/템플릿/LH간이종심100-300억_템플릿.xlsx
+++ b/템플릿/LH간이종심100-300억_템플릿.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\99_완료\백업\템플릿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ihwijae\Desktop\템플릿\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3665,7 +3665,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3924,9 +3924,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4026,6 +4023,114 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4078,114 +4183,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4545,32 +4542,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="102"/>
-      <c r="B1" s="103" t="s">
+      <c r="A1" s="101"/>
+      <c r="B1" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="103" t="s">
+      <c r="C1" s="102" t="s">
         <v>49</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="125"/>
-      <c r="F1" s="126"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="161"/>
       <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="127"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="129"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="164"/>
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="127">
-        <v>0</v>
-      </c>
-      <c r="M1" s="128"/>
-      <c r="N1" s="130"/>
+      <c r="L1" s="162">
+        <v>0</v>
+      </c>
+      <c r="M1" s="163"/>
+      <c r="N1" s="165"/>
       <c r="O1" s="6" t="s">
         <v>51</v>
       </c>
@@ -4584,20 +4581,20 @@
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
-      <c r="Z1" s="120" t="s">
+      <c r="Z1" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="120"/>
+      <c r="AA1" s="155"/>
       <c r="AB1" s="7"/>
-      <c r="AC1" s="120" t="s">
+      <c r="AC1" s="155" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="121" t="s">
+      <c r="AD1" s="155"/>
+      <c r="AE1" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="AF1" s="122"/>
-      <c r="AG1" s="123"/>
+      <c r="AF1" s="157"/>
+      <c r="AG1" s="158"/>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
@@ -4608,69 +4605,69 @@
       <c r="AO1" s="8"/>
     </row>
     <row r="2" spans="1:41" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="148"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
       <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="143"/>
       <c r="G2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="149">
+      <c r="H2" s="142">
         <f>E2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="151"/>
-      <c r="J2" s="150"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="152">
+      <c r="L2" s="145">
         <f>H2*3</f>
         <v>0</v>
       </c>
-      <c r="M2" s="153"/>
+      <c r="M2" s="146"/>
       <c r="N2" s="12" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="154" t="s">
+      <c r="P2" s="147" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="154"/>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="154"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
       <c r="U2" s="79" t="s">
         <v>50</v>
       </c>
       <c r="V2" s="14"/>
       <c r="W2" s="15"/>
-      <c r="X2" s="124" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="124"/>
-      <c r="Z2" s="131"/>
-      <c r="AA2" s="132"/>
+      <c r="X2" s="159" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="159"/>
+      <c r="Z2" s="166"/>
+      <c r="AA2" s="167"/>
       <c r="AB2" s="78"/>
-      <c r="AC2" s="133">
+      <c r="AC2" s="168">
         <f>H1</f>
         <v>0</v>
       </c>
-      <c r="AD2" s="134"/>
-      <c r="AE2" s="135" t="e">
+      <c r="AD2" s="169"/>
+      <c r="AE2" s="170" t="e">
         <f>Z2/AC2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2" s="136"/>
-      <c r="AG2" s="137"/>
+      <c r="AF2" s="171"/>
+      <c r="AG2" s="172"/>
       <c r="AI2" s="16"/>
       <c r="AJ2" s="17"/>
       <c r="AK2" s="17"/>
@@ -4681,96 +4678,96 @@
       </c>
     </row>
     <row r="3" spans="1:41" s="22" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="138" t="s">
+      <c r="A3" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="142"/>
-      <c r="E3" s="142"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="143" t="s">
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="152" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="144"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="142" t="s">
+      <c r="J3" s="134"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="158"/>
-      <c r="P3" s="142" t="s">
+      <c r="O3" s="125"/>
+      <c r="P3" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="142"/>
-      <c r="R3" s="142"/>
-      <c r="S3" s="142"/>
-      <c r="T3" s="173"/>
-      <c r="U3" s="169" t="s">
+      <c r="Q3" s="138"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="138"/>
+      <c r="T3" s="139"/>
+      <c r="U3" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="V3" s="144"/>
-      <c r="W3" s="144"/>
-      <c r="X3" s="144"/>
-      <c r="Y3" s="144"/>
-      <c r="Z3" s="144"/>
-      <c r="AA3" s="144"/>
-      <c r="AB3" s="144"/>
-      <c r="AC3" s="144"/>
-      <c r="AD3" s="144"/>
-      <c r="AE3" s="144"/>
-      <c r="AF3" s="144"/>
-      <c r="AG3" s="144"/>
-      <c r="AH3" s="170"/>
+      <c r="V3" s="134"/>
+      <c r="W3" s="134"/>
+      <c r="X3" s="134"/>
+      <c r="Y3" s="134"/>
+      <c r="Z3" s="134"/>
+      <c r="AA3" s="134"/>
+      <c r="AB3" s="134"/>
+      <c r="AC3" s="134"/>
+      <c r="AD3" s="134"/>
+      <c r="AE3" s="134"/>
+      <c r="AF3" s="134"/>
+      <c r="AG3" s="134"/>
+      <c r="AH3" s="135"/>
       <c r="AI3" s="26"/>
-      <c r="AJ3" s="171" t="s">
+      <c r="AJ3" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="AK3" s="158" t="s">
+      <c r="AK3" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="AL3" s="160" t="s">
+      <c r="AL3" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="AM3" s="162" t="s">
+      <c r="AM3" s="129" t="s">
         <v>26</v>
       </c>
       <c r="AN3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AO3" s="164" t="s">
+      <c r="AO3" s="131" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:41" s="22" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="139"/>
-      <c r="B4" s="141"/>
+      <c r="A4" s="149"/>
+      <c r="B4" s="151"/>
       <c r="C4" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="108" t="s">
+      <c r="E4" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="108" t="s">
+      <c r="F4" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="108" t="s">
+      <c r="G4" s="107" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="109" t="s">
+      <c r="I4" s="108" t="s">
         <v>29</v>
       </c>
       <c r="J4" s="24" t="s">
@@ -4779,14 +4776,14 @@
       <c r="K4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="109" t="s">
+      <c r="L4" s="108" t="s">
         <v>1</v>
       </c>
       <c r="M4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="146"/>
-      <c r="O4" s="159"/>
+      <c r="N4" s="154"/>
+      <c r="O4" s="126"/>
       <c r="P4" s="23" t="s">
         <v>36</v>
       </c>
@@ -4796,16 +4793,16 @@
       <c r="R4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="S4" s="109" t="s">
+      <c r="S4" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="T4" s="108" t="s">
+      <c r="T4" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="U4" s="92" t="s">
+      <c r="U4" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="93" t="s">
+      <c r="V4" s="92" t="s">
         <v>38</v>
       </c>
       <c r="W4" s="27" t="s">
@@ -4826,45 +4823,45 @@
       <c r="AB4" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AC4" s="94" t="s">
+      <c r="AC4" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="AD4" s="93" t="s">
+      <c r="AD4" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="AE4" s="95" t="s">
+      <c r="AE4" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="AF4" s="96" t="s">
+      <c r="AF4" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="AG4" s="97" t="s">
+      <c r="AG4" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="AH4" s="98" t="s">
+      <c r="AH4" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="AI4" s="99" t="s">
+      <c r="AI4" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="AJ4" s="172"/>
-      <c r="AK4" s="159"/>
-      <c r="AL4" s="161"/>
-      <c r="AM4" s="163"/>
+      <c r="AJ4" s="137"/>
+      <c r="AK4" s="126"/>
+      <c r="AL4" s="128"/>
+      <c r="AM4" s="130"/>
       <c r="AN4" s="31"/>
-      <c r="AO4" s="165"/>
+      <c r="AO4" s="132"/>
     </row>
     <row r="5" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="84"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="113"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="112"/>
       <c r="H5" s="34"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="60"/>
       <c r="K5" s="36"/>
       <c r="L5" s="36"/>
       <c r="M5" s="81"/>
@@ -4873,11 +4870,11 @@
         <v>0</v>
       </c>
       <c r="O5" s="37"/>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="115"/>
-      <c r="S5" s="115"/>
-      <c r="T5" s="115"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
       <c r="U5" s="40">
         <f>ROUND(((P5*I5)+(Q5*J5)+(R5*K5)+(S5*L5)+(T5*M5)),3)</f>
         <v>0</v>
@@ -4903,14 +4900,14 @@
         <f t="shared" ref="AD5" si="1">IF(AC5&gt;=11,11,AC5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE5" s="100">
+      <c r="AE5" s="99">
         <f>IF(U6&gt;=94,4,IF(U6&gt;=91,3.9,IF(U6&gt;=88,3.8,IF(U6&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF5" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG5" s="101">
+      <c r="AG5" s="100">
         <v>17</v>
       </c>
       <c r="AH5" s="44" t="e">
@@ -4936,14 +4933,14 @@
     </row>
     <row r="6" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="85"/>
-      <c r="B6" s="112"/>
-      <c r="C6" s="166" t="s">
+      <c r="B6" s="111"/>
+      <c r="C6" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="168"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="121"/>
       <c r="H6" s="34"/>
       <c r="I6" s="56"/>
       <c r="J6" s="60"/>
@@ -4952,11 +4949,11 @@
       <c r="M6" s="80"/>
       <c r="N6" s="61"/>
       <c r="O6" s="37"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="117"/>
-      <c r="R6" s="117"/>
-      <c r="S6" s="117"/>
-      <c r="T6" s="117"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="116"/>
+      <c r="R6" s="116"/>
+      <c r="S6" s="116"/>
+      <c r="T6" s="116"/>
       <c r="U6" s="74">
         <f>(I5*P6)+(J5*Q6)+(K5*R6)+(L5*S6)+(M5*T6)</f>
         <v>0</v>
@@ -4970,7 +4967,7 @@
       <c r="AB6" s="70"/>
       <c r="AC6" s="75"/>
       <c r="AD6" s="71"/>
-      <c r="AE6" s="100"/>
+      <c r="AE6" s="99"/>
       <c r="AF6" s="43"/>
       <c r="AG6" s="64"/>
       <c r="AH6" s="44"/>
@@ -4984,15 +4981,15 @@
     </row>
     <row r="7" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="84"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="119"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="113"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="112"/>
       <c r="H7" s="34"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="36"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="60"/>
       <c r="K7" s="36"/>
       <c r="L7" s="36"/>
       <c r="M7" s="81"/>
@@ -5001,11 +4998,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="37"/>
-      <c r="P7" s="114"/>
-      <c r="Q7" s="115"/>
-      <c r="R7" s="115"/>
-      <c r="S7" s="115"/>
-      <c r="T7" s="115"/>
+      <c r="P7" s="113"/>
+      <c r="Q7" s="114"/>
+      <c r="R7" s="114"/>
+      <c r="S7" s="114"/>
+      <c r="T7" s="114"/>
       <c r="U7" s="40">
         <f>ROUND(((P7*I7)+(Q7*J7)+(R7*K7)+(S7*L7)+(T7*M7)),3)</f>
         <v>0</v>
@@ -5031,14 +5028,14 @@
         <f>IF(AC7&gt;=11,11,AC7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE7" s="100">
+      <c r="AE7" s="99">
         <f>IF(U8&gt;=94,4,IF(U8&gt;=91,3.9,IF(U8&gt;=88,3.8,IF(U8&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF7" s="43">
         <v>0.1</v>
       </c>
-      <c r="AG7" s="101">
+      <c r="AG7" s="100">
         <v>17</v>
       </c>
       <c r="AH7" s="44" t="e">
@@ -5064,14 +5061,14 @@
     </row>
     <row r="8" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="85"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="166" t="s">
+      <c r="B8" s="110"/>
+      <c r="C8" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="121"/>
       <c r="H8" s="34"/>
       <c r="I8" s="56"/>
       <c r="J8" s="60"/>
@@ -5080,11 +5077,11 @@
       <c r="M8" s="80"/>
       <c r="N8" s="61"/>
       <c r="O8" s="37"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="117"/>
-      <c r="R8" s="117"/>
-      <c r="S8" s="117"/>
-      <c r="T8" s="117"/>
+      <c r="P8" s="115"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="116"/>
+      <c r="S8" s="116"/>
+      <c r="T8" s="116"/>
       <c r="U8" s="74">
         <f>(I7*P8)+(J7*Q8)+(K7*R8)+(L7*S8)+(M7*T8)</f>
         <v>0</v>
@@ -5098,7 +5095,7 @@
       <c r="AB8" s="70"/>
       <c r="AC8" s="75"/>
       <c r="AD8" s="71"/>
-      <c r="AE8" s="100"/>
+      <c r="AE8" s="99"/>
       <c r="AF8" s="43"/>
       <c r="AG8" s="64"/>
       <c r="AH8" s="44"/>
@@ -5112,14 +5109,14 @@
     </row>
     <row r="9" spans="1:41" s="22" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="84"/>
-      <c r="B9" s="111"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="113"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="112"/>
       <c r="H9" s="34"/>
-      <c r="I9" s="35"/>
+      <c r="I9" s="56"/>
       <c r="J9" s="60"/>
       <c r="K9" s="60"/>
       <c r="L9" s="36"/>
@@ -5129,11 +5126,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="37"/>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="115"/>
-      <c r="R9" s="115"/>
-      <c r="S9" s="115"/>
-      <c r="T9" s="115"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="114"/>
+      <c r="R9" s="114"/>
+      <c r="S9" s="114"/>
+      <c r="T9" s="114"/>
       <c r="U9" s="40">
         <f>ROUND(((P9*I9)+(Q9*J9)+(R9*K9)+(S9*L9)+(T9*M9)),3)</f>
         <v>0</v>
@@ -5159,14 +5156,14 @@
         <f t="shared" ref="AD9" si="3">IF(AC9&gt;=11,11,AC9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE9" s="100">
+      <c r="AE9" s="99">
         <f>IF(U10&gt;=94,4,IF(U10&gt;=91,3.9,IF(U10&gt;=88,3.8,IF(U10&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF9" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG9" s="101">
+      <c r="AG9" s="100">
         <v>17</v>
       </c>
       <c r="AH9" s="44" t="e">
@@ -5192,14 +5189,14 @@
     </row>
     <row r="10" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="85"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="166" t="s">
+      <c r="B10" s="111"/>
+      <c r="C10" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="121"/>
       <c r="H10" s="34"/>
       <c r="I10" s="56"/>
       <c r="J10" s="60"/>
@@ -5208,11 +5205,11 @@
       <c r="M10" s="80"/>
       <c r="N10" s="61"/>
       <c r="O10" s="37"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="117"/>
-      <c r="R10" s="117"/>
-      <c r="S10" s="117"/>
-      <c r="T10" s="117"/>
+      <c r="P10" s="115"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="116"/>
       <c r="U10" s="74">
         <f>(I9*P10)+(J9*Q10)+(K9*R10)+(L9*S10)+(M9*T10)</f>
         <v>0</v>
@@ -5226,7 +5223,7 @@
       <c r="AB10" s="70"/>
       <c r="AC10" s="75"/>
       <c r="AD10" s="71"/>
-      <c r="AE10" s="100"/>
+      <c r="AE10" s="99"/>
       <c r="AF10" s="43"/>
       <c r="AG10" s="64"/>
       <c r="AH10" s="44"/>
@@ -5240,15 +5237,15 @@
     </row>
     <row r="11" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="84"/>
-      <c r="B11" s="111"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="113"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="112"/>
       <c r="H11" s="34"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="60"/>
       <c r="K11" s="36"/>
       <c r="L11" s="36"/>
       <c r="M11" s="81"/>
@@ -5257,11 +5254,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="37"/>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="115"/>
-      <c r="R11" s="115"/>
-      <c r="S11" s="115"/>
-      <c r="T11" s="115"/>
+      <c r="P11" s="113"/>
+      <c r="Q11" s="114"/>
+      <c r="R11" s="114"/>
+      <c r="S11" s="114"/>
+      <c r="T11" s="114"/>
       <c r="U11" s="40">
         <f>ROUND(((P11*I11)+(Q11*J11)+(R11*K11)+(S11*L11)+(T11*M11)),3)</f>
         <v>0</v>
@@ -5287,14 +5284,14 @@
         <f t="shared" ref="AD11" si="5">IF(AC11&gt;=11,11,AC11)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE11" s="100">
+      <c r="AE11" s="99">
         <f>IF(U12&gt;=94,4,IF(U12&gt;=91,3.9,IF(U12&gt;=88,3.8,IF(U12&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF11" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG11" s="101">
+      <c r="AG11" s="100">
         <v>17</v>
       </c>
       <c r="AH11" s="44" t="e">
@@ -5320,14 +5317,14 @@
     </row>
     <row r="12" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="85"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="166" t="s">
+      <c r="B12" s="111"/>
+      <c r="C12" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="168"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="121"/>
       <c r="H12" s="34"/>
       <c r="I12" s="56"/>
       <c r="J12" s="60"/>
@@ -5336,11 +5333,11 @@
       <c r="M12" s="80"/>
       <c r="N12" s="61"/>
       <c r="O12" s="37"/>
-      <c r="P12" s="116"/>
-      <c r="Q12" s="117"/>
-      <c r="R12" s="117"/>
-      <c r="S12" s="117"/>
-      <c r="T12" s="117"/>
+      <c r="P12" s="115"/>
+      <c r="Q12" s="116"/>
+      <c r="R12" s="116"/>
+      <c r="S12" s="116"/>
+      <c r="T12" s="116"/>
       <c r="U12" s="74">
         <f>(I11*P12)+(J11*Q12)+(K11*R12)+(L11*S12)+(M11*T12)</f>
         <v>0</v>
@@ -5354,7 +5351,7 @@
       <c r="AB12" s="70"/>
       <c r="AC12" s="75"/>
       <c r="AD12" s="71"/>
-      <c r="AE12" s="100"/>
+      <c r="AE12" s="99"/>
       <c r="AF12" s="43"/>
       <c r="AG12" s="64"/>
       <c r="AH12" s="44"/>
@@ -5368,15 +5365,15 @@
     </row>
     <row r="13" spans="1:41" s="22" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="84"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="113"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="112"/>
       <c r="H13" s="34"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="60"/>
       <c r="K13" s="36"/>
       <c r="L13" s="36"/>
       <c r="M13" s="81"/>
@@ -5385,11 +5382,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="37"/>
-      <c r="P13" s="114"/>
-      <c r="Q13" s="115"/>
-      <c r="R13" s="115"/>
-      <c r="S13" s="115"/>
-      <c r="T13" s="115"/>
+      <c r="P13" s="113"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
       <c r="U13" s="40">
         <f>ROUND(((P13*I13)+(Q13*J13)+(R13*K13)+(S13*L13)+(T13*M13)),3)</f>
         <v>0</v>
@@ -5415,14 +5412,14 @@
         <f>IF(AC13&gt;=11,11,AC13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE13" s="100">
+      <c r="AE13" s="99">
         <f>IF(U14&gt;=94,4,IF(U14&gt;=91,3.9,IF(U14&gt;=88,3.8,IF(U14&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF13" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG13" s="101">
+      <c r="AG13" s="100">
         <v>17</v>
       </c>
       <c r="AH13" s="44" t="e">
@@ -5449,13 +5446,13 @@
     <row r="14" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="85"/>
       <c r="B14" s="83"/>
-      <c r="C14" s="166" t="s">
+      <c r="C14" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="167"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="168"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="121"/>
       <c r="H14" s="34"/>
       <c r="I14" s="56"/>
       <c r="J14" s="60"/>
@@ -5464,11 +5461,11 @@
       <c r="M14" s="80"/>
       <c r="N14" s="61"/>
       <c r="O14" s="37"/>
-      <c r="P14" s="115"/>
-      <c r="Q14" s="115"/>
-      <c r="R14" s="115"/>
-      <c r="S14" s="115"/>
-      <c r="T14" s="117"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="116"/>
       <c r="U14" s="74">
         <f>(I13*P14)+(J13*Q14)+(K13*R14)+(L13*S14)+(M13*T14)</f>
         <v>0</v>
@@ -5482,7 +5479,7 @@
       <c r="AB14" s="70"/>
       <c r="AC14" s="75"/>
       <c r="AD14" s="71"/>
-      <c r="AE14" s="100"/>
+      <c r="AE14" s="99"/>
       <c r="AF14" s="43"/>
       <c r="AG14" s="64"/>
       <c r="AH14" s="44"/>
@@ -5497,14 +5494,14 @@
     <row r="15" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="84"/>
       <c r="B15" s="82"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="113"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="112"/>
       <c r="H15" s="34"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="36"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="60"/>
       <c r="K15" s="36"/>
       <c r="L15" s="36"/>
       <c r="M15" s="81"/>
@@ -5513,11 +5510,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="37"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="115"/>
-      <c r="R15" s="115"/>
-      <c r="S15" s="115"/>
-      <c r="T15" s="115"/>
+      <c r="P15" s="113"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
       <c r="U15" s="40">
         <f>ROUND(((P15*I15)+(Q15*J15)+(R15*K15)+(S15*L15)+(T15*M15)),3)</f>
         <v>0</v>
@@ -5543,14 +5540,14 @@
         <f t="shared" ref="AD15" si="7">IF(AC15&gt;=11,11,AC15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE15" s="100">
+      <c r="AE15" s="99">
         <f>IF(U16&gt;=94,4,IF(U16&gt;=91,3.9,IF(U16&gt;=88,3.8,IF(U16&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF15" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG15" s="101">
+      <c r="AG15" s="100">
         <v>17</v>
       </c>
       <c r="AH15" s="44" t="e">
@@ -5577,13 +5574,13 @@
     <row r="16" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="85"/>
       <c r="B16" s="83"/>
-      <c r="C16" s="166" t="s">
+      <c r="C16" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="167"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="168"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="121"/>
       <c r="H16" s="34"/>
       <c r="I16" s="56"/>
       <c r="J16" s="60"/>
@@ -5592,11 +5589,11 @@
       <c r="M16" s="80"/>
       <c r="N16" s="61"/>
       <c r="O16" s="37"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="117"/>
-      <c r="S16" s="117"/>
-      <c r="T16" s="117"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="116"/>
+      <c r="S16" s="116"/>
+      <c r="T16" s="116"/>
       <c r="U16" s="74">
         <f>(I15*P16)+(J15*Q16)+(K15*R16)+(L15*S16)+(M15*T16)</f>
         <v>0</v>
@@ -5610,7 +5607,7 @@
       <c r="AB16" s="70"/>
       <c r="AC16" s="75"/>
       <c r="AD16" s="71"/>
-      <c r="AE16" s="100"/>
+      <c r="AE16" s="99"/>
       <c r="AF16" s="43"/>
       <c r="AG16" s="64"/>
       <c r="AH16" s="44"/>
@@ -5625,14 +5622,14 @@
     <row r="17" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="84"/>
       <c r="B17" s="82"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="113"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="112"/>
       <c r="H17" s="57"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="36"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="60"/>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
       <c r="M17" s="81"/>
@@ -5641,11 +5638,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="37"/>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="115"/>
-      <c r="R17" s="115"/>
-      <c r="S17" s="115"/>
-      <c r="T17" s="115"/>
+      <c r="P17" s="113"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
       <c r="U17" s="40">
         <f>ROUND(((P17*I17)+(Q17*J17)+(R17*K17)+(S17*L17)+(T17*M17)),3)</f>
         <v>0</v>
@@ -5671,14 +5668,14 @@
         <f t="shared" ref="AD17" si="9">IF(AC17&gt;=11,11,AC17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE17" s="100">
+      <c r="AE17" s="99">
         <f>IF(U18&gt;=94,4,IF(U18&gt;=91,3.9,IF(U18&gt;=88,3.8,IF(U18&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF17" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG17" s="101">
+      <c r="AG17" s="100">
         <v>17</v>
       </c>
       <c r="AH17" s="44" t="e">
@@ -5705,13 +5702,13 @@
     <row r="18" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="85"/>
       <c r="B18" s="83"/>
-      <c r="C18" s="166" t="s">
+      <c r="C18" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="167"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="168"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="121"/>
       <c r="H18" s="34"/>
       <c r="I18" s="56"/>
       <c r="J18" s="60"/>
@@ -5720,11 +5717,11 @@
       <c r="M18" s="80"/>
       <c r="N18" s="61"/>
       <c r="O18" s="37"/>
-      <c r="P18" s="115"/>
-      <c r="Q18" s="115"/>
-      <c r="R18" s="116"/>
-      <c r="S18" s="117"/>
-      <c r="T18" s="117"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="115"/>
+      <c r="S18" s="116"/>
+      <c r="T18" s="116"/>
       <c r="U18" s="74">
         <f>(I17*P18)+(J17*Q18)+(K17*R18)+(L17*S18)+(M17*T18)</f>
         <v>0</v>
@@ -5738,7 +5735,7 @@
       <c r="AB18" s="70"/>
       <c r="AC18" s="75"/>
       <c r="AD18" s="71"/>
-      <c r="AE18" s="100"/>
+      <c r="AE18" s="99"/>
       <c r="AF18" s="43"/>
       <c r="AG18" s="64"/>
       <c r="AH18" s="44"/>
@@ -5753,14 +5750,14 @@
     <row r="19" spans="1:41" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="84"/>
       <c r="B19" s="82"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="113"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="112"/>
       <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="36"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="60"/>
       <c r="K19" s="36"/>
       <c r="L19" s="36"/>
       <c r="M19" s="81"/>
@@ -5769,11 +5766,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="37"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="115"/>
-      <c r="R19" s="115"/>
-      <c r="S19" s="115"/>
-      <c r="T19" s="115"/>
+      <c r="P19" s="113"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
       <c r="U19" s="40">
         <f>ROUND(((P19*I19)+(Q19*J19)+(R19*K19)+(S19*L19)+(T19*M19)),3)</f>
         <v>0</v>
@@ -5799,14 +5796,14 @@
         <f t="shared" ref="AD19" si="10">IF(AC19&gt;=11,11,AC19)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE19" s="100">
+      <c r="AE19" s="99">
         <f>IF(U20&gt;=94,4,IF(U20&gt;=91,3.9,IF(U20&gt;=88,3.8,IF(U20&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF19" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG19" s="101">
+      <c r="AG19" s="100">
         <v>17</v>
       </c>
       <c r="AH19" s="44" t="e">
@@ -5833,13 +5830,13 @@
     <row r="20" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="85"/>
       <c r="B20" s="83"/>
-      <c r="C20" s="155" t="s">
+      <c r="C20" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="156"/>
-      <c r="E20" s="156"/>
-      <c r="F20" s="156"/>
-      <c r="G20" s="157"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="124"/>
       <c r="H20" s="34"/>
       <c r="I20" s="56"/>
       <c r="J20" s="60"/>
@@ -5866,7 +5863,7 @@
       <c r="AB20" s="70"/>
       <c r="AC20" s="75"/>
       <c r="AD20" s="71"/>
-      <c r="AE20" s="100"/>
+      <c r="AE20" s="99"/>
       <c r="AF20" s="43"/>
       <c r="AG20" s="64"/>
       <c r="AH20" s="44"/>
@@ -5881,18 +5878,18 @@
     <row r="21" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="84"/>
       <c r="B21" s="82"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="113"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="112"/>
       <c r="H21" s="34"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="105"/>
-      <c r="N21" s="104">
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="103">
         <f>SUM(I21:M21)</f>
         <v>0</v>
       </c>
@@ -5927,14 +5924,14 @@
         <f t="shared" ref="AD21" si="11">IF(AC21&gt;=11,11,AC21)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE21" s="100">
+      <c r="AE21" s="99">
         <f>IF(U22&gt;=94,4,IF(U22&gt;=91,3.9,IF(U22&gt;=88,3.8,IF(U22&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF21" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG21" s="101">
+      <c r="AG21" s="100">
         <v>17</v>
       </c>
       <c r="AH21" s="44" t="e">
@@ -5955,20 +5952,20 @@
     <row r="22" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="85"/>
       <c r="B22" s="83"/>
-      <c r="C22" s="155" t="s">
+      <c r="C22" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="156"/>
-      <c r="G22" s="157"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="104"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="87"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="103"/>
       <c r="O22" s="37"/>
       <c r="P22" s="40"/>
       <c r="Q22" s="40"/>
@@ -5988,7 +5985,7 @@
       <c r="AB22" s="70"/>
       <c r="AC22" s="75"/>
       <c r="AD22" s="71"/>
-      <c r="AE22" s="100"/>
+      <c r="AE22" s="99"/>
       <c r="AF22" s="43"/>
       <c r="AG22" s="64"/>
       <c r="AH22" s="44"/>
@@ -6003,14 +6000,14 @@
     <row r="23" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="84"/>
       <c r="B23" s="82"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="113"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="112"/>
       <c r="H23" s="57"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="36"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="60"/>
       <c r="K23" s="36"/>
       <c r="L23" s="36"/>
       <c r="M23" s="81"/>
@@ -6049,14 +6046,14 @@
         <f t="shared" ref="AD23" si="13">IF(AC23&gt;=11,11,AC23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE23" s="100">
+      <c r="AE23" s="99">
         <f>IF(U24&gt;=94,4,IF(U24&gt;=91,3.9,IF(U24&gt;=88,3.8,IF(U24&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF23" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG23" s="101">
+      <c r="AG23" s="100">
         <v>17</v>
       </c>
       <c r="AH23" s="44" t="e">
@@ -6077,13 +6074,13 @@
     <row r="24" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="85"/>
       <c r="B24" s="83"/>
-      <c r="C24" s="155" t="s">
+      <c r="C24" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="156"/>
-      <c r="E24" s="156"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="157"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="124"/>
       <c r="H24" s="34"/>
       <c r="I24" s="56"/>
       <c r="J24" s="60"/>
@@ -6110,7 +6107,7 @@
       <c r="AB24" s="70"/>
       <c r="AC24" s="75"/>
       <c r="AD24" s="71"/>
-      <c r="AE24" s="100"/>
+      <c r="AE24" s="99"/>
       <c r="AF24" s="43"/>
       <c r="AG24" s="64"/>
       <c r="AH24" s="44"/>
@@ -6125,14 +6122,14 @@
     <row r="25" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="84"/>
       <c r="B25" s="82"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="113"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="112"/>
       <c r="H25" s="34"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="36"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="60"/>
       <c r="K25" s="36"/>
       <c r="L25" s="36"/>
       <c r="M25" s="81"/>
@@ -6171,14 +6168,14 @@
         <f>IF(AC25&gt;=11,11,AC25)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE25" s="100">
+      <c r="AE25" s="99">
         <f>IF(U26&gt;=94,4,IF(U26&gt;=91,3.9,IF(U26&gt;=88,3.8,IF(U26&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF25" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG25" s="101">
+      <c r="AG25" s="100">
         <v>17</v>
       </c>
       <c r="AH25" s="44" t="e">
@@ -6199,13 +6196,13 @@
     <row r="26" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="85"/>
       <c r="B26" s="83"/>
-      <c r="C26" s="155" t="s">
+      <c r="C26" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="156"/>
-      <c r="G26" s="157"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="124"/>
       <c r="H26" s="34"/>
       <c r="I26" s="56"/>
       <c r="J26" s="60"/>
@@ -6232,7 +6229,7 @@
       <c r="AB26" s="70"/>
       <c r="AC26" s="75"/>
       <c r="AD26" s="71"/>
-      <c r="AE26" s="100"/>
+      <c r="AE26" s="99"/>
       <c r="AF26" s="43"/>
       <c r="AG26" s="64"/>
       <c r="AH26" s="44"/>
@@ -6247,14 +6244,14 @@
     <row r="27" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="84"/>
       <c r="B27" s="82"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="113"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="112"/>
       <c r="H27" s="34"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="36"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="60"/>
       <c r="K27" s="36"/>
       <c r="L27" s="36"/>
       <c r="M27" s="81"/>
@@ -6263,9 +6260,9 @@
         <v>0</v>
       </c>
       <c r="O27" s="37"/>
-      <c r="P27" s="114"/>
-      <c r="Q27" s="115"/>
-      <c r="R27" s="115"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
       <c r="S27" s="39"/>
       <c r="T27" s="39"/>
       <c r="U27" s="40">
@@ -6293,14 +6290,14 @@
         <f t="shared" ref="AD27" si="15">IF(AC27&gt;=11,11,AC27)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE27" s="100">
+      <c r="AE27" s="99">
         <f>IF(U28&gt;=94,4,IF(U28&gt;=91,3.9,IF(U28&gt;=88,3.8,IF(U28&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF27" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG27" s="101">
+      <c r="AG27" s="100">
         <v>17</v>
       </c>
       <c r="AH27" s="44" t="e">
@@ -6327,24 +6324,24 @@
     <row r="28" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="85"/>
       <c r="B28" s="83"/>
-      <c r="C28" s="166" t="s">
+      <c r="C28" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="167"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="168"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="121"/>
       <c r="H28" s="59"/>
       <c r="I28" s="56"/>
       <c r="J28" s="60"/>
       <c r="K28" s="60"/>
       <c r="L28" s="60"/>
-      <c r="M28" s="110"/>
+      <c r="M28" s="109"/>
       <c r="N28" s="61"/>
       <c r="O28" s="37"/>
-      <c r="P28" s="117"/>
-      <c r="Q28" s="117"/>
-      <c r="R28" s="117"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="116"/>
       <c r="S28" s="40"/>
       <c r="T28" s="40"/>
       <c r="U28" s="74">
@@ -6360,7 +6357,7 @@
       <c r="AB28" s="70"/>
       <c r="AC28" s="75"/>
       <c r="AD28" s="71"/>
-      <c r="AE28" s="100"/>
+      <c r="AE28" s="99"/>
       <c r="AF28" s="43"/>
       <c r="AG28" s="64"/>
       <c r="AH28" s="44"/>
@@ -6375,14 +6372,14 @@
     <row r="29" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="84"/>
       <c r="B29" s="82"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="113"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="112"/>
       <c r="H29" s="34"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="36"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="60"/>
       <c r="K29" s="36"/>
       <c r="L29" s="60"/>
       <c r="M29" s="81"/>
@@ -6391,9 +6388,9 @@
         <v>0</v>
       </c>
       <c r="O29" s="37"/>
-      <c r="P29" s="114"/>
-      <c r="Q29" s="115"/>
-      <c r="R29" s="115"/>
+      <c r="P29" s="113"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
       <c r="S29" s="39"/>
       <c r="T29" s="39"/>
       <c r="U29" s="40">
@@ -6421,14 +6418,14 @@
         <f>IF(AC29&gt;=11,11,AC29)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE29" s="100">
+      <c r="AE29" s="99">
         <f>IF(U30&gt;=94,4,IF(U30&gt;=91,3.9,IF(U30&gt;=88,3.8,IF(U30&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF29" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG29" s="101">
+      <c r="AG29" s="100">
         <v>17</v>
       </c>
       <c r="AH29" s="44" t="e">
@@ -6455,13 +6452,13 @@
     <row r="30" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="85"/>
       <c r="B30" s="83"/>
-      <c r="C30" s="155" t="s">
+      <c r="C30" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156"/>
-      <c r="G30" s="157"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="123"/>
+      <c r="G30" s="124"/>
       <c r="H30" s="34"/>
       <c r="I30" s="56"/>
       <c r="J30" s="60"/>
@@ -6470,9 +6467,9 @@
       <c r="M30" s="80"/>
       <c r="N30" s="61"/>
       <c r="O30" s="37"/>
-      <c r="P30" s="116"/>
-      <c r="Q30" s="117"/>
-      <c r="R30" s="117"/>
+      <c r="P30" s="115"/>
+      <c r="Q30" s="116"/>
+      <c r="R30" s="116"/>
       <c r="S30" s="40"/>
       <c r="T30" s="40"/>
       <c r="U30" s="74">
@@ -6488,7 +6485,7 @@
       <c r="AB30" s="70"/>
       <c r="AC30" s="75"/>
       <c r="AD30" s="71"/>
-      <c r="AE30" s="100"/>
+      <c r="AE30" s="99"/>
       <c r="AF30" s="43"/>
       <c r="AG30" s="64"/>
       <c r="AH30" s="44"/>
@@ -6503,25 +6500,25 @@
     <row r="31" spans="1:41" s="22" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="84"/>
       <c r="B31" s="82"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="113"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="112"/>
       <c r="H31" s="34"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="104">
+      <c r="I31" s="88"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="86"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="103">
         <f>SUM(I31:M31)</f>
         <v>0</v>
       </c>
       <c r="O31" s="37"/>
-      <c r="P31" s="114"/>
-      <c r="Q31" s="114"/>
-      <c r="R31" s="115"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="114"/>
       <c r="S31" s="39"/>
       <c r="T31" s="39"/>
       <c r="U31" s="40">
@@ -6549,14 +6546,14 @@
         <f t="shared" ref="AD31" si="16">IF(AC31&gt;=11,11,AC31)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE31" s="100">
+      <c r="AE31" s="99">
         <f>IF(U32&gt;=94,4,IF(U32&gt;=91,3.9,IF(U32&gt;=88,3.8,IF(U32&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF31" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG31" s="101">
+      <c r="AG31" s="100">
         <v>17</v>
       </c>
       <c r="AH31" s="44" t="e">
@@ -6577,24 +6574,24 @@
     <row r="32" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="85"/>
       <c r="B32" s="83"/>
-      <c r="C32" s="155" t="s">
+      <c r="C32" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="157"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="106"/>
-      <c r="N32" s="104"/>
+      <c r="D32" s="123"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="124"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="88"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="89"/>
+      <c r="L32" s="89"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="103"/>
       <c r="O32" s="37"/>
-      <c r="P32" s="116"/>
-      <c r="Q32" s="117"/>
-      <c r="R32" s="117"/>
+      <c r="P32" s="115"/>
+      <c r="Q32" s="116"/>
+      <c r="R32" s="116"/>
       <c r="S32" s="40"/>
       <c r="T32" s="40"/>
       <c r="U32" s="74">
@@ -6610,7 +6607,7 @@
       <c r="AB32" s="70"/>
       <c r="AC32" s="75"/>
       <c r="AD32" s="71"/>
-      <c r="AE32" s="100"/>
+      <c r="AE32" s="99"/>
       <c r="AF32" s="43"/>
       <c r="AG32" s="64"/>
       <c r="AH32" s="44"/>
@@ -6625,14 +6622,14 @@
     <row r="33" spans="1:41" s="22" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="84"/>
       <c r="B33" s="82"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="113"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="112"/>
       <c r="H33" s="34"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="36"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="60"/>
       <c r="K33" s="36"/>
       <c r="L33" s="36"/>
       <c r="M33" s="65"/>
@@ -6671,14 +6668,14 @@
         <f>IF(AC33&gt;=11,11,AC33)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE33" s="100">
+      <c r="AE33" s="99">
         <f>IF(U34&gt;=94,4,IF(U34&gt;=91,3.9,IF(U34&gt;=88,3.8,IF(U34&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF33" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG33" s="101">
+      <c r="AG33" s="100">
         <v>17</v>
       </c>
       <c r="AH33" s="44" t="e">
@@ -6705,13 +6702,13 @@
     <row r="34" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="85"/>
       <c r="B34" s="83"/>
-      <c r="C34" s="155" t="s">
+      <c r="C34" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="156"/>
-      <c r="E34" s="156"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="157"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="123"/>
+      <c r="G34" s="124"/>
       <c r="H34" s="34"/>
       <c r="I34" s="56"/>
       <c r="J34" s="60"/>
@@ -6738,7 +6735,7 @@
       <c r="AB34" s="70"/>
       <c r="AC34" s="75"/>
       <c r="AD34" s="71"/>
-      <c r="AE34" s="100"/>
+      <c r="AE34" s="99"/>
       <c r="AF34" s="43"/>
       <c r="AG34" s="64"/>
       <c r="AH34" s="44"/>
@@ -6753,14 +6750,14 @@
     <row r="35" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="84"/>
       <c r="B35" s="82"/>
-      <c r="C35" s="119"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="113"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="112"/>
       <c r="H35" s="34"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="36"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="60"/>
       <c r="K35" s="36"/>
       <c r="L35" s="60"/>
       <c r="M35" s="80"/>
@@ -6769,11 +6766,11 @@
         <v>0</v>
       </c>
       <c r="O35" s="37"/>
-      <c r="P35" s="114"/>
-      <c r="Q35" s="115"/>
-      <c r="R35" s="115"/>
-      <c r="S35" s="115"/>
-      <c r="T35" s="115"/>
+      <c r="P35" s="113"/>
+      <c r="Q35" s="114"/>
+      <c r="R35" s="114"/>
+      <c r="S35" s="114"/>
+      <c r="T35" s="114"/>
       <c r="U35" s="40">
         <f>ROUND(((P35*I35)+(Q35*J35)+(R35*K35)+(S35*L35)+(T35*M35)),3)</f>
         <v>0</v>
@@ -6799,14 +6796,14 @@
         <f t="shared" ref="AD35" si="17">IF(AC35&gt;=11,11,AC35)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE35" s="100">
+      <c r="AE35" s="99">
         <f>IF(U36&gt;=94,4,IF(U36&gt;=91,3.9,IF(U36&gt;=88,3.8,IF(U36&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF35" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG35" s="101">
+      <c r="AG35" s="100">
         <v>17</v>
       </c>
       <c r="AH35" s="44" t="e">
@@ -6833,13 +6830,13 @@
     <row r="36" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="85"/>
       <c r="B36" s="83"/>
-      <c r="C36" s="155" t="s">
+      <c r="C36" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="156"/>
-      <c r="E36" s="156"/>
-      <c r="F36" s="156"/>
-      <c r="G36" s="157"/>
+      <c r="D36" s="123"/>
+      <c r="E36" s="123"/>
+      <c r="F36" s="123"/>
+      <c r="G36" s="124"/>
       <c r="H36" s="34"/>
       <c r="I36" s="56"/>
       <c r="J36" s="60"/>
@@ -6848,11 +6845,11 @@
       <c r="M36" s="80"/>
       <c r="N36" s="61"/>
       <c r="O36" s="37"/>
-      <c r="P36" s="117"/>
-      <c r="Q36" s="117"/>
-      <c r="R36" s="117"/>
-      <c r="S36" s="117"/>
-      <c r="T36" s="117"/>
+      <c r="P36" s="116"/>
+      <c r="Q36" s="116"/>
+      <c r="R36" s="116"/>
+      <c r="S36" s="116"/>
+      <c r="T36" s="116"/>
       <c r="U36" s="74">
         <f>(I35*P36)+(J35*Q36)+(K35*R36)+(L35*S36)+(M35*T36)</f>
         <v>0</v>
@@ -6866,7 +6863,7 @@
       <c r="AB36" s="70"/>
       <c r="AC36" s="75"/>
       <c r="AD36" s="71"/>
-      <c r="AE36" s="100"/>
+      <c r="AE36" s="99"/>
       <c r="AF36" s="43"/>
       <c r="AG36" s="64"/>
       <c r="AH36" s="44"/>
@@ -6881,14 +6878,14 @@
     <row r="37" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="84"/>
       <c r="B37" s="82"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="113"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="112"/>
       <c r="H37" s="34"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="36"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="60"/>
       <c r="K37" s="36"/>
       <c r="L37" s="36"/>
       <c r="M37" s="81"/>
@@ -6897,11 +6894,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="37"/>
-      <c r="P37" s="114"/>
-      <c r="Q37" s="115"/>
-      <c r="R37" s="115"/>
-      <c r="S37" s="115"/>
-      <c r="T37" s="115"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="114"/>
+      <c r="R37" s="114"/>
+      <c r="S37" s="114"/>
+      <c r="T37" s="114"/>
       <c r="U37" s="40">
         <f>ROUND(((P37*I37)+(Q37*J37)+(R37*K37)+(S37*L37)+(T37*M37)),3)</f>
         <v>0</v>
@@ -6927,14 +6924,14 @@
         <f>IF(AC37&gt;=11,11,AC37)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE37" s="100">
+      <c r="AE37" s="99">
         <f>IF(U38&gt;=94,4,IF(U38&gt;=91,3.9,IF(U38&gt;=88,3.8,IF(U38&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF37" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG37" s="101">
+      <c r="AG37" s="100">
         <v>17</v>
       </c>
       <c r="AH37" s="44" t="e">
@@ -6961,13 +6958,13 @@
     <row r="38" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="85"/>
       <c r="B38" s="83"/>
-      <c r="C38" s="155" t="s">
+      <c r="C38" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="156"/>
-      <c r="E38" s="156"/>
-      <c r="F38" s="156"/>
-      <c r="G38" s="157"/>
+      <c r="D38" s="123"/>
+      <c r="E38" s="123"/>
+      <c r="F38" s="123"/>
+      <c r="G38" s="124"/>
       <c r="H38" s="34"/>
       <c r="I38" s="56"/>
       <c r="J38" s="60"/>
@@ -6976,11 +6973,11 @@
       <c r="M38" s="80"/>
       <c r="N38" s="61"/>
       <c r="O38" s="37"/>
-      <c r="P38" s="116"/>
-      <c r="Q38" s="117"/>
-      <c r="R38" s="115"/>
-      <c r="S38" s="117"/>
-      <c r="T38" s="117"/>
+      <c r="P38" s="115"/>
+      <c r="Q38" s="116"/>
+      <c r="R38" s="114"/>
+      <c r="S38" s="116"/>
+      <c r="T38" s="116"/>
       <c r="U38" s="74">
         <f>(I37*P38)+(J37*Q38)+(K37*R38)+(L37*S38)+(M37*T38)</f>
         <v>0</v>
@@ -6994,7 +6991,7 @@
       <c r="AB38" s="70"/>
       <c r="AC38" s="75"/>
       <c r="AD38" s="71"/>
-      <c r="AE38" s="100"/>
+      <c r="AE38" s="99"/>
       <c r="AF38" s="43"/>
       <c r="AG38" s="64"/>
       <c r="AH38" s="44"/>
@@ -7009,14 +7006,14 @@
     <row r="39" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="84"/>
       <c r="B39" s="82"/>
-      <c r="C39" s="119"/>
-      <c r="D39" s="118"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="113"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="112"/>
       <c r="H39" s="34"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="36"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="60"/>
       <c r="K39" s="36"/>
       <c r="L39" s="36"/>
       <c r="M39" s="81"/>
@@ -7025,11 +7022,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="37"/>
-      <c r="P39" s="114"/>
-      <c r="Q39" s="115"/>
-      <c r="R39" s="115"/>
-      <c r="S39" s="115"/>
-      <c r="T39" s="115"/>
+      <c r="P39" s="113"/>
+      <c r="Q39" s="114"/>
+      <c r="R39" s="114"/>
+      <c r="S39" s="114"/>
+      <c r="T39" s="114"/>
       <c r="U39" s="40">
         <f>ROUND(((P39*I39)+(Q39*J39)+(R39*K39)+(S39*L39)+(T39*M39)),3)</f>
         <v>0</v>
@@ -7055,14 +7052,14 @@
         <f t="shared" ref="AD39" si="19">IF(AC39&gt;=11,11,AC39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE39" s="100">
+      <c r="AE39" s="99">
         <f>IF(U40&gt;=94,4,IF(U40&gt;=91,3.9,IF(U40&gt;=88,3.8,IF(U40&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF39" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG39" s="101">
+      <c r="AG39" s="100">
         <v>17</v>
       </c>
       <c r="AH39" s="44" t="e">
@@ -7089,13 +7086,13 @@
     <row r="40" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="85"/>
       <c r="B40" s="83"/>
-      <c r="C40" s="155" t="s">
+      <c r="C40" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
-      <c r="F40" s="156"/>
-      <c r="G40" s="157"/>
+      <c r="D40" s="123"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="123"/>
+      <c r="G40" s="124"/>
       <c r="H40" s="34"/>
       <c r="I40" s="56"/>
       <c r="J40" s="60"/>
@@ -7104,11 +7101,11 @@
       <c r="M40" s="80"/>
       <c r="N40" s="61"/>
       <c r="O40" s="37"/>
-      <c r="P40" s="116"/>
-      <c r="Q40" s="117"/>
-      <c r="R40" s="117"/>
-      <c r="S40" s="117"/>
-      <c r="T40" s="117"/>
+      <c r="P40" s="115"/>
+      <c r="Q40" s="116"/>
+      <c r="R40" s="116"/>
+      <c r="S40" s="116"/>
+      <c r="T40" s="116"/>
       <c r="U40" s="74">
         <f>(I39*P40)+(J39*Q40)+(K39*R40)+(L39*S40)+(M39*T40)</f>
         <v>0</v>
@@ -7122,7 +7119,7 @@
       <c r="AB40" s="70"/>
       <c r="AC40" s="75"/>
       <c r="AD40" s="71"/>
-      <c r="AE40" s="100"/>
+      <c r="AE40" s="99"/>
       <c r="AF40" s="43"/>
       <c r="AG40" s="64"/>
       <c r="AH40" s="44"/>
@@ -7137,14 +7134,14 @@
     <row r="41" spans="1:41" s="22" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="84"/>
       <c r="B41" s="82"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="119"/>
-      <c r="G41" s="113"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="112"/>
       <c r="H41" s="34"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="36"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="60"/>
       <c r="K41" s="36"/>
       <c r="L41" s="36"/>
       <c r="M41" s="81"/>
@@ -7153,11 +7150,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="37"/>
-      <c r="P41" s="114"/>
-      <c r="Q41" s="115"/>
-      <c r="R41" s="115"/>
-      <c r="S41" s="115"/>
-      <c r="T41" s="115"/>
+      <c r="P41" s="113"/>
+      <c r="Q41" s="114"/>
+      <c r="R41" s="114"/>
+      <c r="S41" s="114"/>
+      <c r="T41" s="114"/>
       <c r="U41" s="40">
         <f>ROUND(((P41*I41)+(Q41*J41)+(R41*K41)+(S41*L41)+(T41*M41)),3)</f>
         <v>0</v>
@@ -7183,14 +7180,14 @@
         <f t="shared" ref="AD41" si="21">IF(AC41&gt;=11,11,AC41)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE41" s="100">
+      <c r="AE41" s="99">
         <f>IF(U42&gt;=94,4,IF(U42&gt;=91,3.9,IF(U42&gt;=88,3.8,IF(U42&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF41" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG41" s="101">
+      <c r="AG41" s="100">
         <v>17</v>
       </c>
       <c r="AH41" s="44" t="e">
@@ -7217,13 +7214,13 @@
     <row r="42" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="85"/>
       <c r="B42" s="83"/>
-      <c r="C42" s="155" t="s">
+      <c r="C42" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="156"/>
-      <c r="E42" s="156"/>
-      <c r="F42" s="156"/>
-      <c r="G42" s="157"/>
+      <c r="D42" s="123"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="123"/>
+      <c r="G42" s="124"/>
       <c r="H42" s="34"/>
       <c r="I42" s="56"/>
       <c r="J42" s="60"/>
@@ -7232,11 +7229,11 @@
       <c r="M42" s="80"/>
       <c r="N42" s="61"/>
       <c r="O42" s="37"/>
-      <c r="P42" s="116"/>
-      <c r="Q42" s="117"/>
-      <c r="R42" s="117"/>
-      <c r="S42" s="117"/>
-      <c r="T42" s="117"/>
+      <c r="P42" s="115"/>
+      <c r="Q42" s="116"/>
+      <c r="R42" s="116"/>
+      <c r="S42" s="116"/>
+      <c r="T42" s="116"/>
       <c r="U42" s="74">
         <f>(I41*P42)+(J41*Q42)+(K41*R42)+(L41*S42)+(M41*T42)</f>
         <v>0</v>
@@ -7250,7 +7247,7 @@
       <c r="AB42" s="70"/>
       <c r="AC42" s="75"/>
       <c r="AD42" s="71"/>
-      <c r="AE42" s="100"/>
+      <c r="AE42" s="99"/>
       <c r="AF42" s="43"/>
       <c r="AG42" s="64"/>
       <c r="AH42" s="44"/>
@@ -7265,14 +7262,14 @@
     <row r="43" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="84"/>
       <c r="B43" s="82"/>
-      <c r="C43" s="119"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="119"/>
-      <c r="G43" s="113"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="112"/>
       <c r="H43" s="55"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="36"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="60"/>
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
       <c r="M43" s="81"/>
@@ -7281,11 +7278,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="37"/>
-      <c r="P43" s="114"/>
-      <c r="Q43" s="115"/>
-      <c r="R43" s="115"/>
-      <c r="S43" s="115"/>
-      <c r="T43" s="115"/>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="114"/>
+      <c r="R43" s="114"/>
+      <c r="S43" s="114"/>
+      <c r="T43" s="114"/>
       <c r="U43" s="40">
         <f>ROUND(((P43*I43)+(Q43*J43)+(R43*K43)+(S43*L43)+(T43*M43)),3)</f>
         <v>0</v>
@@ -7311,14 +7308,14 @@
         <f t="shared" ref="AD43" si="23">IF(AC43&gt;=11,11,AC43)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE43" s="100">
+      <c r="AE43" s="99">
         <f>IF(U44&gt;=94,4,IF(U44&gt;=91,3.9,IF(U44&gt;=88,3.8,IF(U44&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF43" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG43" s="101">
+      <c r="AG43" s="100">
         <v>17</v>
       </c>
       <c r="AH43" s="44" t="e">
@@ -7345,13 +7342,13 @@
     <row r="44" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="85"/>
       <c r="B44" s="83"/>
-      <c r="C44" s="155" t="s">
+      <c r="C44" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D44" s="156"/>
-      <c r="E44" s="156"/>
-      <c r="F44" s="156"/>
-      <c r="G44" s="157"/>
+      <c r="D44" s="123"/>
+      <c r="E44" s="123"/>
+      <c r="F44" s="123"/>
+      <c r="G44" s="124"/>
       <c r="H44" s="34"/>
       <c r="I44" s="56"/>
       <c r="J44" s="60"/>
@@ -7360,11 +7357,11 @@
       <c r="M44" s="80"/>
       <c r="N44" s="61"/>
       <c r="O44" s="37"/>
-      <c r="P44" s="116"/>
-      <c r="Q44" s="115"/>
-      <c r="R44" s="115"/>
-      <c r="S44" s="117"/>
-      <c r="T44" s="117"/>
+      <c r="P44" s="115"/>
+      <c r="Q44" s="114"/>
+      <c r="R44" s="114"/>
+      <c r="S44" s="116"/>
+      <c r="T44" s="116"/>
       <c r="U44" s="74">
         <f>(I43*P44)+(J43*Q44)+(K43*R44)+(L43*S44)+(M43*T44)</f>
         <v>0</v>
@@ -7378,7 +7375,7 @@
       <c r="AB44" s="70"/>
       <c r="AC44" s="75"/>
       <c r="AD44" s="71"/>
-      <c r="AE44" s="100"/>
+      <c r="AE44" s="99"/>
       <c r="AF44" s="43"/>
       <c r="AG44" s="64"/>
       <c r="AH44" s="44"/>
@@ -7393,14 +7390,14 @@
     <row r="45" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="84"/>
       <c r="B45" s="82"/>
-      <c r="C45" s="119"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="119"/>
-      <c r="G45" s="113"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="112"/>
       <c r="H45" s="34"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="36"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="60"/>
       <c r="K45" s="36"/>
       <c r="L45" s="36"/>
       <c r="M45" s="81"/>
@@ -7409,11 +7406,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="37"/>
-      <c r="P45" s="114"/>
-      <c r="Q45" s="115"/>
-      <c r="R45" s="115"/>
-      <c r="S45" s="115"/>
-      <c r="T45" s="115"/>
+      <c r="P45" s="113"/>
+      <c r="Q45" s="114"/>
+      <c r="R45" s="114"/>
+      <c r="S45" s="114"/>
+      <c r="T45" s="114"/>
       <c r="U45" s="40">
         <f>ROUND(((P45*I45)+(Q45*J45)+(R45*K45)+(S45*L45)+(T45*M45)),3)</f>
         <v>0</v>
@@ -7439,14 +7436,14 @@
         <f t="shared" ref="AD45" si="25">IF(AC45&gt;=11,11,AC45)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE45" s="100">
+      <c r="AE45" s="99">
         <f>IF(U46&gt;=94,4,IF(U46&gt;=91,3.9,IF(U46&gt;=88,3.8,IF(U46&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF45" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG45" s="101">
+      <c r="AG45" s="100">
         <v>17</v>
       </c>
       <c r="AH45" s="44" t="e">
@@ -7473,13 +7470,13 @@
     <row r="46" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="85"/>
       <c r="B46" s="83"/>
-      <c r="C46" s="155" t="s">
+      <c r="C46" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D46" s="156"/>
-      <c r="E46" s="156"/>
-      <c r="F46" s="156"/>
-      <c r="G46" s="157"/>
+      <c r="D46" s="123"/>
+      <c r="E46" s="123"/>
+      <c r="F46" s="123"/>
+      <c r="G46" s="124"/>
       <c r="H46" s="34"/>
       <c r="I46" s="56"/>
       <c r="J46" s="60"/>
@@ -7488,11 +7485,11 @@
       <c r="M46" s="80"/>
       <c r="N46" s="61"/>
       <c r="O46" s="37"/>
-      <c r="P46" s="116"/>
-      <c r="Q46" s="117"/>
-      <c r="R46" s="117"/>
-      <c r="S46" s="117"/>
-      <c r="T46" s="117"/>
+      <c r="P46" s="115"/>
+      <c r="Q46" s="116"/>
+      <c r="R46" s="116"/>
+      <c r="S46" s="116"/>
+      <c r="T46" s="116"/>
       <c r="U46" s="74">
         <f>(I45*P46)+(J45*Q46)+(K45*R46)+(L45*S46)+(M45*T46)</f>
         <v>0</v>
@@ -7506,7 +7503,7 @@
       <c r="AB46" s="70"/>
       <c r="AC46" s="75"/>
       <c r="AD46" s="71"/>
-      <c r="AE46" s="100"/>
+      <c r="AE46" s="99"/>
       <c r="AF46" s="43"/>
       <c r="AG46" s="64"/>
       <c r="AH46" s="44"/>
@@ -7521,14 +7518,14 @@
     <row r="47" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="84"/>
       <c r="B47" s="82"/>
-      <c r="C47" s="119"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="113"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="118"/>
+      <c r="G47" s="112"/>
       <c r="H47" s="34"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="36"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="60"/>
       <c r="K47" s="36"/>
       <c r="L47" s="60"/>
       <c r="M47" s="81"/>
@@ -7537,11 +7534,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="37"/>
-      <c r="P47" s="114"/>
-      <c r="Q47" s="115"/>
-      <c r="R47" s="115"/>
-      <c r="S47" s="115"/>
-      <c r="T47" s="115"/>
+      <c r="P47" s="113"/>
+      <c r="Q47" s="114"/>
+      <c r="R47" s="114"/>
+      <c r="S47" s="114"/>
+      <c r="T47" s="114"/>
       <c r="U47" s="40">
         <f>ROUND(((P47*I47)+(Q47*J47)+(R47*K47)+(S47*L47)+(T47*M47)),3)</f>
         <v>0</v>
@@ -7567,14 +7564,14 @@
         <f>IF(AC47&gt;=11,11,AC47)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE47" s="100">
+      <c r="AE47" s="99">
         <f>IF(U48&gt;=94,4,IF(U48&gt;=91,3.9,IF(U48&gt;=88,3.8,IF(U48&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF47" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG47" s="101">
+      <c r="AG47" s="100">
         <v>17</v>
       </c>
       <c r="AH47" s="44" t="e">
@@ -7601,13 +7598,13 @@
     <row r="48" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="85"/>
       <c r="B48" s="83"/>
-      <c r="C48" s="155" t="s">
+      <c r="C48" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D48" s="156"/>
-      <c r="E48" s="156"/>
-      <c r="F48" s="156"/>
-      <c r="G48" s="157"/>
+      <c r="D48" s="123"/>
+      <c r="E48" s="123"/>
+      <c r="F48" s="123"/>
+      <c r="G48" s="124"/>
       <c r="H48" s="34"/>
       <c r="I48" s="56"/>
       <c r="J48" s="60"/>
@@ -7616,11 +7613,11 @@
       <c r="M48" s="80"/>
       <c r="N48" s="61"/>
       <c r="O48" s="37"/>
-      <c r="P48" s="116"/>
-      <c r="Q48" s="115"/>
-      <c r="R48" s="115"/>
-      <c r="S48" s="117"/>
-      <c r="T48" s="117"/>
+      <c r="P48" s="115"/>
+      <c r="Q48" s="114"/>
+      <c r="R48" s="114"/>
+      <c r="S48" s="116"/>
+      <c r="T48" s="116"/>
       <c r="U48" s="74">
         <f>(I47*P48)+(J47*Q48)+(K47*R48)+(L47*S48)+(M47*T48)</f>
         <v>0</v>
@@ -7634,7 +7631,7 @@
       <c r="AB48" s="70"/>
       <c r="AC48" s="75"/>
       <c r="AD48" s="71"/>
-      <c r="AE48" s="100"/>
+      <c r="AE48" s="99"/>
       <c r="AF48" s="43"/>
       <c r="AG48" s="64"/>
       <c r="AH48" s="44"/>
@@ -7649,14 +7646,14 @@
     <row r="49" spans="1:41" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="84"/>
       <c r="B49" s="82"/>
-      <c r="C49" s="119"/>
-      <c r="D49" s="118"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="113"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="G49" s="112"/>
       <c r="H49" s="34"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="35"/>
+      <c r="I49" s="60"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="36"/>
       <c r="L49" s="36"/>
       <c r="M49" s="81"/>
@@ -7665,11 +7662,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="37"/>
-      <c r="P49" s="114"/>
-      <c r="Q49" s="115"/>
-      <c r="R49" s="115"/>
-      <c r="S49" s="115"/>
-      <c r="T49" s="115"/>
+      <c r="P49" s="113"/>
+      <c r="Q49" s="114"/>
+      <c r="R49" s="114"/>
+      <c r="S49" s="114"/>
+      <c r="T49" s="114"/>
       <c r="U49" s="40">
         <f>ROUND(((P49*I49)+(Q49*J49)+(R49*K49)+(S49*L49)+(T49*M49)),3)</f>
         <v>0</v>
@@ -7695,14 +7692,14 @@
         <f t="shared" ref="AD49" si="27">IF(AC49&gt;=11,11,AC49)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE49" s="100">
+      <c r="AE49" s="99">
         <f>IF(U50&gt;=94,4,IF(U50&gt;=91,3.9,IF(U50&gt;=88,3.8,IF(U50&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF49" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG49" s="101">
+      <c r="AG49" s="100">
         <v>17</v>
       </c>
       <c r="AH49" s="44" t="e">
@@ -7729,13 +7726,13 @@
     <row r="50" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="85"/>
       <c r="B50" s="83"/>
-      <c r="C50" s="155" t="s">
+      <c r="C50" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D50" s="156"/>
-      <c r="E50" s="156"/>
-      <c r="F50" s="156"/>
-      <c r="G50" s="157"/>
+      <c r="D50" s="123"/>
+      <c r="E50" s="123"/>
+      <c r="F50" s="123"/>
+      <c r="G50" s="124"/>
       <c r="H50" s="34"/>
       <c r="I50" s="56"/>
       <c r="J50" s="60"/>
@@ -7744,11 +7741,11 @@
       <c r="M50" s="80"/>
       <c r="N50" s="61"/>
       <c r="O50" s="37"/>
-      <c r="P50" s="116"/>
-      <c r="Q50" s="117"/>
-      <c r="R50" s="117"/>
-      <c r="S50" s="117"/>
-      <c r="T50" s="117"/>
+      <c r="P50" s="115"/>
+      <c r="Q50" s="116"/>
+      <c r="R50" s="116"/>
+      <c r="S50" s="116"/>
+      <c r="T50" s="116"/>
       <c r="U50" s="74">
         <f>(I49*P50)+(J49*Q50)+(K49*R50)+(L49*S50)+(M49*T50)</f>
         <v>0</v>
@@ -7762,7 +7759,7 @@
       <c r="AB50" s="70"/>
       <c r="AC50" s="75"/>
       <c r="AD50" s="71"/>
-      <c r="AE50" s="100"/>
+      <c r="AE50" s="99"/>
       <c r="AF50" s="43"/>
       <c r="AG50" s="64"/>
       <c r="AH50" s="44"/>
@@ -7777,14 +7774,14 @@
     <row r="51" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="84"/>
       <c r="B51" s="82"/>
-      <c r="C51" s="119"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="113"/>
+      <c r="C51" s="118"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="118"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="112"/>
       <c r="H51" s="57"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="36"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="60"/>
       <c r="K51" s="36"/>
       <c r="L51" s="36"/>
       <c r="M51" s="81"/>
@@ -7793,11 +7790,11 @@
         <v>0</v>
       </c>
       <c r="O51" s="37"/>
-      <c r="P51" s="114"/>
-      <c r="Q51" s="115"/>
-      <c r="R51" s="115"/>
-      <c r="S51" s="115"/>
-      <c r="T51" s="115"/>
+      <c r="P51" s="113"/>
+      <c r="Q51" s="114"/>
+      <c r="R51" s="114"/>
+      <c r="S51" s="114"/>
+      <c r="T51" s="114"/>
       <c r="U51" s="40">
         <f>ROUND(((P51*I51)+(Q51*J51)+(R51*K51)+(S51*L51)+(T51*M51)),3)</f>
         <v>0</v>
@@ -7823,14 +7820,14 @@
         <f t="shared" ref="AD51" si="29">IF(AC51&gt;=11,11,AC51)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE51" s="100">
+      <c r="AE51" s="99">
         <f>IF(U52&gt;=94,4,IF(U52&gt;=91,3.9,IF(U52&gt;=88,3.8,IF(U52&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF51" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG51" s="101">
+      <c r="AG51" s="100">
         <v>17</v>
       </c>
       <c r="AH51" s="44" t="e">
@@ -7857,13 +7854,13 @@
     <row r="52" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="85"/>
       <c r="B52" s="83"/>
-      <c r="C52" s="155" t="s">
+      <c r="C52" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="156"/>
-      <c r="E52" s="156"/>
-      <c r="F52" s="156"/>
-      <c r="G52" s="157"/>
+      <c r="D52" s="123"/>
+      <c r="E52" s="123"/>
+      <c r="F52" s="123"/>
+      <c r="G52" s="124"/>
       <c r="H52" s="34"/>
       <c r="I52" s="56"/>
       <c r="J52" s="60"/>
@@ -7872,11 +7869,11 @@
       <c r="M52" s="80"/>
       <c r="N52" s="61"/>
       <c r="O52" s="37"/>
-      <c r="P52" s="116"/>
-      <c r="Q52" s="115"/>
-      <c r="R52" s="117"/>
-      <c r="S52" s="117"/>
-      <c r="T52" s="117"/>
+      <c r="P52" s="115"/>
+      <c r="Q52" s="114"/>
+      <c r="R52" s="116"/>
+      <c r="S52" s="116"/>
+      <c r="T52" s="116"/>
       <c r="U52" s="74">
         <f>(I51*P52)+(J51*Q52)+(K51*R52)+(L51*S52)+(M51*T52)</f>
         <v>0</v>
@@ -7890,7 +7887,7 @@
       <c r="AB52" s="70"/>
       <c r="AC52" s="75"/>
       <c r="AD52" s="71"/>
-      <c r="AE52" s="100"/>
+      <c r="AE52" s="99"/>
       <c r="AF52" s="43"/>
       <c r="AG52" s="64"/>
       <c r="AH52" s="44"/>
@@ -7905,14 +7902,14 @@
     <row r="53" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="84"/>
       <c r="B53" s="82"/>
-      <c r="C53" s="119"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="113"/>
+      <c r="C53" s="118"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="112"/>
       <c r="H53" s="57"/>
-      <c r="I53" s="35"/>
-      <c r="J53" s="36"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="60"/>
       <c r="K53" s="36"/>
       <c r="L53" s="36"/>
       <c r="M53" s="81"/>
@@ -7921,11 +7918,11 @@
         <v>0</v>
       </c>
       <c r="O53" s="37"/>
-      <c r="P53" s="114"/>
-      <c r="Q53" s="115"/>
-      <c r="R53" s="115"/>
-      <c r="S53" s="115"/>
-      <c r="T53" s="115"/>
+      <c r="P53" s="113"/>
+      <c r="Q53" s="114"/>
+      <c r="R53" s="114"/>
+      <c r="S53" s="114"/>
+      <c r="T53" s="114"/>
       <c r="U53" s="40">
         <f>ROUND(((P53*I53)+(Q53*J53)+(R53*K53)+(S53*L53)+(T53*M53)),3)</f>
         <v>0</v>
@@ -7951,14 +7948,14 @@
         <f t="shared" ref="AD53" si="31">IF(AC53&gt;=11,11,AC53)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE53" s="100">
+      <c r="AE53" s="99">
         <f>IF(U54&gt;=94,4,IF(U54&gt;=91,3.9,IF(U54&gt;=88,3.8,IF(U54&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF53" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG53" s="101">
+      <c r="AG53" s="100">
         <v>17</v>
       </c>
       <c r="AH53" s="44" t="e">
@@ -7985,13 +7982,13 @@
     <row r="54" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="85"/>
       <c r="B54" s="83"/>
-      <c r="C54" s="155" t="s">
+      <c r="C54" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="156"/>
-      <c r="E54" s="156"/>
-      <c r="F54" s="156"/>
-      <c r="G54" s="157"/>
+      <c r="D54" s="123"/>
+      <c r="E54" s="123"/>
+      <c r="F54" s="123"/>
+      <c r="G54" s="124"/>
       <c r="H54" s="34"/>
       <c r="I54" s="56"/>
       <c r="J54" s="60"/>
@@ -8000,11 +7997,11 @@
       <c r="M54" s="80"/>
       <c r="N54" s="61"/>
       <c r="O54" s="37"/>
-      <c r="P54" s="116"/>
-      <c r="Q54" s="116"/>
-      <c r="R54" s="117"/>
-      <c r="S54" s="117"/>
-      <c r="T54" s="117"/>
+      <c r="P54" s="115"/>
+      <c r="Q54" s="115"/>
+      <c r="R54" s="116"/>
+      <c r="S54" s="116"/>
+      <c r="T54" s="116"/>
       <c r="U54" s="74">
         <f>(I53*P54)+(J53*Q54)+(K53*R54)+(L53*S54)+(M53*T54)</f>
         <v>0</v>
@@ -8018,7 +8015,7 @@
       <c r="AB54" s="70"/>
       <c r="AC54" s="75"/>
       <c r="AD54" s="71"/>
-      <c r="AE54" s="100"/>
+      <c r="AE54" s="99"/>
       <c r="AF54" s="43"/>
       <c r="AG54" s="64"/>
       <c r="AH54" s="44"/>
@@ -8033,14 +8030,14 @@
     <row r="55" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="84"/>
       <c r="B55" s="82"/>
-      <c r="C55" s="119"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="119"/>
-      <c r="F55" s="119"/>
-      <c r="G55" s="113"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="117"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="112"/>
       <c r="H55" s="57"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="36"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="60"/>
       <c r="K55" s="36"/>
       <c r="L55" s="60"/>
       <c r="M55" s="81"/>
@@ -8049,11 +8046,11 @@
         <v>0</v>
       </c>
       <c r="O55" s="37"/>
-      <c r="P55" s="114"/>
-      <c r="Q55" s="115"/>
-      <c r="R55" s="115"/>
-      <c r="S55" s="115"/>
-      <c r="T55" s="115"/>
+      <c r="P55" s="113"/>
+      <c r="Q55" s="114"/>
+      <c r="R55" s="114"/>
+      <c r="S55" s="114"/>
+      <c r="T55" s="114"/>
       <c r="U55" s="40">
         <f>ROUND(((P55*I55)+(Q55*J55)+(R55*K55)+(S55*L55)+(T55*M55)),3)</f>
         <v>0</v>
@@ -8079,14 +8076,14 @@
         <f t="shared" ref="AD55" si="33">IF(AC55&gt;=11,11,AC55)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE55" s="100">
+      <c r="AE55" s="99">
         <f>IF(U56&gt;=94,4,IF(U56&gt;=91,3.9,IF(U56&gt;=88,3.8,IF(U56&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF55" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG55" s="101">
+      <c r="AG55" s="100">
         <v>17</v>
       </c>
       <c r="AH55" s="44" t="e">
@@ -8113,13 +8110,13 @@
     <row r="56" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="85"/>
       <c r="B56" s="83"/>
-      <c r="C56" s="155" t="s">
+      <c r="C56" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D56" s="156"/>
-      <c r="E56" s="156"/>
-      <c r="F56" s="156"/>
-      <c r="G56" s="157"/>
+      <c r="D56" s="123"/>
+      <c r="E56" s="123"/>
+      <c r="F56" s="123"/>
+      <c r="G56" s="124"/>
       <c r="H56" s="34"/>
       <c r="I56" s="56"/>
       <c r="J56" s="60"/>
@@ -8128,11 +8125,11 @@
       <c r="M56" s="80"/>
       <c r="N56" s="61"/>
       <c r="O56" s="37"/>
-      <c r="P56" s="116"/>
-      <c r="Q56" s="116"/>
-      <c r="R56" s="116"/>
-      <c r="S56" s="117"/>
-      <c r="T56" s="117"/>
+      <c r="P56" s="115"/>
+      <c r="Q56" s="115"/>
+      <c r="R56" s="115"/>
+      <c r="S56" s="116"/>
+      <c r="T56" s="116"/>
       <c r="U56" s="74">
         <f>(I55*P56)+(J55*Q56)+(K55*R56)+(L55*S56)+(M55*T56)</f>
         <v>0</v>
@@ -8146,7 +8143,7 @@
       <c r="AB56" s="70"/>
       <c r="AC56" s="75"/>
       <c r="AD56" s="71"/>
-      <c r="AE56" s="100"/>
+      <c r="AE56" s="99"/>
       <c r="AF56" s="43"/>
       <c r="AG56" s="64"/>
       <c r="AH56" s="44"/>
@@ -8161,27 +8158,27 @@
     <row r="57" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="84"/>
       <c r="B57" s="82"/>
-      <c r="C57" s="119"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="119"/>
-      <c r="F57" s="119"/>
-      <c r="G57" s="113"/>
+      <c r="C57" s="118"/>
+      <c r="D57" s="117"/>
+      <c r="E57" s="118"/>
+      <c r="F57" s="118"/>
+      <c r="G57" s="112"/>
       <c r="H57" s="34"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="87"/>
-      <c r="K57" s="87"/>
-      <c r="L57" s="87"/>
-      <c r="M57" s="105"/>
-      <c r="N57" s="104">
+      <c r="I57" s="88"/>
+      <c r="J57" s="89"/>
+      <c r="K57" s="86"/>
+      <c r="L57" s="86"/>
+      <c r="M57" s="104"/>
+      <c r="N57" s="103">
         <f>SUM(I57:M57)</f>
         <v>0</v>
       </c>
       <c r="O57" s="37"/>
-      <c r="P57" s="114"/>
-      <c r="Q57" s="114"/>
-      <c r="R57" s="115"/>
-      <c r="S57" s="115"/>
-      <c r="T57" s="115"/>
+      <c r="P57" s="113"/>
+      <c r="Q57" s="113"/>
+      <c r="R57" s="114"/>
+      <c r="S57" s="114"/>
+      <c r="T57" s="114"/>
       <c r="U57" s="40">
         <f>ROUND(((P57*I57)+(Q57*J57)+(R57*K57)+(S57*L57)+(T57*M57)),3)</f>
         <v>0</v>
@@ -8207,14 +8204,14 @@
         <f t="shared" ref="AD57" si="35">IF(AC57&gt;=11,11,AC57)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE57" s="100">
+      <c r="AE57" s="99">
         <f>IF(U58&gt;=94,4,IF(U58&gt;=91,3.9,IF(U58&gt;=88,3.8,IF(U58&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF57" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG57" s="101">
+      <c r="AG57" s="100">
         <v>17</v>
       </c>
       <c r="AH57" s="44" t="e">
@@ -8235,26 +8232,26 @@
     <row r="58" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="85"/>
       <c r="B58" s="83"/>
-      <c r="C58" s="155" t="s">
+      <c r="C58" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D58" s="156"/>
-      <c r="E58" s="156"/>
-      <c r="F58" s="156"/>
-      <c r="G58" s="157"/>
-      <c r="H58" s="88"/>
-      <c r="I58" s="89"/>
-      <c r="J58" s="90"/>
-      <c r="K58" s="90"/>
-      <c r="L58" s="90"/>
-      <c r="M58" s="106"/>
-      <c r="N58" s="104"/>
+      <c r="D58" s="123"/>
+      <c r="E58" s="123"/>
+      <c r="F58" s="123"/>
+      <c r="G58" s="124"/>
+      <c r="H58" s="87"/>
+      <c r="I58" s="88"/>
+      <c r="J58" s="89"/>
+      <c r="K58" s="89"/>
+      <c r="L58" s="89"/>
+      <c r="M58" s="105"/>
+      <c r="N58" s="103"/>
       <c r="O58" s="37"/>
-      <c r="P58" s="117"/>
-      <c r="Q58" s="117"/>
-      <c r="R58" s="117"/>
-      <c r="S58" s="117"/>
-      <c r="T58" s="117"/>
+      <c r="P58" s="116"/>
+      <c r="Q58" s="116"/>
+      <c r="R58" s="116"/>
+      <c r="S58" s="116"/>
+      <c r="T58" s="116"/>
       <c r="U58" s="74">
         <f>(I57*P58)+(J57*Q58)+(K57*R58)+(L57*S58)+(M57*T58)</f>
         <v>0</v>
@@ -8268,7 +8265,7 @@
       <c r="AB58" s="70"/>
       <c r="AC58" s="75"/>
       <c r="AD58" s="71"/>
-      <c r="AE58" s="100"/>
+      <c r="AE58" s="99"/>
       <c r="AF58" s="43"/>
       <c r="AG58" s="64"/>
       <c r="AH58" s="44"/>
@@ -8283,14 +8280,14 @@
     <row r="59" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="84"/>
       <c r="B59" s="82"/>
-      <c r="C59" s="119"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="119"/>
-      <c r="F59" s="119"/>
-      <c r="G59" s="113"/>
+      <c r="C59" s="118"/>
+      <c r="D59" s="117"/>
+      <c r="E59" s="118"/>
+      <c r="F59" s="118"/>
+      <c r="G59" s="112"/>
       <c r="H59" s="34"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="36"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="60"/>
       <c r="K59" s="36"/>
       <c r="L59" s="36"/>
       <c r="M59" s="81"/>
@@ -8299,11 +8296,11 @@
         <v>0</v>
       </c>
       <c r="O59" s="37"/>
-      <c r="P59" s="114"/>
-      <c r="Q59" s="115"/>
-      <c r="R59" s="115"/>
-      <c r="S59" s="115"/>
-      <c r="T59" s="115"/>
+      <c r="P59" s="113"/>
+      <c r="Q59" s="114"/>
+      <c r="R59" s="114"/>
+      <c r="S59" s="114"/>
+      <c r="T59" s="114"/>
       <c r="U59" s="40">
         <f>ROUND(((P59*I59)+(Q59*J59)+(R59*K59)+(S59*L59)+(T59*M59)),3)</f>
         <v>0</v>
@@ -8329,14 +8326,14 @@
         <f t="shared" ref="AD59" si="37">IF(AC59&gt;=11,11,AC59)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE59" s="100">
+      <c r="AE59" s="99">
         <f>IF(U60&gt;=94,4,IF(U60&gt;=91,3.9,IF(U60&gt;=88,3.8,IF(U60&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF59" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG59" s="101">
+      <c r="AG59" s="100">
         <v>17</v>
       </c>
       <c r="AH59" s="44" t="e">
@@ -8363,13 +8360,13 @@
     <row r="60" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="85"/>
       <c r="B60" s="83"/>
-      <c r="C60" s="155" t="s">
+      <c r="C60" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D60" s="156"/>
-      <c r="E60" s="156"/>
-      <c r="F60" s="156"/>
-      <c r="G60" s="157"/>
+      <c r="D60" s="123"/>
+      <c r="E60" s="123"/>
+      <c r="F60" s="123"/>
+      <c r="G60" s="124"/>
       <c r="H60" s="34"/>
       <c r="I60" s="56"/>
       <c r="J60" s="60"/>
@@ -8378,11 +8375,11 @@
       <c r="M60" s="80"/>
       <c r="N60" s="61"/>
       <c r="O60" s="37"/>
-      <c r="P60" s="116"/>
-      <c r="Q60" s="117"/>
-      <c r="R60" s="117"/>
-      <c r="S60" s="117"/>
-      <c r="T60" s="117"/>
+      <c r="P60" s="115"/>
+      <c r="Q60" s="116"/>
+      <c r="R60" s="116"/>
+      <c r="S60" s="116"/>
+      <c r="T60" s="116"/>
       <c r="U60" s="74">
         <f>(I59*P60)+(J59*Q60)+(K59*R60)+(L59*S60)+(M59*T60)</f>
         <v>0</v>
@@ -8396,7 +8393,7 @@
       <c r="AB60" s="70"/>
       <c r="AC60" s="75"/>
       <c r="AD60" s="71"/>
-      <c r="AE60" s="100"/>
+      <c r="AE60" s="99"/>
       <c r="AF60" s="43"/>
       <c r="AG60" s="64"/>
       <c r="AH60" s="44"/>
@@ -8411,14 +8408,14 @@
     <row r="61" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="84"/>
       <c r="B61" s="82"/>
-      <c r="C61" s="119"/>
-      <c r="D61" s="118"/>
-      <c r="E61" s="119"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="113"/>
+      <c r="C61" s="118"/>
+      <c r="D61" s="117"/>
+      <c r="E61" s="118"/>
+      <c r="F61" s="118"/>
+      <c r="G61" s="112"/>
       <c r="H61" s="34"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="36"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="60"/>
       <c r="K61" s="36"/>
       <c r="L61" s="36"/>
       <c r="M61" s="81"/>
@@ -8427,11 +8424,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="37"/>
-      <c r="P61" s="114"/>
-      <c r="Q61" s="115"/>
-      <c r="R61" s="115"/>
-      <c r="S61" s="115"/>
-      <c r="T61" s="115"/>
+      <c r="P61" s="113"/>
+      <c r="Q61" s="114"/>
+      <c r="R61" s="114"/>
+      <c r="S61" s="114"/>
+      <c r="T61" s="114"/>
       <c r="U61" s="40">
         <f>ROUND(((P61*I61)+(Q61*J61)+(R61*K61)+(S61*L61)+(T61*M61)),3)</f>
         <v>0</v>
@@ -8457,14 +8454,14 @@
         <f>IF(AC61&gt;=11,11,AC61)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE61" s="100">
+      <c r="AE61" s="99">
         <f>IF(U62&gt;=94,4,IF(U62&gt;=91,3.9,IF(U62&gt;=88,3.8,IF(U62&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF61" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG61" s="101">
+      <c r="AG61" s="100">
         <v>17</v>
       </c>
       <c r="AH61" s="44" t="e">
@@ -8491,13 +8488,13 @@
     <row r="62" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="85"/>
       <c r="B62" s="83"/>
-      <c r="C62" s="155" t="s">
+      <c r="C62" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D62" s="156"/>
-      <c r="E62" s="156"/>
-      <c r="F62" s="156"/>
-      <c r="G62" s="157"/>
+      <c r="D62" s="123"/>
+      <c r="E62" s="123"/>
+      <c r="F62" s="123"/>
+      <c r="G62" s="124"/>
       <c r="H62" s="34"/>
       <c r="I62" s="56"/>
       <c r="J62" s="60"/>
@@ -8506,11 +8503,11 @@
       <c r="M62" s="80"/>
       <c r="N62" s="61"/>
       <c r="O62" s="37"/>
-      <c r="P62" s="117"/>
-      <c r="Q62" s="117"/>
-      <c r="R62" s="117"/>
-      <c r="S62" s="117"/>
-      <c r="T62" s="117"/>
+      <c r="P62" s="116"/>
+      <c r="Q62" s="116"/>
+      <c r="R62" s="116"/>
+      <c r="S62" s="116"/>
+      <c r="T62" s="116"/>
       <c r="U62" s="74">
         <f>(I61*P62)+(J61*Q62)+(K61*R62)+(L61*S62)+(M61*T62)</f>
         <v>0</v>
@@ -8524,7 +8521,7 @@
       <c r="AB62" s="70"/>
       <c r="AC62" s="75"/>
       <c r="AD62" s="71"/>
-      <c r="AE62" s="100"/>
+      <c r="AE62" s="99"/>
       <c r="AF62" s="43"/>
       <c r="AG62" s="64"/>
       <c r="AH62" s="44"/>
@@ -8538,15 +8535,15 @@
     </row>
     <row r="63" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="84"/>
-      <c r="B63" s="91"/>
-      <c r="C63" s="119"/>
-      <c r="D63" s="118"/>
-      <c r="E63" s="119"/>
-      <c r="F63" s="119"/>
-      <c r="G63" s="113"/>
+      <c r="B63" s="90"/>
+      <c r="C63" s="118"/>
+      <c r="D63" s="117"/>
+      <c r="E63" s="118"/>
+      <c r="F63" s="118"/>
+      <c r="G63" s="112"/>
       <c r="H63" s="57"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="36"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="60"/>
       <c r="K63" s="36"/>
       <c r="L63" s="36"/>
       <c r="M63" s="81"/>
@@ -8555,11 +8552,11 @@
         <v>0</v>
       </c>
       <c r="O63" s="37"/>
-      <c r="P63" s="114"/>
-      <c r="Q63" s="115"/>
-      <c r="R63" s="115"/>
-      <c r="S63" s="115"/>
-      <c r="T63" s="115"/>
+      <c r="P63" s="113"/>
+      <c r="Q63" s="114"/>
+      <c r="R63" s="114"/>
+      <c r="S63" s="114"/>
+      <c r="T63" s="114"/>
       <c r="U63" s="40">
         <f>ROUND(((P63*I63)+(Q63*J63)+(R63*K63)+(S63*L63)+(T63*M63)),3)</f>
         <v>0</v>
@@ -8585,14 +8582,14 @@
         <f>IF(AC63&gt;=11,11,AC63)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE63" s="100">
+      <c r="AE63" s="99">
         <f>IF(U64&gt;=94,4,IF(U64&gt;=91,3.9,IF(U64&gt;=88,3.8,IF(U64&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF63" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG63" s="101">
+      <c r="AG63" s="100">
         <v>17</v>
       </c>
       <c r="AH63" s="44" t="e">
@@ -8619,13 +8616,13 @@
     <row r="64" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="85"/>
       <c r="B64" s="83"/>
-      <c r="C64" s="155" t="s">
+      <c r="C64" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D64" s="156"/>
-      <c r="E64" s="156"/>
-      <c r="F64" s="156"/>
-      <c r="G64" s="157"/>
+      <c r="D64" s="123"/>
+      <c r="E64" s="123"/>
+      <c r="F64" s="123"/>
+      <c r="G64" s="124"/>
       <c r="H64" s="34"/>
       <c r="I64" s="56"/>
       <c r="J64" s="60"/>
@@ -8634,11 +8631,11 @@
       <c r="M64" s="80"/>
       <c r="N64" s="61"/>
       <c r="O64" s="37"/>
-      <c r="P64" s="117"/>
-      <c r="Q64" s="117"/>
-      <c r="R64" s="117"/>
-      <c r="S64" s="117"/>
-      <c r="T64" s="117"/>
+      <c r="P64" s="116"/>
+      <c r="Q64" s="116"/>
+      <c r="R64" s="116"/>
+      <c r="S64" s="116"/>
+      <c r="T64" s="116"/>
       <c r="U64" s="74">
         <f>(I63*P64)+(J63*Q64)+(K63*R64)+(L63*S64)+(M63*T64)</f>
         <v>0</v>
@@ -8652,7 +8649,7 @@
       <c r="AB64" s="70"/>
       <c r="AC64" s="75"/>
       <c r="AD64" s="71"/>
-      <c r="AE64" s="100"/>
+      <c r="AE64" s="99"/>
       <c r="AF64" s="43"/>
       <c r="AG64" s="64"/>
       <c r="AH64" s="44"/>
@@ -8667,14 +8664,14 @@
     <row r="65" spans="1:41" s="22" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="84"/>
       <c r="B65" s="82"/>
-      <c r="C65" s="119"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="119"/>
-      <c r="F65" s="119"/>
-      <c r="G65" s="113"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="117"/>
+      <c r="E65" s="118"/>
+      <c r="F65" s="118"/>
+      <c r="G65" s="112"/>
       <c r="H65" s="57"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="36"/>
+      <c r="I65" s="56"/>
+      <c r="J65" s="60"/>
       <c r="K65" s="36"/>
       <c r="L65" s="36"/>
       <c r="M65" s="81"/>
@@ -8683,11 +8680,11 @@
         <v>0</v>
       </c>
       <c r="O65" s="37"/>
-      <c r="P65" s="114"/>
-      <c r="Q65" s="115"/>
-      <c r="R65" s="115"/>
-      <c r="S65" s="115"/>
-      <c r="T65" s="115"/>
+      <c r="P65" s="113"/>
+      <c r="Q65" s="114"/>
+      <c r="R65" s="114"/>
+      <c r="S65" s="114"/>
+      <c r="T65" s="114"/>
       <c r="U65" s="40">
         <f>ROUND(((P65*I65)+(Q65*J65)+(R65*K65)+(S65*L65)+(T65*M65)),3)</f>
         <v>0</v>
@@ -8713,14 +8710,14 @@
         <f t="shared" ref="AD65" si="39">IF(AC65&gt;=11,11,AC65)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE65" s="100">
+      <c r="AE65" s="99">
         <f>IF(U66&gt;=94,4,IF(U66&gt;=91,3.9,IF(U66&gt;=88,3.8,IF(U66&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF65" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG65" s="101">
+      <c r="AG65" s="100">
         <v>17</v>
       </c>
       <c r="AH65" s="44" t="e">
@@ -8747,13 +8744,13 @@
     <row r="66" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="85"/>
       <c r="B66" s="83"/>
-      <c r="C66" s="155" t="s">
+      <c r="C66" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D66" s="156"/>
-      <c r="E66" s="156"/>
-      <c r="F66" s="156"/>
-      <c r="G66" s="157"/>
+      <c r="D66" s="123"/>
+      <c r="E66" s="123"/>
+      <c r="F66" s="123"/>
+      <c r="G66" s="124"/>
       <c r="H66" s="34"/>
       <c r="I66" s="56"/>
       <c r="J66" s="60"/>
@@ -8762,11 +8759,11 @@
       <c r="M66" s="80"/>
       <c r="N66" s="61"/>
       <c r="O66" s="37"/>
-      <c r="P66" s="116"/>
-      <c r="Q66" s="117"/>
-      <c r="R66" s="117"/>
-      <c r="S66" s="117"/>
-      <c r="T66" s="117"/>
+      <c r="P66" s="115"/>
+      <c r="Q66" s="116"/>
+      <c r="R66" s="116"/>
+      <c r="S66" s="116"/>
+      <c r="T66" s="116"/>
       <c r="U66" s="74">
         <f>(I65*P66)+(J65*Q66)+(K65*R66)+(L65*S66)+(M65*T66)</f>
         <v>0</v>
@@ -8780,7 +8777,7 @@
       <c r="AB66" s="70"/>
       <c r="AC66" s="75"/>
       <c r="AD66" s="71"/>
-      <c r="AE66" s="100"/>
+      <c r="AE66" s="99"/>
       <c r="AF66" s="43"/>
       <c r="AG66" s="64"/>
       <c r="AH66" s="44"/>
@@ -8795,14 +8792,14 @@
     <row r="67" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="84"/>
       <c r="B67" s="82"/>
-      <c r="C67" s="119"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="119"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="113"/>
+      <c r="C67" s="118"/>
+      <c r="D67" s="117"/>
+      <c r="E67" s="118"/>
+      <c r="F67" s="118"/>
+      <c r="G67" s="112"/>
       <c r="H67" s="57"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="36"/>
+      <c r="I67" s="56"/>
+      <c r="J67" s="60"/>
       <c r="K67" s="36"/>
       <c r="L67" s="60"/>
       <c r="M67" s="81"/>
@@ -8811,11 +8808,11 @@
         <v>0</v>
       </c>
       <c r="O67" s="37"/>
-      <c r="P67" s="114"/>
-      <c r="Q67" s="115"/>
-      <c r="R67" s="115"/>
-      <c r="S67" s="115"/>
-      <c r="T67" s="115"/>
+      <c r="P67" s="113"/>
+      <c r="Q67" s="114"/>
+      <c r="R67" s="114"/>
+      <c r="S67" s="114"/>
+      <c r="T67" s="114"/>
       <c r="U67" s="40">
         <f>ROUND(((P67*I67)+(Q67*J67)+(R67*K67)+(S67*L67)+(T67*M67)),3)</f>
         <v>0</v>
@@ -8841,14 +8838,14 @@
         <f t="shared" ref="AD67" si="41">IF(AC67&gt;=11,11,AC67)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE67" s="100">
+      <c r="AE67" s="99">
         <f>IF(U68&gt;=94,4,IF(U68&gt;=91,3.9,IF(U68&gt;=88,3.8,IF(U68&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF67" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG67" s="101">
+      <c r="AG67" s="100">
         <v>17</v>
       </c>
       <c r="AH67" s="44" t="e">
@@ -8875,13 +8872,13 @@
     <row r="68" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="85"/>
       <c r="B68" s="83"/>
-      <c r="C68" s="155" t="s">
+      <c r="C68" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="D68" s="156"/>
-      <c r="E68" s="156"/>
-      <c r="F68" s="156"/>
-      <c r="G68" s="157"/>
+      <c r="D68" s="123"/>
+      <c r="E68" s="123"/>
+      <c r="F68" s="123"/>
+      <c r="G68" s="124"/>
       <c r="H68" s="34"/>
       <c r="I68" s="56"/>
       <c r="J68" s="60"/>
@@ -8890,11 +8887,11 @@
       <c r="M68" s="80"/>
       <c r="N68" s="61"/>
       <c r="O68" s="37"/>
-      <c r="P68" s="116"/>
-      <c r="Q68" s="115"/>
-      <c r="R68" s="115"/>
-      <c r="S68" s="117"/>
-      <c r="T68" s="117"/>
+      <c r="P68" s="115"/>
+      <c r="Q68" s="114"/>
+      <c r="R68" s="114"/>
+      <c r="S68" s="116"/>
+      <c r="T68" s="116"/>
       <c r="U68" s="74">
         <f>(I67*P68)+(J67*Q68)+(K67*R68)+(L67*S68)+(M67*T68)</f>
         <v>0</v>
@@ -8908,7 +8905,7 @@
       <c r="AB68" s="70"/>
       <c r="AC68" s="75"/>
       <c r="AD68" s="71"/>
-      <c r="AE68" s="100"/>
+      <c r="AE68" s="99"/>
       <c r="AF68" s="43"/>
       <c r="AG68" s="64"/>
       <c r="AH68" s="44"/>
@@ -8923,14 +8920,14 @@
     <row r="69" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="84"/>
       <c r="B69" s="82"/>
-      <c r="C69" s="119"/>
-      <c r="D69" s="118"/>
-      <c r="E69" s="119"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="113"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="117"/>
+      <c r="E69" s="118"/>
+      <c r="F69" s="118"/>
+      <c r="G69" s="112"/>
       <c r="H69" s="57"/>
-      <c r="I69" s="35"/>
-      <c r="J69" s="36"/>
+      <c r="I69" s="56"/>
+      <c r="J69" s="60"/>
       <c r="K69" s="36"/>
       <c r="L69" s="36"/>
       <c r="M69" s="81"/>
@@ -8939,11 +8936,11 @@
         <v>0</v>
       </c>
       <c r="O69" s="37"/>
-      <c r="P69" s="114"/>
-      <c r="Q69" s="115"/>
-      <c r="R69" s="115"/>
-      <c r="S69" s="115"/>
-      <c r="T69" s="115"/>
+      <c r="P69" s="113"/>
+      <c r="Q69" s="114"/>
+      <c r="R69" s="114"/>
+      <c r="S69" s="114"/>
+      <c r="T69" s="114"/>
       <c r="U69" s="40">
         <f>ROUND(((P69*I69)+(Q69*J69)+(R69*K69)+(S69*L69)+(T69*M69)),3)</f>
         <v>0</v>
@@ -8969,14 +8966,14 @@
         <f t="shared" ref="AD69" si="43">IF(AC69&gt;=11,11,AC69)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE69" s="100">
+      <c r="AE69" s="99">
         <f>IF(U70&gt;=94,4,IF(U70&gt;=91,3.9,IF(U70&gt;=88,3.8,IF(U70&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF69" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG69" s="101">
+      <c r="AG69" s="100">
         <v>17</v>
       </c>
       <c r="AH69" s="44" t="e">
@@ -9003,13 +9000,13 @@
     <row r="70" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="85"/>
       <c r="B70" s="83"/>
-      <c r="C70" s="166" t="s">
+      <c r="C70" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D70" s="167"/>
-      <c r="E70" s="167"/>
-      <c r="F70" s="167"/>
-      <c r="G70" s="168"/>
+      <c r="D70" s="120"/>
+      <c r="E70" s="120"/>
+      <c r="F70" s="120"/>
+      <c r="G70" s="121"/>
       <c r="H70" s="34"/>
       <c r="I70" s="56"/>
       <c r="J70" s="60"/>
@@ -9018,11 +9015,11 @@
       <c r="M70" s="80"/>
       <c r="N70" s="61"/>
       <c r="O70" s="37"/>
-      <c r="P70" s="116"/>
-      <c r="Q70" s="116"/>
-      <c r="R70" s="116"/>
-      <c r="S70" s="117"/>
-      <c r="T70" s="117"/>
+      <c r="P70" s="115"/>
+      <c r="Q70" s="115"/>
+      <c r="R70" s="115"/>
+      <c r="S70" s="116"/>
+      <c r="T70" s="116"/>
       <c r="U70" s="74">
         <f>(I69*P70)+(J69*Q70)+(K69*R70)+(L69*S70)+(M69*T70)</f>
         <v>0</v>
@@ -9036,7 +9033,7 @@
       <c r="AB70" s="70"/>
       <c r="AC70" s="75"/>
       <c r="AD70" s="71"/>
-      <c r="AE70" s="100"/>
+      <c r="AE70" s="99"/>
       <c r="AF70" s="43"/>
       <c r="AG70" s="64"/>
       <c r="AH70" s="44"/>
@@ -9051,14 +9048,14 @@
     <row r="71" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="84"/>
       <c r="B71" s="82"/>
-      <c r="C71" s="119"/>
-      <c r="D71" s="118"/>
-      <c r="E71" s="119"/>
-      <c r="F71" s="119"/>
-      <c r="G71" s="113"/>
+      <c r="C71" s="118"/>
+      <c r="D71" s="117"/>
+      <c r="E71" s="118"/>
+      <c r="F71" s="118"/>
+      <c r="G71" s="112"/>
       <c r="H71" s="34"/>
-      <c r="I71" s="35"/>
-      <c r="J71" s="36"/>
+      <c r="I71" s="56"/>
+      <c r="J71" s="60"/>
       <c r="K71" s="36"/>
       <c r="L71" s="36"/>
       <c r="M71" s="81"/>
@@ -9067,11 +9064,11 @@
         <v>0</v>
       </c>
       <c r="O71" s="37"/>
-      <c r="P71" s="114"/>
-      <c r="Q71" s="115"/>
-      <c r="R71" s="115"/>
-      <c r="S71" s="115"/>
-      <c r="T71" s="115"/>
+      <c r="P71" s="113"/>
+      <c r="Q71" s="114"/>
+      <c r="R71" s="114"/>
+      <c r="S71" s="114"/>
+      <c r="T71" s="114"/>
       <c r="U71" s="40">
         <f>ROUND(((P71*I71)+(Q71*J71)+(R71*K71)+(S71*L71)+(T71*M71)),2)</f>
         <v>0</v>
@@ -9097,14 +9094,14 @@
         <f t="shared" ref="AD71" si="45">IF(AC71&gt;=11,11,AC71)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE71" s="100">
+      <c r="AE71" s="99">
         <f>IF(U72&gt;=94,4,IF(U72&gt;=91,3.9,IF(U72&gt;=88,3.8,IF(U72&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF71" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG71" s="101">
+      <c r="AG71" s="100">
         <v>17</v>
       </c>
       <c r="AH71" s="44" t="e">
@@ -9125,13 +9122,13 @@
     <row r="72" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="85"/>
       <c r="B72" s="83"/>
-      <c r="C72" s="166" t="s">
+      <c r="C72" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D72" s="167"/>
-      <c r="E72" s="167"/>
-      <c r="F72" s="167"/>
-      <c r="G72" s="168"/>
+      <c r="D72" s="120"/>
+      <c r="E72" s="120"/>
+      <c r="F72" s="120"/>
+      <c r="G72" s="121"/>
       <c r="H72" s="34"/>
       <c r="I72" s="56"/>
       <c r="J72" s="60"/>
@@ -9140,11 +9137,11 @@
       <c r="M72" s="80"/>
       <c r="N72" s="61"/>
       <c r="O72" s="37"/>
-      <c r="P72" s="117"/>
-      <c r="Q72" s="117"/>
-      <c r="R72" s="117"/>
-      <c r="S72" s="117"/>
-      <c r="T72" s="117"/>
+      <c r="P72" s="116"/>
+      <c r="Q72" s="116"/>
+      <c r="R72" s="116"/>
+      <c r="S72" s="116"/>
+      <c r="T72" s="116"/>
       <c r="U72" s="74">
         <f>(I71*P72)+(J71*Q72)+(K71*R72)+(L71*S72)+(M71*T72)</f>
         <v>0</v>
@@ -9158,7 +9155,7 @@
       <c r="AB72" s="70"/>
       <c r="AC72" s="75"/>
       <c r="AD72" s="71"/>
-      <c r="AE72" s="100"/>
+      <c r="AE72" s="99"/>
       <c r="AF72" s="43"/>
       <c r="AG72" s="64"/>
       <c r="AH72" s="44"/>
@@ -9173,14 +9170,14 @@
     <row r="73" spans="1:41" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="84"/>
       <c r="B73" s="82"/>
-      <c r="C73" s="119"/>
-      <c r="D73" s="118"/>
-      <c r="E73" s="119"/>
-      <c r="F73" s="119"/>
-      <c r="G73" s="113"/>
+      <c r="C73" s="118"/>
+      <c r="D73" s="117"/>
+      <c r="E73" s="118"/>
+      <c r="F73" s="118"/>
+      <c r="G73" s="112"/>
       <c r="H73" s="34"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="36"/>
+      <c r="I73" s="56"/>
+      <c r="J73" s="60"/>
       <c r="K73" s="36"/>
       <c r="L73" s="36"/>
       <c r="M73" s="81"/>
@@ -9189,11 +9186,11 @@
         <v>0</v>
       </c>
       <c r="O73" s="37"/>
-      <c r="P73" s="114"/>
-      <c r="Q73" s="115"/>
-      <c r="R73" s="115"/>
-      <c r="S73" s="115"/>
-      <c r="T73" s="115"/>
+      <c r="P73" s="113"/>
+      <c r="Q73" s="114"/>
+      <c r="R73" s="114"/>
+      <c r="S73" s="114"/>
+      <c r="T73" s="114"/>
       <c r="U73" s="40">
         <f>ROUND(((P73*I73)+(Q73*J73)+(R73*K73)+(S73*L73)+(T73*M73)),3)</f>
         <v>0</v>
@@ -9219,14 +9216,14 @@
         <f t="shared" ref="AD73" si="47">IF(AC73&gt;=11,11,AC73)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE73" s="100">
+      <c r="AE73" s="99">
         <f>IF(U74&gt;=94,4,IF(U74&gt;=91,3.9,IF(U74&gt;=88,3.8,IF(U74&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF73" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG73" s="101">
+      <c r="AG73" s="100">
         <v>17</v>
       </c>
       <c r="AH73" s="44" t="e">
@@ -9253,13 +9250,13 @@
     <row r="74" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="85"/>
       <c r="B74" s="83"/>
-      <c r="C74" s="166" t="s">
+      <c r="C74" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D74" s="167"/>
-      <c r="E74" s="167"/>
-      <c r="F74" s="167"/>
-      <c r="G74" s="168"/>
+      <c r="D74" s="120"/>
+      <c r="E74" s="120"/>
+      <c r="F74" s="120"/>
+      <c r="G74" s="121"/>
       <c r="H74" s="34"/>
       <c r="I74" s="56"/>
       <c r="J74" s="60"/>
@@ -9268,11 +9265,11 @@
       <c r="M74" s="80"/>
       <c r="N74" s="61"/>
       <c r="O74" s="37"/>
-      <c r="P74" s="116"/>
-      <c r="Q74" s="117"/>
-      <c r="R74" s="117"/>
-      <c r="S74" s="117"/>
-      <c r="T74" s="117"/>
+      <c r="P74" s="115"/>
+      <c r="Q74" s="116"/>
+      <c r="R74" s="116"/>
+      <c r="S74" s="116"/>
+      <c r="T74" s="116"/>
       <c r="U74" s="74">
         <f>(I73*P74)+(J73*Q74)+(K73*R74)+(L73*S74)+(M73*T74)</f>
         <v>0</v>
@@ -9286,7 +9283,7 @@
       <c r="AB74" s="70"/>
       <c r="AC74" s="75"/>
       <c r="AD74" s="71"/>
-      <c r="AE74" s="100"/>
+      <c r="AE74" s="99"/>
       <c r="AF74" s="43"/>
       <c r="AG74" s="64"/>
       <c r="AH74" s="44"/>
@@ -9301,27 +9298,27 @@
     <row r="75" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="84"/>
       <c r="B75" s="82"/>
-      <c r="C75" s="119"/>
-      <c r="D75" s="118"/>
-      <c r="E75" s="119"/>
-      <c r="F75" s="119"/>
-      <c r="G75" s="113"/>
+      <c r="C75" s="118"/>
+      <c r="D75" s="117"/>
+      <c r="E75" s="118"/>
+      <c r="F75" s="118"/>
+      <c r="G75" s="112"/>
       <c r="H75" s="34"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="36"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="60"/>
       <c r="K75" s="36"/>
       <c r="L75" s="36"/>
       <c r="M75" s="81"/>
-      <c r="N75" s="107">
+      <c r="N75" s="106">
         <f>SUM(I75:M75)</f>
         <v>0</v>
       </c>
       <c r="O75" s="37"/>
-      <c r="P75" s="114"/>
-      <c r="Q75" s="115"/>
-      <c r="R75" s="115"/>
-      <c r="S75" s="115"/>
-      <c r="T75" s="115"/>
+      <c r="P75" s="113"/>
+      <c r="Q75" s="114"/>
+      <c r="R75" s="114"/>
+      <c r="S75" s="114"/>
+      <c r="T75" s="114"/>
       <c r="U75" s="40">
         <f>ROUND(((P75*I75)+(Q75*J75)+(R75*K75)+(S75*L75)+(T75*M75)),3)</f>
         <v>0</v>
@@ -9347,14 +9344,14 @@
         <f t="shared" ref="AD75" si="49">IF(AC75&gt;=11,11,AC75)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE75" s="100">
+      <c r="AE75" s="99">
         <f>IF(U76&gt;=94,4,IF(U76&gt;=91,3.9,IF(U76&gt;=88,3.8,IF(U76&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF75" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG75" s="101">
+      <c r="AG75" s="100">
         <v>17</v>
       </c>
       <c r="AH75" s="44" t="e">
@@ -9381,13 +9378,13 @@
     <row r="76" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="85"/>
       <c r="B76" s="83"/>
-      <c r="C76" s="166" t="s">
+      <c r="C76" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D76" s="167"/>
-      <c r="E76" s="167"/>
-      <c r="F76" s="167"/>
-      <c r="G76" s="168"/>
+      <c r="D76" s="120"/>
+      <c r="E76" s="120"/>
+      <c r="F76" s="120"/>
+      <c r="G76" s="121"/>
       <c r="H76" s="34"/>
       <c r="I76" s="56"/>
       <c r="J76" s="60"/>
@@ -9396,11 +9393,11 @@
       <c r="M76" s="80"/>
       <c r="N76" s="61"/>
       <c r="O76" s="37"/>
-      <c r="P76" s="116"/>
-      <c r="Q76" s="117"/>
-      <c r="R76" s="117"/>
-      <c r="S76" s="117"/>
-      <c r="T76" s="117"/>
+      <c r="P76" s="115"/>
+      <c r="Q76" s="116"/>
+      <c r="R76" s="116"/>
+      <c r="S76" s="116"/>
+      <c r="T76" s="116"/>
       <c r="U76" s="74">
         <f>(I75*P76)+(J75*Q76)+(K75*R76)+(L75*S76)+(M75*T76)</f>
         <v>0</v>
@@ -9414,7 +9411,7 @@
       <c r="AB76" s="70"/>
       <c r="AC76" s="75"/>
       <c r="AD76" s="71"/>
-      <c r="AE76" s="100"/>
+      <c r="AE76" s="99"/>
       <c r="AF76" s="43"/>
       <c r="AG76" s="64"/>
       <c r="AH76" s="44"/>
@@ -9429,14 +9426,14 @@
     <row r="77" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="84"/>
       <c r="B77" s="82"/>
-      <c r="C77" s="119"/>
-      <c r="D77" s="118"/>
-      <c r="E77" s="119"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="113"/>
+      <c r="C77" s="118"/>
+      <c r="D77" s="117"/>
+      <c r="E77" s="118"/>
+      <c r="F77" s="118"/>
+      <c r="G77" s="112"/>
       <c r="H77" s="34"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="36"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="60"/>
       <c r="K77" s="36"/>
       <c r="L77" s="36"/>
       <c r="M77" s="81"/>
@@ -9445,11 +9442,11 @@
         <v>0</v>
       </c>
       <c r="O77" s="37"/>
-      <c r="P77" s="115"/>
-      <c r="Q77" s="115"/>
-      <c r="R77" s="115"/>
-      <c r="S77" s="115"/>
-      <c r="T77" s="115"/>
+      <c r="P77" s="114"/>
+      <c r="Q77" s="114"/>
+      <c r="R77" s="114"/>
+      <c r="S77" s="114"/>
+      <c r="T77" s="114"/>
       <c r="U77" s="40">
         <f>ROUND(((P77*I77)+(Q77*J77)+(R77*K77)+(S77*L77)+(T77*M77)),3)</f>
         <v>0</v>
@@ -9475,14 +9472,14 @@
         <f t="shared" ref="AD77" si="51">IF(AC77&gt;=11,11,AC77)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE77" s="100">
+      <c r="AE77" s="99">
         <f>IF(U78&gt;=94,4,IF(U78&gt;=91,3.9,IF(U78&gt;=88,3.8,IF(U78&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF77" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG77" s="101">
+      <c r="AG77" s="100">
         <v>17</v>
       </c>
       <c r="AH77" s="44" t="e">
@@ -9509,13 +9506,13 @@
     <row r="78" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="85"/>
       <c r="B78" s="83"/>
-      <c r="C78" s="166" t="s">
+      <c r="C78" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D78" s="167"/>
-      <c r="E78" s="167"/>
-      <c r="F78" s="167"/>
-      <c r="G78" s="168"/>
+      <c r="D78" s="120"/>
+      <c r="E78" s="120"/>
+      <c r="F78" s="120"/>
+      <c r="G78" s="121"/>
       <c r="H78" s="34"/>
       <c r="I78" s="56"/>
       <c r="J78" s="60"/>
@@ -9524,11 +9521,11 @@
       <c r="M78" s="80"/>
       <c r="N78" s="61"/>
       <c r="O78" s="37"/>
-      <c r="P78" s="116"/>
-      <c r="Q78" s="117"/>
-      <c r="R78" s="117"/>
-      <c r="S78" s="117"/>
-      <c r="T78" s="117"/>
+      <c r="P78" s="115"/>
+      <c r="Q78" s="116"/>
+      <c r="R78" s="116"/>
+      <c r="S78" s="116"/>
+      <c r="T78" s="116"/>
       <c r="U78" s="74">
         <f>(I77*P78)+(J77*Q78)+(K77*R78)+(L77*S78)+(M77*T78)</f>
         <v>0</v>
@@ -9542,7 +9539,7 @@
       <c r="AB78" s="70"/>
       <c r="AC78" s="75"/>
       <c r="AD78" s="71"/>
-      <c r="AE78" s="100"/>
+      <c r="AE78" s="99"/>
       <c r="AF78" s="43"/>
       <c r="AG78" s="64"/>
       <c r="AH78" s="44"/>
@@ -9557,11 +9554,11 @@
     <row r="79" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="84"/>
       <c r="B79" s="82"/>
-      <c r="C79" s="119"/>
-      <c r="D79" s="118"/>
-      <c r="E79" s="119"/>
-      <c r="F79" s="119"/>
-      <c r="G79" s="113"/>
+      <c r="C79" s="118"/>
+      <c r="D79" s="117"/>
+      <c r="E79" s="118"/>
+      <c r="F79" s="118"/>
+      <c r="G79" s="112"/>
       <c r="H79" s="57"/>
       <c r="I79" s="35"/>
       <c r="J79" s="36"/>
@@ -9573,11 +9570,11 @@
         <v>0</v>
       </c>
       <c r="O79" s="37"/>
-      <c r="P79" s="114"/>
-      <c r="Q79" s="115"/>
-      <c r="R79" s="115"/>
-      <c r="S79" s="115"/>
-      <c r="T79" s="115"/>
+      <c r="P79" s="113"/>
+      <c r="Q79" s="114"/>
+      <c r="R79" s="114"/>
+      <c r="S79" s="114"/>
+      <c r="T79" s="114"/>
       <c r="U79" s="40">
         <f>ROUND(((P79*I79)+(Q79*J79)+(R79*K79)+(S79*L79)+(T79*M79)),3)</f>
         <v>0</v>
@@ -9603,14 +9600,14 @@
         <f t="shared" ref="AD79" si="53">IF(AC79&gt;=11,11,AC79)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE79" s="100">
+      <c r="AE79" s="99">
         <f>IF(U80&gt;=94,4,IF(U80&gt;=91,3.9,IF(U80&gt;=88,3.8,IF(U80&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF79" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG79" s="101">
+      <c r="AG79" s="100">
         <v>17</v>
       </c>
       <c r="AH79" s="44" t="e">
@@ -9637,13 +9634,13 @@
     <row r="80" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="85"/>
       <c r="B80" s="83"/>
-      <c r="C80" s="166" t="s">
+      <c r="C80" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D80" s="167"/>
-      <c r="E80" s="167"/>
-      <c r="F80" s="167"/>
-      <c r="G80" s="168"/>
+      <c r="D80" s="120"/>
+      <c r="E80" s="120"/>
+      <c r="F80" s="120"/>
+      <c r="G80" s="121"/>
       <c r="H80" s="34"/>
       <c r="I80" s="56"/>
       <c r="J80" s="60"/>
@@ -9652,11 +9649,11 @@
       <c r="M80" s="80"/>
       <c r="N80" s="61"/>
       <c r="O80" s="37"/>
-      <c r="P80" s="117"/>
-      <c r="Q80" s="117"/>
-      <c r="R80" s="115"/>
-      <c r="S80" s="117"/>
-      <c r="T80" s="117"/>
+      <c r="P80" s="116"/>
+      <c r="Q80" s="116"/>
+      <c r="R80" s="114"/>
+      <c r="S80" s="116"/>
+      <c r="T80" s="116"/>
       <c r="U80" s="74">
         <f>(I79*P80)+(J79*Q80)+(K79*R80)+(L79*S80)+(M79*T80)</f>
         <v>0</v>
@@ -9670,7 +9667,7 @@
       <c r="AB80" s="70"/>
       <c r="AC80" s="75"/>
       <c r="AD80" s="71"/>
-      <c r="AE80" s="100"/>
+      <c r="AE80" s="99"/>
       <c r="AF80" s="43"/>
       <c r="AG80" s="64"/>
       <c r="AH80" s="44"/>
@@ -9685,11 +9682,11 @@
     <row r="81" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="84"/>
       <c r="B81" s="82"/>
-      <c r="C81" s="119"/>
-      <c r="D81" s="118"/>
-      <c r="E81" s="119"/>
-      <c r="F81" s="119"/>
-      <c r="G81" s="113"/>
+      <c r="C81" s="118"/>
+      <c r="D81" s="117"/>
+      <c r="E81" s="118"/>
+      <c r="F81" s="118"/>
+      <c r="G81" s="112"/>
       <c r="H81" s="34"/>
       <c r="I81" s="35"/>
       <c r="J81" s="36"/>
@@ -9701,11 +9698,11 @@
         <v>0</v>
       </c>
       <c r="O81" s="37"/>
-      <c r="P81" s="114"/>
-      <c r="Q81" s="115"/>
-      <c r="R81" s="115"/>
-      <c r="S81" s="115"/>
-      <c r="T81" s="115"/>
+      <c r="P81" s="113"/>
+      <c r="Q81" s="114"/>
+      <c r="R81" s="114"/>
+      <c r="S81" s="114"/>
+      <c r="T81" s="114"/>
       <c r="U81" s="40">
         <f>ROUND(((P81*I81)+(Q81*J81)+(R81*K81)+(S81*L81)+(T81*M81)),3)</f>
         <v>0</v>
@@ -9731,14 +9728,14 @@
         <f t="shared" ref="AD81" si="54">IF(AC81&gt;=11,11,AC81)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE81" s="100">
+      <c r="AE81" s="99">
         <f>IF(U82&gt;=94,4,IF(U82&gt;=91,3.9,IF(U82&gt;=88,3.8,IF(U82&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF81" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG81" s="101">
+      <c r="AG81" s="100">
         <v>17</v>
       </c>
       <c r="AH81" s="44" t="e">
@@ -9765,13 +9762,13 @@
     <row r="82" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="85"/>
       <c r="B82" s="83"/>
-      <c r="C82" s="166" t="s">
+      <c r="C82" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D82" s="167"/>
-      <c r="E82" s="167"/>
-      <c r="F82" s="167"/>
-      <c r="G82" s="168"/>
+      <c r="D82" s="120"/>
+      <c r="E82" s="120"/>
+      <c r="F82" s="120"/>
+      <c r="G82" s="121"/>
       <c r="H82" s="34"/>
       <c r="I82" s="56"/>
       <c r="J82" s="60"/>
@@ -9780,11 +9777,11 @@
       <c r="M82" s="80"/>
       <c r="N82" s="61"/>
       <c r="O82" s="37"/>
-      <c r="P82" s="116"/>
-      <c r="Q82" s="117"/>
-      <c r="R82" s="117"/>
-      <c r="S82" s="117"/>
-      <c r="T82" s="117"/>
+      <c r="P82" s="115"/>
+      <c r="Q82" s="116"/>
+      <c r="R82" s="116"/>
+      <c r="S82" s="116"/>
+      <c r="T82" s="116"/>
       <c r="U82" s="74">
         <f>(I81*P82)+(J81*Q82)+(K81*R82)+(L81*S82)+(M81*T82)</f>
         <v>0</v>
@@ -9798,7 +9795,7 @@
       <c r="AB82" s="70"/>
       <c r="AC82" s="75"/>
       <c r="AD82" s="71"/>
-      <c r="AE82" s="100"/>
+      <c r="AE82" s="99"/>
       <c r="AF82" s="43"/>
       <c r="AG82" s="64"/>
       <c r="AH82" s="44"/>
@@ -9813,11 +9810,11 @@
     <row r="83" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="84"/>
       <c r="B83" s="82"/>
-      <c r="C83" s="119"/>
-      <c r="D83" s="118"/>
-      <c r="E83" s="119"/>
-      <c r="F83" s="119"/>
-      <c r="G83" s="113"/>
+      <c r="C83" s="118"/>
+      <c r="D83" s="117"/>
+      <c r="E83" s="118"/>
+      <c r="F83" s="118"/>
+      <c r="G83" s="112"/>
       <c r="H83" s="34"/>
       <c r="I83" s="35"/>
       <c r="J83" s="36"/>
@@ -9829,11 +9826,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="37"/>
-      <c r="P83" s="114"/>
-      <c r="Q83" s="115"/>
-      <c r="R83" s="115"/>
-      <c r="S83" s="115"/>
-      <c r="T83" s="115"/>
+      <c r="P83" s="113"/>
+      <c r="Q83" s="114"/>
+      <c r="R83" s="114"/>
+      <c r="S83" s="114"/>
+      <c r="T83" s="114"/>
       <c r="U83" s="40">
         <f>ROUND(((P83*I83)+(Q83*J83)+(R83*K83)+(S83*L83)+(T83*M83)),3)</f>
         <v>0</v>
@@ -9859,14 +9856,14 @@
         <f>IF(AC83&gt;=11,11,AC83)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE83" s="100">
+      <c r="AE83" s="99">
         <f>IF(U84&gt;=94,4,IF(U84&gt;=91,3.9,IF(U84&gt;=88,3.8,IF(U84&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF83" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG83" s="101">
+      <c r="AG83" s="100">
         <v>17</v>
       </c>
       <c r="AH83" s="44" t="e">
@@ -9893,13 +9890,13 @@
     <row r="84" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="85"/>
       <c r="B84" s="82"/>
-      <c r="C84" s="166" t="s">
+      <c r="C84" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D84" s="167"/>
-      <c r="E84" s="167"/>
-      <c r="F84" s="167"/>
-      <c r="G84" s="168"/>
+      <c r="D84" s="120"/>
+      <c r="E84" s="120"/>
+      <c r="F84" s="120"/>
+      <c r="G84" s="121"/>
       <c r="H84" s="34"/>
       <c r="I84" s="56"/>
       <c r="J84" s="60"/>
@@ -9908,11 +9905,11 @@
       <c r="M84" s="80"/>
       <c r="N84" s="61"/>
       <c r="O84" s="37"/>
-      <c r="P84" s="116"/>
-      <c r="Q84" s="117"/>
-      <c r="R84" s="117"/>
-      <c r="S84" s="117"/>
-      <c r="T84" s="117"/>
+      <c r="P84" s="115"/>
+      <c r="Q84" s="116"/>
+      <c r="R84" s="116"/>
+      <c r="S84" s="116"/>
+      <c r="T84" s="116"/>
       <c r="U84" s="74">
         <f>(I83*P84)+(J83*Q84)+(K83*R84)+(L83*S84)+(M83*T84)</f>
         <v>0</v>
@@ -9926,7 +9923,7 @@
       <c r="AB84" s="70"/>
       <c r="AC84" s="75"/>
       <c r="AD84" s="71"/>
-      <c r="AE84" s="100"/>
+      <c r="AE84" s="99"/>
       <c r="AF84" s="43"/>
       <c r="AG84" s="64"/>
       <c r="AH84" s="44"/>
@@ -9941,11 +9938,11 @@
     <row r="85" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="84"/>
       <c r="B85" s="82"/>
-      <c r="C85" s="119"/>
-      <c r="D85" s="118"/>
-      <c r="E85" s="119"/>
-      <c r="F85" s="119"/>
-      <c r="G85" s="113"/>
+      <c r="C85" s="118"/>
+      <c r="D85" s="117"/>
+      <c r="E85" s="118"/>
+      <c r="F85" s="118"/>
+      <c r="G85" s="112"/>
       <c r="H85" s="57"/>
       <c r="I85" s="35"/>
       <c r="J85" s="36"/>
@@ -9957,11 +9954,11 @@
         <v>0</v>
       </c>
       <c r="O85" s="37"/>
-      <c r="P85" s="114"/>
-      <c r="Q85" s="115"/>
-      <c r="R85" s="115"/>
-      <c r="S85" s="115"/>
-      <c r="T85" s="115"/>
+      <c r="P85" s="113"/>
+      <c r="Q85" s="114"/>
+      <c r="R85" s="114"/>
+      <c r="S85" s="114"/>
+      <c r="T85" s="114"/>
       <c r="U85" s="40">
         <f>ROUND(((P85*I85)+(Q85*J85)+(R85*K85)+(S85*L85)+(T85*M85)),3)</f>
         <v>0</v>
@@ -9987,14 +9984,14 @@
         <f>IF(AC85&gt;=11,11,AC85)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE85" s="100">
+      <c r="AE85" s="99">
         <f>IF(U86&gt;=94,4,IF(U86&gt;=91,3.9,IF(U86&gt;=88,3.8,IF(U86&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF85" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG85" s="101">
+      <c r="AG85" s="100">
         <v>17</v>
       </c>
       <c r="AH85" s="44" t="e">
@@ -10015,13 +10012,13 @@
     <row r="86" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="85"/>
       <c r="B86" s="83"/>
-      <c r="C86" s="166" t="s">
+      <c r="C86" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D86" s="167"/>
-      <c r="E86" s="167"/>
-      <c r="F86" s="167"/>
-      <c r="G86" s="168"/>
+      <c r="D86" s="120"/>
+      <c r="E86" s="120"/>
+      <c r="F86" s="120"/>
+      <c r="G86" s="121"/>
       <c r="H86" s="34"/>
       <c r="I86" s="56"/>
       <c r="J86" s="60"/>
@@ -10030,11 +10027,11 @@
       <c r="M86" s="80"/>
       <c r="N86" s="61"/>
       <c r="O86" s="37"/>
-      <c r="P86" s="116"/>
-      <c r="Q86" s="115"/>
-      <c r="R86" s="115"/>
-      <c r="S86" s="117"/>
-      <c r="T86" s="117"/>
+      <c r="P86" s="115"/>
+      <c r="Q86" s="114"/>
+      <c r="R86" s="114"/>
+      <c r="S86" s="116"/>
+      <c r="T86" s="116"/>
       <c r="U86" s="74">
         <f>(I85*P86)+(J85*Q86)+(K85*R86)+(L85*S86)+(M85*T86)</f>
         <v>0</v>
@@ -10048,7 +10045,7 @@
       <c r="AB86" s="70"/>
       <c r="AC86" s="75"/>
       <c r="AD86" s="71"/>
-      <c r="AE86" s="100"/>
+      <c r="AE86" s="99"/>
       <c r="AF86" s="43"/>
       <c r="AG86" s="64"/>
       <c r="AH86" s="44"/>
@@ -10079,11 +10076,11 @@
         <v>0</v>
       </c>
       <c r="O87" s="37"/>
-      <c r="P87" s="114"/>
-      <c r="Q87" s="115"/>
-      <c r="R87" s="115"/>
-      <c r="S87" s="115"/>
-      <c r="T87" s="115"/>
+      <c r="P87" s="113"/>
+      <c r="Q87" s="114"/>
+      <c r="R87" s="114"/>
+      <c r="S87" s="114"/>
+      <c r="T87" s="114"/>
       <c r="U87" s="40">
         <f>ROUND(((P87*I87)+(Q87*J87)+(R87*K87)+(S87*L87)+(T87*M87)),3)</f>
         <v>0</v>
@@ -10109,14 +10106,14 @@
         <f t="shared" ref="AD87" si="57">IF(AC87&gt;=11,11,AC87)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE87" s="100">
+      <c r="AE87" s="99">
         <f>IF(U88&gt;=94,4,IF(U88&gt;=91,3.9,IF(U88&gt;=88,3.8,IF(U88&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF87" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG87" s="101">
+      <c r="AG87" s="100">
         <v>17</v>
       </c>
       <c r="AH87" s="44" t="e">
@@ -10143,13 +10140,13 @@
     <row r="88" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="85"/>
       <c r="B88" s="83"/>
-      <c r="C88" s="166" t="s">
+      <c r="C88" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D88" s="167"/>
-      <c r="E88" s="167"/>
-      <c r="F88" s="167"/>
-      <c r="G88" s="168"/>
+      <c r="D88" s="120"/>
+      <c r="E88" s="120"/>
+      <c r="F88" s="120"/>
+      <c r="G88" s="121"/>
       <c r="H88" s="34"/>
       <c r="I88" s="56"/>
       <c r="J88" s="60"/>
@@ -10158,11 +10155,11 @@
       <c r="M88" s="80"/>
       <c r="N88" s="61"/>
       <c r="O88" s="37"/>
-      <c r="P88" s="116"/>
-      <c r="Q88" s="117"/>
-      <c r="R88" s="117"/>
-      <c r="S88" s="117"/>
-      <c r="T88" s="117"/>
+      <c r="P88" s="115"/>
+      <c r="Q88" s="116"/>
+      <c r="R88" s="116"/>
+      <c r="S88" s="116"/>
+      <c r="T88" s="116"/>
       <c r="U88" s="74">
         <f>(I87*P88)+(J87*Q88)+(K87*R88)+(L87*S88)+(M87*T88)</f>
         <v>0</v>
@@ -10176,7 +10173,7 @@
       <c r="AB88" s="70"/>
       <c r="AC88" s="75"/>
       <c r="AD88" s="71"/>
-      <c r="AE88" s="100"/>
+      <c r="AE88" s="99"/>
       <c r="AF88" s="43"/>
       <c r="AG88" s="64"/>
       <c r="AH88" s="44"/>
@@ -10207,11 +10204,11 @@
         <v>0</v>
       </c>
       <c r="O89" s="37"/>
-      <c r="P89" s="114"/>
-      <c r="Q89" s="115"/>
-      <c r="R89" s="115"/>
-      <c r="S89" s="115"/>
-      <c r="T89" s="115"/>
+      <c r="P89" s="113"/>
+      <c r="Q89" s="114"/>
+      <c r="R89" s="114"/>
+      <c r="S89" s="114"/>
+      <c r="T89" s="114"/>
       <c r="U89" s="40">
         <f>ROUND(((P89*I89)+(Q89*J89)+(R89*K89)+(S89*L89)+(T89*M89)),3)</f>
         <v>0</v>
@@ -10237,14 +10234,14 @@
         <f>IF(AC89&gt;=11,11,AC89)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE89" s="100">
+      <c r="AE89" s="99">
         <f>IF(U90&gt;=94,4,IF(U90&gt;=91,3.9,IF(U90&gt;=88,3.8,IF(U90&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF89" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG89" s="101">
+      <c r="AG89" s="100">
         <v>17</v>
       </c>
       <c r="AH89" s="44" t="e">
@@ -10271,13 +10268,13 @@
     <row r="90" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="58"/>
       <c r="B90" s="63"/>
-      <c r="C90" s="166" t="s">
+      <c r="C90" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D90" s="167"/>
-      <c r="E90" s="167"/>
-      <c r="F90" s="167"/>
-      <c r="G90" s="168"/>
+      <c r="D90" s="120"/>
+      <c r="E90" s="120"/>
+      <c r="F90" s="120"/>
+      <c r="G90" s="121"/>
       <c r="H90" s="34"/>
       <c r="I90" s="56"/>
       <c r="J90" s="60"/>
@@ -10286,11 +10283,11 @@
       <c r="M90" s="80"/>
       <c r="N90" s="61"/>
       <c r="O90" s="37"/>
-      <c r="P90" s="116"/>
-      <c r="Q90" s="117"/>
-      <c r="R90" s="117"/>
-      <c r="S90" s="117"/>
-      <c r="T90" s="117"/>
+      <c r="P90" s="115"/>
+      <c r="Q90" s="116"/>
+      <c r="R90" s="116"/>
+      <c r="S90" s="116"/>
+      <c r="T90" s="116"/>
       <c r="U90" s="74">
         <f>(I89*P90)+(J89*Q90)+(K89*R90)+(L89*S90)+(M89*T90)</f>
         <v>0</v>
@@ -10304,7 +10301,7 @@
       <c r="AB90" s="70"/>
       <c r="AC90" s="75"/>
       <c r="AD90" s="71"/>
-      <c r="AE90" s="100"/>
+      <c r="AE90" s="99"/>
       <c r="AF90" s="43"/>
       <c r="AG90" s="64"/>
       <c r="AH90" s="44"/>
@@ -10318,14 +10315,53 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="U3:AH3"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C36:G36"/>
     <mergeCell ref="C42:G42"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C86:G86"/>
@@ -10342,53 +10378,14 @@
     <mergeCell ref="C64:G64"/>
     <mergeCell ref="C66:G66"/>
     <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="U3:AH3"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:T3"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C84:G84"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/템플릿/LH간이종심100-300억_템플릿.xlsx
+++ b/템플릿/LH간이종심100-300억_템플릿.xlsx
@@ -4021,6 +4021,165 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="16" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="6" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4073,165 +4232,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="4" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="16" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="6" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4599,22 +4599,22 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="115"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="168"/>
       <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="116"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="118"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="171"/>
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="116">
-        <v>0</v>
-      </c>
-      <c r="M1" s="117"/>
-      <c r="N1" s="119"/>
+      <c r="L1" s="169">
+        <v>0</v>
+      </c>
+      <c r="M1" s="170"/>
+      <c r="N1" s="172"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
@@ -4625,21 +4625,21 @@
       <c r="V1" s="6"/>
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
-      <c r="Y1" s="109" t="s">
+      <c r="Y1" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="109"/>
+      <c r="Z1" s="162"/>
       <c r="AA1" s="7"/>
-      <c r="AB1" s="109" t="s">
+      <c r="AB1" s="162" t="s">
         <v>7</v>
       </c>
-      <c r="AC1" s="109"/>
-      <c r="AD1" s="110" t="s">
+      <c r="AC1" s="162"/>
+      <c r="AD1" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="112"/>
-      <c r="AG1" s="160"/>
+      <c r="AE1" s="164"/>
+      <c r="AF1" s="165"/>
+      <c r="AG1" s="109"/>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
@@ -4650,69 +4650,69 @@
       <c r="AO1" s="8"/>
     </row>
     <row r="2" spans="1:41" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="147"/>
       <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="137"/>
-      <c r="F2" s="138"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="149"/>
       <c r="G2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="137">
+      <c r="H2" s="148">
         <f>E2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="139"/>
-      <c r="J2" s="138"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="149"/>
       <c r="K2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="140">
+      <c r="L2" s="151">
         <f>H2*3</f>
         <v>0</v>
       </c>
-      <c r="M2" s="141"/>
+      <c r="M2" s="152"/>
       <c r="N2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="167" t="s">
+      <c r="O2" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="P2" s="172" t="s">
+      <c r="P2" s="153" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="172"/>
-      <c r="R2" s="172"/>
-      <c r="S2" s="172"/>
+      <c r="Q2" s="153"/>
+      <c r="R2" s="153"/>
+      <c r="S2" s="153"/>
       <c r="T2" s="74" t="s">
         <v>49</v>
       </c>
       <c r="U2" s="13"/>
       <c r="V2" s="14"/>
-      <c r="W2" s="113" t="s">
-        <v>0</v>
-      </c>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
+      <c r="W2" s="166" t="s">
+        <v>0</v>
+      </c>
+      <c r="X2" s="166"/>
+      <c r="Y2" s="173"/>
+      <c r="Z2" s="174"/>
       <c r="AA2" s="73"/>
-      <c r="AB2" s="122">
+      <c r="AB2" s="175">
         <f>H1</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="123"/>
-      <c r="AD2" s="124" t="e">
+      <c r="AC2" s="176"/>
+      <c r="AD2" s="177" t="e">
         <f>Y2/AB2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE2" s="125"/>
-      <c r="AF2" s="126"/>
-      <c r="AG2" s="161"/>
+      <c r="AE2" s="178"/>
+      <c r="AF2" s="179"/>
+      <c r="AG2" s="110"/>
       <c r="AI2" s="15"/>
       <c r="AJ2" s="16"/>
       <c r="AK2" s="16"/>
@@ -4723,77 +4723,77 @@
       </c>
     </row>
     <row r="3" spans="1:41" s="21" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="154" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="131" t="s">
+      <c r="C3" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="132" t="s">
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="133"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="168" t="s">
+      <c r="J3" s="141"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="131" t="s">
+      <c r="O3" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="131"/>
-      <c r="R3" s="131"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="156" t="s">
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
+      <c r="S3" s="143"/>
+      <c r="T3" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="133"/>
-      <c r="V3" s="133"/>
-      <c r="W3" s="133"/>
-      <c r="X3" s="133"/>
-      <c r="Y3" s="133"/>
-      <c r="Z3" s="133"/>
-      <c r="AA3" s="133"/>
-      <c r="AB3" s="133"/>
-      <c r="AC3" s="133"/>
-      <c r="AD3" s="133"/>
-      <c r="AE3" s="133"/>
-      <c r="AF3" s="133"/>
-      <c r="AG3" s="131"/>
-      <c r="AH3" s="159"/>
+      <c r="U3" s="141"/>
+      <c r="V3" s="141"/>
+      <c r="W3" s="141"/>
+      <c r="X3" s="141"/>
+      <c r="Y3" s="141"/>
+      <c r="Z3" s="141"/>
+      <c r="AA3" s="141"/>
+      <c r="AB3" s="141"/>
+      <c r="AC3" s="141"/>
+      <c r="AD3" s="141"/>
+      <c r="AE3" s="141"/>
+      <c r="AF3" s="141"/>
+      <c r="AG3" s="142"/>
+      <c r="AH3" s="143"/>
       <c r="AI3" s="25"/>
-      <c r="AJ3" s="157" t="s">
+      <c r="AJ3" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="AK3" s="145" t="s">
+      <c r="AK3" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="AL3" s="147" t="s">
+      <c r="AL3" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="AM3" s="149" t="s">
+      <c r="AM3" s="136" t="s">
         <v>25</v>
       </c>
       <c r="AN3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="AO3" s="151" t="s">
+      <c r="AO3" s="138" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:41" s="21" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="128"/>
-      <c r="B4" s="130"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="157"/>
       <c r="C4" s="22" t="s">
         <v>28</v>
       </c>
@@ -4827,7 +4827,7 @@
       <c r="M4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="169"/>
+      <c r="N4" s="161"/>
       <c r="O4" s="108" t="s">
         <v>35</v>
       </c>
@@ -4879,24 +4879,24 @@
       <c r="AE4" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="AF4" s="162" t="s">
+      <c r="AF4" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="AG4" s="165" t="s">
+      <c r="AG4" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="AH4" s="164" t="s">
+      <c r="AH4" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="AI4" s="163" t="s">
+      <c r="AI4" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="AJ4" s="158"/>
-      <c r="AK4" s="146"/>
-      <c r="AL4" s="148"/>
-      <c r="AM4" s="150"/>
+      <c r="AJ4" s="145"/>
+      <c r="AK4" s="133"/>
+      <c r="AL4" s="135"/>
+      <c r="AM4" s="137"/>
       <c r="AN4" s="30"/>
-      <c r="AO4" s="152"/>
+      <c r="AO4" s="139"/>
     </row>
     <row r="5" spans="1:41" s="21" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="79"/>
@@ -4912,7 +4912,7 @@
       <c r="K5" s="35"/>
       <c r="L5" s="35"/>
       <c r="M5" s="76"/>
-      <c r="N5" s="170">
+      <c r="N5" s="117">
         <f>SUM(I5:M5)</f>
         <v>0</v>
       </c>
@@ -4950,22 +4950,20 @@
         <f>T6</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF5" s="173">
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="119">
         <f>10+4+ROUND(1*I5+1*J5+1*K5+1*L5+1*M5,3)+ROUND(2*I5+2*J5+2*K5+2*L5+2*M5,3)</f>
         <v>14</v>
       </c>
-      <c r="AG5" s="166" t="e">
+      <c r="AG5" s="115" t="e">
         <f>U5+AC5+AD5+AF5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH5" s="175" t="e">
+      <c r="AH5" s="121" t="e">
         <f>AG5+AE5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI5" s="176" t="e">
+      <c r="AI5" s="122" t="e">
         <f>IF(AH5&gt;=40,40,AH5)</f>
         <v>#DIV/0!</v>
       </c>
@@ -4985,20 +4983,20 @@
     <row r="6" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="80"/>
       <c r="B6" s="100"/>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
-      <c r="F6" s="154"/>
-      <c r="G6" s="155"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="128"/>
       <c r="H6" s="33"/>
       <c r="I6" s="53"/>
       <c r="J6" s="57"/>
       <c r="K6" s="57"/>
       <c r="L6" s="57"/>
       <c r="M6" s="75"/>
-      <c r="N6" s="171"/>
+      <c r="N6" s="118"/>
       <c r="O6" s="104"/>
       <c r="P6" s="105"/>
       <c r="Q6" s="105"/>
@@ -5019,10 +5017,10 @@
       <c r="AC6" s="66"/>
       <c r="AD6" s="91"/>
       <c r="AE6" s="41"/>
-      <c r="AF6" s="177"/>
-      <c r="AG6" s="178"/>
-      <c r="AH6" s="175"/>
-      <c r="AI6" s="176"/>
+      <c r="AF6" s="123"/>
+      <c r="AG6" s="124"/>
+      <c r="AH6" s="121"/>
+      <c r="AI6" s="122"/>
       <c r="AJ6" s="42"/>
       <c r="AK6" s="43"/>
       <c r="AL6" s="44"/>
@@ -5044,7 +5042,7 @@
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
       <c r="M7" s="76"/>
-      <c r="N7" s="171">
+      <c r="N7" s="118">
         <f>SUM(I7:M7)</f>
         <v>0</v>
       </c>
@@ -5082,22 +5080,20 @@
         <f>T8</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="41">
-        <v>0.1</v>
-      </c>
-      <c r="AF7" s="174">
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="120">
         <f>10+4+ROUND(1*I7+1*J7+1*K7+1*L7+1*M7,3)+ROUND(2*I7+2*J7+2*K7+2*L7+2*M7,3)</f>
         <v>14</v>
       </c>
-      <c r="AG7" s="166" t="e">
+      <c r="AG7" s="115" t="e">
         <f>U7+AC7+AD7+AF7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH7" s="175" t="e">
+      <c r="AH7" s="121" t="e">
         <f>AG7+AE7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI7" s="176" t="e">
+      <c r="AI7" s="122" t="e">
         <f>IF(AH7&gt;=40,40,AH7)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5117,20 +5113,20 @@
     <row r="8" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="80"/>
       <c r="B8" s="99"/>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="155"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="128"/>
       <c r="H8" s="33"/>
       <c r="I8" s="53"/>
       <c r="J8" s="57"/>
       <c r="K8" s="57"/>
       <c r="L8" s="57"/>
       <c r="M8" s="75"/>
-      <c r="N8" s="171"/>
+      <c r="N8" s="118"/>
       <c r="O8" s="104"/>
       <c r="P8" s="105"/>
       <c r="Q8" s="105"/>
@@ -5151,10 +5147,10 @@
       <c r="AC8" s="66"/>
       <c r="AD8" s="91"/>
       <c r="AE8" s="41"/>
-      <c r="AF8" s="179"/>
-      <c r="AG8" s="178"/>
-      <c r="AH8" s="175"/>
-      <c r="AI8" s="176"/>
+      <c r="AF8" s="125"/>
+      <c r="AG8" s="124"/>
+      <c r="AH8" s="121"/>
+      <c r="AI8" s="122"/>
       <c r="AJ8" s="42"/>
       <c r="AK8" s="43"/>
       <c r="AL8" s="44"/>
@@ -5176,7 +5172,7 @@
       <c r="K9" s="57"/>
       <c r="L9" s="35"/>
       <c r="M9" s="76"/>
-      <c r="N9" s="171">
+      <c r="N9" s="118">
         <f>SUM(I9:M9)</f>
         <v>0</v>
       </c>
@@ -5214,22 +5210,20 @@
         <f>T10</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF9" s="174">
+      <c r="AE9" s="41"/>
+      <c r="AF9" s="120">
         <f>10+4+ROUND(1*I9+1*J9+1*K9+1*L9+1*M9,3)+ROUND(2*I9+2*J9+2*K9+2*L9+2*M9,3)</f>
         <v>14</v>
       </c>
-      <c r="AG9" s="166" t="e">
+      <c r="AG9" s="115" t="e">
         <f>U9+AC9+AD9+AF9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH9" s="175" t="e">
+      <c r="AH9" s="121" t="e">
         <f>AG9+AE9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI9" s="176" t="e">
+      <c r="AI9" s="122" t="e">
         <f>IF(AH9&gt;=40,40,AH9)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5249,20 +5243,20 @@
     <row r="10" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="80"/>
       <c r="B10" s="100"/>
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="155"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="128"/>
       <c r="H10" s="33"/>
       <c r="I10" s="53"/>
       <c r="J10" s="57"/>
       <c r="K10" s="57"/>
       <c r="L10" s="57"/>
       <c r="M10" s="75"/>
-      <c r="N10" s="171"/>
+      <c r="N10" s="118"/>
       <c r="O10" s="104"/>
       <c r="P10" s="105"/>
       <c r="Q10" s="105"/>
@@ -5283,10 +5277,10 @@
       <c r="AC10" s="66"/>
       <c r="AD10" s="91"/>
       <c r="AE10" s="41"/>
-      <c r="AF10" s="179"/>
-      <c r="AG10" s="178"/>
-      <c r="AH10" s="175"/>
-      <c r="AI10" s="176"/>
+      <c r="AF10" s="125"/>
+      <c r="AG10" s="124"/>
+      <c r="AH10" s="121"/>
+      <c r="AI10" s="122"/>
       <c r="AJ10" s="42"/>
       <c r="AK10" s="43"/>
       <c r="AL10" s="44"/>
@@ -5308,7 +5302,7 @@
       <c r="K11" s="35"/>
       <c r="L11" s="35"/>
       <c r="M11" s="76"/>
-      <c r="N11" s="171">
+      <c r="N11" s="118">
         <f>SUM(I11:M11)</f>
         <v>0</v>
       </c>
@@ -5346,22 +5340,20 @@
         <f>T12</f>
         <v>0</v>
       </c>
-      <c r="AE11" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF11" s="174">
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="120">
         <f>10+4+ROUND(1*I11+1*J11+1*K11+1*L11+1*M11,3)+ROUND(2*I11+2*J11+2*K11+2*L11+2*M11,3)</f>
         <v>14</v>
       </c>
-      <c r="AG11" s="166" t="e">
+      <c r="AG11" s="115" t="e">
         <f>U11+AC11+AD11+AF11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH11" s="175" t="e">
+      <c r="AH11" s="121" t="e">
         <f>AG11+AE11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI11" s="176" t="e">
+      <c r="AI11" s="122" t="e">
         <f>IF(AH11&gt;=40,40,AH11)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5381,20 +5373,20 @@
     <row r="12" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="80"/>
       <c r="B12" s="100"/>
-      <c r="C12" s="153" t="s">
+      <c r="C12" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="154"/>
-      <c r="E12" s="154"/>
-      <c r="F12" s="154"/>
-      <c r="G12" s="155"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="128"/>
       <c r="H12" s="33"/>
       <c r="I12" s="53"/>
       <c r="J12" s="57"/>
       <c r="K12" s="57"/>
       <c r="L12" s="57"/>
       <c r="M12" s="75"/>
-      <c r="N12" s="171"/>
+      <c r="N12" s="118"/>
       <c r="O12" s="104"/>
       <c r="P12" s="105"/>
       <c r="Q12" s="105"/>
@@ -5415,10 +5407,10 @@
       <c r="AC12" s="66"/>
       <c r="AD12" s="91"/>
       <c r="AE12" s="41"/>
-      <c r="AF12" s="179"/>
-      <c r="AG12" s="178"/>
-      <c r="AH12" s="175"/>
-      <c r="AI12" s="176"/>
+      <c r="AF12" s="125"/>
+      <c r="AG12" s="124"/>
+      <c r="AH12" s="121"/>
+      <c r="AI12" s="122"/>
       <c r="AJ12" s="42"/>
       <c r="AK12" s="43"/>
       <c r="AL12" s="44"/>
@@ -5440,7 +5432,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
       <c r="M13" s="76"/>
-      <c r="N13" s="171">
+      <c r="N13" s="118">
         <f>SUM(I13:M13)</f>
         <v>0</v>
       </c>
@@ -5478,22 +5470,20 @@
         <f>T14</f>
         <v>0</v>
       </c>
-      <c r="AE13" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="AF13" s="174">
+      <c r="AE13" s="41"/>
+      <c r="AF13" s="120">
         <f>10+4+ROUND(1*I13+1*J13+1*K13+1*L13+1*M13,3)+ROUND(2*I13+2*J13+2*K13+2*L13+2*M13,3)</f>
         <v>14</v>
       </c>
-      <c r="AG13" s="166" t="e">
+      <c r="AG13" s="115" t="e">
         <f>U13+AC13+AD13+AF13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH13" s="175" t="e">
+      <c r="AH13" s="121" t="e">
         <f>AG13+AE13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI13" s="176" t="e">
+      <c r="AI13" s="122" t="e">
         <f>IF(AH13&gt;=40,40,AH13)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5513,20 +5503,20 @@
     <row r="14" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="80"/>
       <c r="B14" s="78"/>
-      <c r="C14" s="153" t="s">
+      <c r="C14" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="154"/>
-      <c r="G14" s="155"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="128"/>
       <c r="H14" s="33"/>
       <c r="I14" s="53"/>
       <c r="J14" s="57"/>
       <c r="K14" s="57"/>
       <c r="L14" s="57"/>
       <c r="M14" s="75"/>
-      <c r="N14" s="171"/>
+      <c r="N14" s="118"/>
       <c r="O14" s="103"/>
       <c r="P14" s="103"/>
       <c r="Q14" s="103"/>
@@ -5547,10 +5537,10 @@
       <c r="AC14" s="66"/>
       <c r="AD14" s="91"/>
       <c r="AE14" s="41"/>
-      <c r="AF14" s="179"/>
-      <c r="AG14" s="178"/>
-      <c r="AH14" s="175"/>
-      <c r="AI14" s="176"/>
+      <c r="AF14" s="125"/>
+      <c r="AG14" s="124"/>
+      <c r="AH14" s="121"/>
+      <c r="AI14" s="122"/>
       <c r="AJ14" s="42"/>
       <c r="AK14" s="43"/>
       <c r="AL14" s="44"/>
@@ -5572,7 +5562,7 @@
       <c r="K15" s="35"/>
       <c r="L15" s="35"/>
       <c r="M15" s="76"/>
-      <c r="N15" s="171">
+      <c r="N15" s="118">
         <f>SUM(I15:M15)</f>
         <v>0</v>
       </c>
@@ -5610,22 +5600,20 @@
         <f>T16</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF15" s="174">
+      <c r="AE15" s="41"/>
+      <c r="AF15" s="120">
         <f>10+4+ROUND(1*I15+1*J15+1*K15+1*L15+1*M15,3)+ROUND(2*I15+2*J15+2*K15+2*L15+2*M15,3)</f>
         <v>14</v>
       </c>
-      <c r="AG15" s="166" t="e">
+      <c r="AG15" s="115" t="e">
         <f>U15+AC15+AD15+AF15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH15" s="175" t="e">
+      <c r="AH15" s="121" t="e">
         <f>AG15+AE15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI15" s="176" t="e">
+      <c r="AI15" s="122" t="e">
         <f>IF(AH15&gt;=40,40,AH15)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5645,20 +5633,20 @@
     <row r="16" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="80"/>
       <c r="B16" s="78"/>
-      <c r="C16" s="153" t="s">
+      <c r="C16" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
-      <c r="F16" s="154"/>
-      <c r="G16" s="155"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="128"/>
       <c r="H16" s="33"/>
       <c r="I16" s="53"/>
       <c r="J16" s="57"/>
       <c r="K16" s="57"/>
       <c r="L16" s="57"/>
       <c r="M16" s="75"/>
-      <c r="N16" s="171"/>
+      <c r="N16" s="118"/>
       <c r="O16" s="104"/>
       <c r="P16" s="105"/>
       <c r="Q16" s="105"/>
@@ -5679,10 +5667,10 @@
       <c r="AC16" s="66"/>
       <c r="AD16" s="91"/>
       <c r="AE16" s="41"/>
-      <c r="AF16" s="179"/>
-      <c r="AG16" s="178"/>
-      <c r="AH16" s="175"/>
-      <c r="AI16" s="176"/>
+      <c r="AF16" s="125"/>
+      <c r="AG16" s="124"/>
+      <c r="AH16" s="121"/>
+      <c r="AI16" s="122"/>
       <c r="AJ16" s="42"/>
       <c r="AK16" s="43"/>
       <c r="AL16" s="44"/>
@@ -5704,7 +5692,7 @@
       <c r="K17" s="35"/>
       <c r="L17" s="35"/>
       <c r="M17" s="76"/>
-      <c r="N17" s="171">
+      <c r="N17" s="118">
         <f>SUM(I17:M17)</f>
         <v>0</v>
       </c>
@@ -5742,22 +5730,20 @@
         <f>T18</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF17" s="174">
+      <c r="AE17" s="41"/>
+      <c r="AF17" s="120">
         <f>10+4+ROUND(1*I17+1*J17+1*K17+1*L17+1*M17,3)+ROUND(2*I17+2*J17+2*K17+2*L17+2*M17,3)</f>
         <v>14</v>
       </c>
-      <c r="AG17" s="166" t="e">
+      <c r="AG17" s="115" t="e">
         <f>U17+AC17+AD17+AF17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH17" s="175" t="e">
+      <c r="AH17" s="121" t="e">
         <f>AG17+AE17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI17" s="176" t="e">
+      <c r="AI17" s="122" t="e">
         <f>IF(AH17&gt;=40,40,AH17)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5777,20 +5763,20 @@
     <row r="18" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="80"/>
       <c r="B18" s="78"/>
-      <c r="C18" s="153" t="s">
+      <c r="C18" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="154"/>
-      <c r="G18" s="155"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="128"/>
       <c r="H18" s="33"/>
       <c r="I18" s="53"/>
       <c r="J18" s="57"/>
       <c r="K18" s="57"/>
       <c r="L18" s="57"/>
       <c r="M18" s="75"/>
-      <c r="N18" s="171"/>
+      <c r="N18" s="118"/>
       <c r="O18" s="103"/>
       <c r="P18" s="103"/>
       <c r="Q18" s="104"/>
@@ -5811,10 +5797,10 @@
       <c r="AC18" s="66"/>
       <c r="AD18" s="91"/>
       <c r="AE18" s="41"/>
-      <c r="AF18" s="179"/>
-      <c r="AG18" s="178"/>
-      <c r="AH18" s="175"/>
-      <c r="AI18" s="176"/>
+      <c r="AF18" s="125"/>
+      <c r="AG18" s="124"/>
+      <c r="AH18" s="121"/>
+      <c r="AI18" s="122"/>
       <c r="AJ18" s="42"/>
       <c r="AK18" s="43"/>
       <c r="AL18" s="44"/>
@@ -5836,7 +5822,7 @@
       <c r="K19" s="35"/>
       <c r="L19" s="35"/>
       <c r="M19" s="76"/>
-      <c r="N19" s="171">
+      <c r="N19" s="118">
         <f>SUM(I19:M19)</f>
         <v>0</v>
       </c>
@@ -5874,22 +5860,20 @@
         <f>T20</f>
         <v>0</v>
       </c>
-      <c r="AE19" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF19" s="174">
+      <c r="AE19" s="41"/>
+      <c r="AF19" s="120">
         <f>10+4+ROUND(1*I19+1*J19+1*K19+1*L19+1*M19,3)+ROUND(2*I19+2*J19+2*K19+2*L19+2*M19,3)</f>
         <v>14</v>
       </c>
-      <c r="AG19" s="166" t="e">
+      <c r="AG19" s="115" t="e">
         <f>U19+AC19+AD19+AF19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH19" s="175" t="e">
+      <c r="AH19" s="121" t="e">
         <f>AG19+AE19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI19" s="176" t="e">
+      <c r="AI19" s="122" t="e">
         <f>IF(AH19&gt;=40,40,AH19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -5909,20 +5893,20 @@
     <row r="20" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="80"/>
       <c r="B20" s="78"/>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="143"/>
-      <c r="E20" s="143"/>
-      <c r="F20" s="143"/>
-      <c r="G20" s="144"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="131"/>
       <c r="H20" s="33"/>
       <c r="I20" s="53"/>
       <c r="J20" s="57"/>
       <c r="K20" s="57"/>
       <c r="L20" s="57"/>
       <c r="M20" s="75"/>
-      <c r="N20" s="171"/>
+      <c r="N20" s="118"/>
       <c r="O20" s="58"/>
       <c r="P20" s="58"/>
       <c r="Q20" s="58"/>
@@ -5943,10 +5927,10 @@
       <c r="AC20" s="66"/>
       <c r="AD20" s="91"/>
       <c r="AE20" s="41"/>
-      <c r="AF20" s="179"/>
-      <c r="AG20" s="178"/>
-      <c r="AH20" s="175"/>
-      <c r="AI20" s="176"/>
+      <c r="AF20" s="125"/>
+      <c r="AG20" s="124"/>
+      <c r="AH20" s="121"/>
+      <c r="AI20" s="122"/>
       <c r="AJ20" s="42"/>
       <c r="AK20" s="43"/>
       <c r="AL20" s="44"/>
@@ -5968,7 +5952,7 @@
       <c r="K21" s="81"/>
       <c r="L21" s="81"/>
       <c r="M21" s="94"/>
-      <c r="N21" s="171">
+      <c r="N21" s="118">
         <f>SUM(I21:M21)</f>
         <v>0</v>
       </c>
@@ -6006,22 +5990,20 @@
         <f>T22</f>
         <v>0</v>
       </c>
-      <c r="AE21" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF21" s="174">
+      <c r="AE21" s="41"/>
+      <c r="AF21" s="120">
         <f>10+4+ROUND(1*I21+1*J21+1*K21+1*L21+1*M21,3)+ROUND(2*I21+2*J21+2*K21+2*L21+2*M21,3)</f>
         <v>14</v>
       </c>
-      <c r="AG21" s="166" t="e">
+      <c r="AG21" s="115" t="e">
         <f>U21+AC21+AD21+AF21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH21" s="175" t="e">
+      <c r="AH21" s="121" t="e">
         <f>AG21+AE21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI21" s="176" t="e">
+      <c r="AI21" s="122" t="e">
         <f>IF(AH21&gt;=40,40,AH21)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6035,20 +6017,20 @@
     <row r="22" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="80"/>
       <c r="B22" s="78"/>
-      <c r="C22" s="142" t="s">
+      <c r="C22" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="143"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="144"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="131"/>
       <c r="H22" s="82"/>
       <c r="I22" s="83"/>
       <c r="J22" s="84"/>
       <c r="K22" s="84"/>
       <c r="L22" s="84"/>
       <c r="M22" s="95"/>
-      <c r="N22" s="171"/>
+      <c r="N22" s="118"/>
       <c r="O22" s="38"/>
       <c r="P22" s="38"/>
       <c r="Q22" s="38"/>
@@ -6069,10 +6051,10 @@
       <c r="AC22" s="66"/>
       <c r="AD22" s="91"/>
       <c r="AE22" s="41"/>
-      <c r="AF22" s="179"/>
-      <c r="AG22" s="178"/>
-      <c r="AH22" s="175"/>
-      <c r="AI22" s="176"/>
+      <c r="AF22" s="125"/>
+      <c r="AG22" s="124"/>
+      <c r="AH22" s="121"/>
+      <c r="AI22" s="122"/>
       <c r="AJ22" s="42"/>
       <c r="AK22" s="43"/>
       <c r="AL22" s="44"/>
@@ -6094,7 +6076,7 @@
       <c r="K23" s="35"/>
       <c r="L23" s="35"/>
       <c r="M23" s="76"/>
-      <c r="N23" s="171">
+      <c r="N23" s="118">
         <f>SUM(I23:M23)</f>
         <v>0</v>
       </c>
@@ -6132,22 +6114,20 @@
         <f>T24</f>
         <v>0</v>
       </c>
-      <c r="AE23" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF23" s="174">
+      <c r="AE23" s="41"/>
+      <c r="AF23" s="120">
         <f>10+4+ROUND(1*I23+1*J23+1*K23+1*L23+1*M23,3)+ROUND(2*I23+2*J23+2*K23+2*L23+2*M23,3)</f>
         <v>14</v>
       </c>
-      <c r="AG23" s="166" t="e">
+      <c r="AG23" s="115" t="e">
         <f>U23+AC23+AD23+AF23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH23" s="175" t="e">
+      <c r="AH23" s="121" t="e">
         <f>AG23+AE23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI23" s="176" t="e">
+      <c r="AI23" s="122" t="e">
         <f>IF(AH23&gt;=40,40,AH23)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6161,20 +6141,20 @@
     <row r="24" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="80"/>
       <c r="B24" s="78"/>
-      <c r="C24" s="142" t="s">
+      <c r="C24" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="143"/>
-      <c r="E24" s="143"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="144"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="131"/>
       <c r="H24" s="33"/>
       <c r="I24" s="53"/>
       <c r="J24" s="57"/>
       <c r="K24" s="57"/>
       <c r="L24" s="57"/>
       <c r="M24" s="75"/>
-      <c r="N24" s="171"/>
+      <c r="N24" s="118"/>
       <c r="O24" s="58"/>
       <c r="P24" s="38"/>
       <c r="Q24" s="37"/>
@@ -6195,10 +6175,10 @@
       <c r="AC24" s="66"/>
       <c r="AD24" s="91"/>
       <c r="AE24" s="41"/>
-      <c r="AF24" s="179"/>
-      <c r="AG24" s="178"/>
-      <c r="AH24" s="175"/>
-      <c r="AI24" s="176"/>
+      <c r="AF24" s="125"/>
+      <c r="AG24" s="124"/>
+      <c r="AH24" s="121"/>
+      <c r="AI24" s="122"/>
       <c r="AJ24" s="42"/>
       <c r="AK24" s="43"/>
       <c r="AL24" s="44"/>
@@ -6220,7 +6200,7 @@
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
       <c r="M25" s="76"/>
-      <c r="N25" s="171">
+      <c r="N25" s="118">
         <f>SUM(I25:M25)</f>
         <v>0</v>
       </c>
@@ -6258,22 +6238,20 @@
         <f>T26</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF25" s="174">
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="120">
         <f>10+4+ROUND(1*I25+1*J25+1*K25+1*L25+1*M25,3)+ROUND(2*I25+2*J25+2*K25+2*L25+2*M25,3)</f>
         <v>14</v>
       </c>
-      <c r="AG25" s="166" t="e">
+      <c r="AG25" s="115" t="e">
         <f>U25+AC25+AD25+AF25</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH25" s="175" t="e">
+      <c r="AH25" s="121" t="e">
         <f>AG25+AE25</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI25" s="176" t="e">
+      <c r="AI25" s="122" t="e">
         <f>IF(AH25&gt;=40,40,AH25)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6287,20 +6265,20 @@
     <row r="26" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="80"/>
       <c r="B26" s="78"/>
-      <c r="C26" s="142" t="s">
+      <c r="C26" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="143"/>
-      <c r="E26" s="143"/>
-      <c r="F26" s="143"/>
-      <c r="G26" s="144"/>
+      <c r="D26" s="130"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="130"/>
+      <c r="G26" s="131"/>
       <c r="H26" s="33"/>
       <c r="I26" s="53"/>
       <c r="J26" s="57"/>
       <c r="K26" s="57"/>
       <c r="L26" s="57"/>
       <c r="M26" s="75"/>
-      <c r="N26" s="171"/>
+      <c r="N26" s="118"/>
       <c r="O26" s="37"/>
       <c r="P26" s="37"/>
       <c r="Q26" s="37"/>
@@ -6321,10 +6299,10 @@
       <c r="AC26" s="66"/>
       <c r="AD26" s="91"/>
       <c r="AE26" s="41"/>
-      <c r="AF26" s="179"/>
-      <c r="AG26" s="178"/>
-      <c r="AH26" s="175"/>
-      <c r="AI26" s="176"/>
+      <c r="AF26" s="125"/>
+      <c r="AG26" s="124"/>
+      <c r="AH26" s="121"/>
+      <c r="AI26" s="122"/>
       <c r="AJ26" s="42"/>
       <c r="AK26" s="43"/>
       <c r="AL26" s="44"/>
@@ -6346,7 +6324,7 @@
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
       <c r="M27" s="76"/>
-      <c r="N27" s="171">
+      <c r="N27" s="118">
         <f>SUM(I27:M27)</f>
         <v>0</v>
       </c>
@@ -6384,22 +6362,20 @@
         <f>T28</f>
         <v>0</v>
       </c>
-      <c r="AE27" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF27" s="174">
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="120">
         <f>10+4+ROUND(1*I27+1*J27+1*K27+1*L27+1*M27,3)+ROUND(2*I27+2*J27+2*K27+2*L27+2*M27,3)</f>
         <v>14</v>
       </c>
-      <c r="AG27" s="166" t="e">
+      <c r="AG27" s="115" t="e">
         <f>U27+AC27+AD27+AF27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH27" s="175" t="e">
+      <c r="AH27" s="121" t="e">
         <f>AG27+AE27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI27" s="176" t="e">
+      <c r="AI27" s="122" t="e">
         <f>IF(AH27&gt;=40,40,AH27)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6419,20 +6395,20 @@
     <row r="28" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="80"/>
       <c r="B28" s="78"/>
-      <c r="C28" s="153" t="s">
+      <c r="C28" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="154"/>
-      <c r="E28" s="154"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="155"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="128"/>
       <c r="H28" s="56"/>
       <c r="I28" s="53"/>
       <c r="J28" s="57"/>
       <c r="K28" s="57"/>
       <c r="L28" s="57"/>
       <c r="M28" s="98"/>
-      <c r="N28" s="171"/>
+      <c r="N28" s="118"/>
       <c r="O28" s="105"/>
       <c r="P28" s="105"/>
       <c r="Q28" s="105"/>
@@ -6453,10 +6429,10 @@
       <c r="AC28" s="66"/>
       <c r="AD28" s="91"/>
       <c r="AE28" s="41"/>
-      <c r="AF28" s="179"/>
-      <c r="AG28" s="178"/>
-      <c r="AH28" s="175"/>
-      <c r="AI28" s="176"/>
+      <c r="AF28" s="125"/>
+      <c r="AG28" s="124"/>
+      <c r="AH28" s="121"/>
+      <c r="AI28" s="122"/>
       <c r="AJ28" s="42"/>
       <c r="AK28" s="43"/>
       <c r="AL28" s="44"/>
@@ -6478,7 +6454,7 @@
       <c r="K29" s="35"/>
       <c r="L29" s="57"/>
       <c r="M29" s="76"/>
-      <c r="N29" s="171">
+      <c r="N29" s="118">
         <f>SUM(I29:M29)</f>
         <v>0</v>
       </c>
@@ -6516,22 +6492,20 @@
         <f>T30</f>
         <v>0</v>
       </c>
-      <c r="AE29" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF29" s="174">
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="120">
         <f>10+4+ROUND(1*I29+1*J29+1*K29+1*L29+1*M29,3)+ROUND(2*I29+2*J29+2*K29+2*L29+2*M29,3)</f>
         <v>14</v>
       </c>
-      <c r="AG29" s="166" t="e">
+      <c r="AG29" s="115" t="e">
         <f>U29+AC29+AD29+AF29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH29" s="175" t="e">
+      <c r="AH29" s="121" t="e">
         <f>AG29+AE29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI29" s="176" t="e">
+      <c r="AI29" s="122" t="e">
         <f>IF(AH29&gt;=40,40,AH29)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6551,20 +6525,20 @@
     <row r="30" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="80"/>
       <c r="B30" s="78"/>
-      <c r="C30" s="142" t="s">
+      <c r="C30" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="143"/>
-      <c r="E30" s="143"/>
-      <c r="F30" s="143"/>
-      <c r="G30" s="144"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="131"/>
       <c r="H30" s="33"/>
       <c r="I30" s="53"/>
       <c r="J30" s="57"/>
       <c r="K30" s="57"/>
       <c r="L30" s="57"/>
       <c r="M30" s="75"/>
-      <c r="N30" s="171"/>
+      <c r="N30" s="118"/>
       <c r="O30" s="104"/>
       <c r="P30" s="105"/>
       <c r="Q30" s="105"/>
@@ -6585,10 +6559,10 @@
       <c r="AC30" s="66"/>
       <c r="AD30" s="91"/>
       <c r="AE30" s="41"/>
-      <c r="AF30" s="179"/>
-      <c r="AG30" s="178"/>
-      <c r="AH30" s="175"/>
-      <c r="AI30" s="176"/>
+      <c r="AF30" s="125"/>
+      <c r="AG30" s="124"/>
+      <c r="AH30" s="121"/>
+      <c r="AI30" s="122"/>
       <c r="AJ30" s="42"/>
       <c r="AK30" s="43"/>
       <c r="AL30" s="44"/>
@@ -6610,7 +6584,7 @@
       <c r="K31" s="81"/>
       <c r="L31" s="81"/>
       <c r="M31" s="94"/>
-      <c r="N31" s="171">
+      <c r="N31" s="118">
         <f>SUM(I31:M31)</f>
         <v>0</v>
       </c>
@@ -6648,22 +6622,20 @@
         <f>T32</f>
         <v>0</v>
       </c>
-      <c r="AE31" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF31" s="174">
+      <c r="AE31" s="41"/>
+      <c r="AF31" s="120">
         <f>10+4+ROUND(1*I31+1*J31+1*K31+1*L31+1*M31,3)+ROUND(2*I31+2*J31+2*K31+2*L31+2*M31,3)</f>
         <v>14</v>
       </c>
-      <c r="AG31" s="166" t="e">
+      <c r="AG31" s="115" t="e">
         <f>U31+AC31+AD31+AF31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH31" s="175" t="e">
+      <c r="AH31" s="121" t="e">
         <f>AG31+AE31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI31" s="176" t="e">
+      <c r="AI31" s="122" t="e">
         <f>IF(AH31&gt;=40,40,AH31)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6677,20 +6649,20 @@
     <row r="32" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="80"/>
       <c r="B32" s="78"/>
-      <c r="C32" s="142" t="s">
+      <c r="C32" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="143"/>
-      <c r="E32" s="143"/>
-      <c r="F32" s="143"/>
-      <c r="G32" s="144"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="131"/>
       <c r="H32" s="82"/>
       <c r="I32" s="83"/>
       <c r="J32" s="84"/>
       <c r="K32" s="84"/>
       <c r="L32" s="84"/>
       <c r="M32" s="95"/>
-      <c r="N32" s="171"/>
+      <c r="N32" s="118"/>
       <c r="O32" s="104"/>
       <c r="P32" s="105"/>
       <c r="Q32" s="105"/>
@@ -6711,10 +6683,10 @@
       <c r="AC32" s="66"/>
       <c r="AD32" s="91"/>
       <c r="AE32" s="41"/>
-      <c r="AF32" s="179"/>
-      <c r="AG32" s="178"/>
-      <c r="AH32" s="175"/>
-      <c r="AI32" s="176"/>
+      <c r="AF32" s="125"/>
+      <c r="AG32" s="124"/>
+      <c r="AH32" s="121"/>
+      <c r="AI32" s="122"/>
       <c r="AJ32" s="42"/>
       <c r="AK32" s="43"/>
       <c r="AL32" s="44"/>
@@ -6736,7 +6708,7 @@
       <c r="K33" s="35"/>
       <c r="L33" s="35"/>
       <c r="M33" s="60"/>
-      <c r="N33" s="171">
+      <c r="N33" s="118">
         <f>SUM(I33:M33)</f>
         <v>0</v>
       </c>
@@ -6774,22 +6746,20 @@
         <f>T34</f>
         <v>0</v>
       </c>
-      <c r="AE33" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF33" s="174">
+      <c r="AE33" s="41"/>
+      <c r="AF33" s="120">
         <f>10+4+ROUND(1*I33+1*J33+1*K33+1*L33+1*M33,3)+ROUND(2*I33+2*J33+2*K33+2*L33+2*M33,3)</f>
         <v>14</v>
       </c>
-      <c r="AG33" s="166" t="e">
+      <c r="AG33" s="115" t="e">
         <f>U33+AC33+AD33+AF33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH33" s="175" t="e">
+      <c r="AH33" s="121" t="e">
         <f>AG33+AE33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI33" s="176" t="e">
+      <c r="AI33" s="122" t="e">
         <f>IF(AH33&gt;=40,40,AH33)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6809,20 +6779,20 @@
     <row r="34" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="80"/>
       <c r="B34" s="78"/>
-      <c r="C34" s="142" t="s">
+      <c r="C34" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="143"/>
-      <c r="E34" s="143"/>
-      <c r="F34" s="143"/>
-      <c r="G34" s="144"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="131"/>
       <c r="H34" s="33"/>
       <c r="I34" s="53"/>
       <c r="J34" s="57"/>
       <c r="K34" s="57"/>
       <c r="L34" s="57"/>
       <c r="M34" s="75"/>
-      <c r="N34" s="171"/>
+      <c r="N34" s="118"/>
       <c r="O34" s="38"/>
       <c r="P34" s="38"/>
       <c r="Q34" s="38"/>
@@ -6843,10 +6813,10 @@
       <c r="AC34" s="66"/>
       <c r="AD34" s="91"/>
       <c r="AE34" s="41"/>
-      <c r="AF34" s="179"/>
-      <c r="AG34" s="178"/>
-      <c r="AH34" s="175"/>
-      <c r="AI34" s="176"/>
+      <c r="AF34" s="125"/>
+      <c r="AG34" s="124"/>
+      <c r="AH34" s="121"/>
+      <c r="AI34" s="122"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="43"/>
       <c r="AL34" s="44"/>
@@ -6868,7 +6838,7 @@
       <c r="K35" s="35"/>
       <c r="L35" s="57"/>
       <c r="M35" s="75"/>
-      <c r="N35" s="171">
+      <c r="N35" s="118">
         <f>SUM(I35:M35)</f>
         <v>0</v>
       </c>
@@ -6906,22 +6876,20 @@
         <f>T36</f>
         <v>0</v>
       </c>
-      <c r="AE35" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF35" s="174">
+      <c r="AE35" s="41"/>
+      <c r="AF35" s="120">
         <f>10+4+ROUND(1*I35+1*J35+1*K35+1*L35+1*M35,3)+ROUND(2*I35+2*J35+2*K35+2*L35+2*M35,3)</f>
         <v>14</v>
       </c>
-      <c r="AG35" s="166" t="e">
+      <c r="AG35" s="115" t="e">
         <f>U35+AC35+AD35+AF35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH35" s="175" t="e">
+      <c r="AH35" s="121" t="e">
         <f>AG35+AE35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI35" s="176" t="e">
+      <c r="AI35" s="122" t="e">
         <f>IF(AH35&gt;=40,40,AH35)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6941,20 +6909,20 @@
     <row r="36" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="80"/>
       <c r="B36" s="78"/>
-      <c r="C36" s="142" t="s">
+      <c r="C36" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="143"/>
-      <c r="E36" s="143"/>
-      <c r="F36" s="143"/>
-      <c r="G36" s="144"/>
+      <c r="D36" s="130"/>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="131"/>
       <c r="H36" s="33"/>
       <c r="I36" s="53"/>
       <c r="J36" s="57"/>
       <c r="K36" s="57"/>
       <c r="L36" s="57"/>
       <c r="M36" s="75"/>
-      <c r="N36" s="171"/>
+      <c r="N36" s="118"/>
       <c r="O36" s="105"/>
       <c r="P36" s="105"/>
       <c r="Q36" s="105"/>
@@ -6975,10 +6943,10 @@
       <c r="AC36" s="66"/>
       <c r="AD36" s="91"/>
       <c r="AE36" s="41"/>
-      <c r="AF36" s="179"/>
-      <c r="AG36" s="178"/>
-      <c r="AH36" s="175"/>
-      <c r="AI36" s="176"/>
+      <c r="AF36" s="125"/>
+      <c r="AG36" s="124"/>
+      <c r="AH36" s="121"/>
+      <c r="AI36" s="122"/>
       <c r="AJ36" s="42"/>
       <c r="AK36" s="43"/>
       <c r="AL36" s="44"/>
@@ -7000,7 +6968,7 @@
       <c r="K37" s="35"/>
       <c r="L37" s="35"/>
       <c r="M37" s="76"/>
-      <c r="N37" s="171">
+      <c r="N37" s="118">
         <f>SUM(I37:M37)</f>
         <v>0</v>
       </c>
@@ -7038,22 +7006,20 @@
         <f>T38</f>
         <v>0</v>
       </c>
-      <c r="AE37" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF37" s="174">
+      <c r="AE37" s="41"/>
+      <c r="AF37" s="120">
         <f>10+4+ROUND(1*I37+1*J37+1*K37+1*L37+1*M37,3)+ROUND(2*I37+2*J37+2*K37+2*L37+2*M37,3)</f>
         <v>14</v>
       </c>
-      <c r="AG37" s="166" t="e">
+      <c r="AG37" s="115" t="e">
         <f>U37+AC37+AD37+AF37</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH37" s="175" t="e">
+      <c r="AH37" s="121" t="e">
         <f>AG37+AE37</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI37" s="176" t="e">
+      <c r="AI37" s="122" t="e">
         <f>IF(AH37&gt;=40,40,AH37)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7073,20 +7039,20 @@
     <row r="38" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="80"/>
       <c r="B38" s="78"/>
-      <c r="C38" s="142" t="s">
+      <c r="C38" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="143"/>
-      <c r="E38" s="143"/>
-      <c r="F38" s="143"/>
-      <c r="G38" s="144"/>
+      <c r="D38" s="130"/>
+      <c r="E38" s="130"/>
+      <c r="F38" s="130"/>
+      <c r="G38" s="131"/>
       <c r="H38" s="33"/>
       <c r="I38" s="53"/>
       <c r="J38" s="57"/>
       <c r="K38" s="57"/>
       <c r="L38" s="57"/>
       <c r="M38" s="75"/>
-      <c r="N38" s="171"/>
+      <c r="N38" s="118"/>
       <c r="O38" s="104"/>
       <c r="P38" s="105"/>
       <c r="Q38" s="103"/>
@@ -7107,10 +7073,10 @@
       <c r="AC38" s="66"/>
       <c r="AD38" s="91"/>
       <c r="AE38" s="41"/>
-      <c r="AF38" s="179"/>
-      <c r="AG38" s="178"/>
-      <c r="AH38" s="175"/>
-      <c r="AI38" s="176"/>
+      <c r="AF38" s="125"/>
+      <c r="AG38" s="124"/>
+      <c r="AH38" s="121"/>
+      <c r="AI38" s="122"/>
       <c r="AJ38" s="42"/>
       <c r="AK38" s="43"/>
       <c r="AL38" s="44"/>
@@ -7132,7 +7098,7 @@
       <c r="K39" s="35"/>
       <c r="L39" s="35"/>
       <c r="M39" s="76"/>
-      <c r="N39" s="171">
+      <c r="N39" s="118">
         <f>SUM(I39:M39)</f>
         <v>0</v>
       </c>
@@ -7170,22 +7136,20 @@
         <f>T40</f>
         <v>0</v>
       </c>
-      <c r="AE39" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF39" s="174">
+      <c r="AE39" s="41"/>
+      <c r="AF39" s="120">
         <f>10+4+ROUND(1*I39+1*J39+1*K39+1*L39+1*M39,3)+ROUND(2*I39+2*J39+2*K39+2*L39+2*M39,3)</f>
         <v>14</v>
       </c>
-      <c r="AG39" s="166" t="e">
+      <c r="AG39" s="115" t="e">
         <f>U39+AC39+AD39+AF39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH39" s="175" t="e">
+      <c r="AH39" s="121" t="e">
         <f>AG39+AE39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI39" s="176" t="e">
+      <c r="AI39" s="122" t="e">
         <f>IF(AH39&gt;=40,40,AH39)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7205,20 +7169,20 @@
     <row r="40" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="80"/>
       <c r="B40" s="78"/>
-      <c r="C40" s="142" t="s">
+      <c r="C40" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="143"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-      <c r="G40" s="144"/>
+      <c r="D40" s="130"/>
+      <c r="E40" s="130"/>
+      <c r="F40" s="130"/>
+      <c r="G40" s="131"/>
       <c r="H40" s="33"/>
       <c r="I40" s="53"/>
       <c r="J40" s="57"/>
       <c r="K40" s="57"/>
       <c r="L40" s="57"/>
       <c r="M40" s="75"/>
-      <c r="N40" s="171"/>
+      <c r="N40" s="118"/>
       <c r="O40" s="104"/>
       <c r="P40" s="105"/>
       <c r="Q40" s="105"/>
@@ -7239,10 +7203,10 @@
       <c r="AC40" s="66"/>
       <c r="AD40" s="91"/>
       <c r="AE40" s="41"/>
-      <c r="AF40" s="179"/>
-      <c r="AG40" s="178"/>
-      <c r="AH40" s="175"/>
-      <c r="AI40" s="176"/>
+      <c r="AF40" s="125"/>
+      <c r="AG40" s="124"/>
+      <c r="AH40" s="121"/>
+      <c r="AI40" s="122"/>
       <c r="AJ40" s="42"/>
       <c r="AK40" s="43"/>
       <c r="AL40" s="44"/>
@@ -7264,7 +7228,7 @@
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
       <c r="M41" s="76"/>
-      <c r="N41" s="171">
+      <c r="N41" s="118">
         <f>SUM(I41:M41)</f>
         <v>0</v>
       </c>
@@ -7302,22 +7266,20 @@
         <f>T42</f>
         <v>0</v>
       </c>
-      <c r="AE41" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF41" s="174">
+      <c r="AE41" s="41"/>
+      <c r="AF41" s="120">
         <f>10+4+ROUND(1*I41+1*J41+1*K41+1*L41+1*M41,3)+ROUND(2*I41+2*J41+2*K41+2*L41+2*M41,3)</f>
         <v>14</v>
       </c>
-      <c r="AG41" s="166" t="e">
+      <c r="AG41" s="115" t="e">
         <f>U41+AC41+AD41+AF41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH41" s="175" t="e">
+      <c r="AH41" s="121" t="e">
         <f>AG41+AE41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI41" s="176" t="e">
+      <c r="AI41" s="122" t="e">
         <f>IF(AH41&gt;=40,40,AH41)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7337,20 +7299,20 @@
     <row r="42" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="80"/>
       <c r="B42" s="78"/>
-      <c r="C42" s="142" t="s">
+      <c r="C42" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="143"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="144"/>
+      <c r="D42" s="130"/>
+      <c r="E42" s="130"/>
+      <c r="F42" s="130"/>
+      <c r="G42" s="131"/>
       <c r="H42" s="33"/>
       <c r="I42" s="53"/>
       <c r="J42" s="57"/>
       <c r="K42" s="57"/>
       <c r="L42" s="57"/>
       <c r="M42" s="75"/>
-      <c r="N42" s="171"/>
+      <c r="N42" s="118"/>
       <c r="O42" s="104"/>
       <c r="P42" s="105"/>
       <c r="Q42" s="105"/>
@@ -7371,10 +7333,10 @@
       <c r="AC42" s="66"/>
       <c r="AD42" s="91"/>
       <c r="AE42" s="41"/>
-      <c r="AF42" s="179"/>
-      <c r="AG42" s="178"/>
-      <c r="AH42" s="175"/>
-      <c r="AI42" s="176"/>
+      <c r="AF42" s="125"/>
+      <c r="AG42" s="124"/>
+      <c r="AH42" s="121"/>
+      <c r="AI42" s="122"/>
       <c r="AJ42" s="42"/>
       <c r="AK42" s="43"/>
       <c r="AL42" s="44"/>
@@ -7396,7 +7358,7 @@
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
       <c r="M43" s="76"/>
-      <c r="N43" s="171">
+      <c r="N43" s="118">
         <f>SUM(I43:M43)</f>
         <v>0</v>
       </c>
@@ -7434,22 +7396,20 @@
         <f>T44</f>
         <v>0</v>
       </c>
-      <c r="AE43" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF43" s="174">
+      <c r="AE43" s="41"/>
+      <c r="AF43" s="120">
         <f>10+4+ROUND(1*I43+1*J43+1*K43+1*L43+1*M43,3)+ROUND(2*I43+2*J43+2*K43+2*L43+2*M43,3)</f>
         <v>14</v>
       </c>
-      <c r="AG43" s="166" t="e">
+      <c r="AG43" s="115" t="e">
         <f>U43+AC43+AD43+AF43</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH43" s="175" t="e">
+      <c r="AH43" s="121" t="e">
         <f>AG43+AE43</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI43" s="176" t="e">
+      <c r="AI43" s="122" t="e">
         <f>IF(AH43&gt;=40,40,AH43)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7469,20 +7429,20 @@
     <row r="44" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="80"/>
       <c r="B44" s="78"/>
-      <c r="C44" s="142" t="s">
+      <c r="C44" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="143"/>
-      <c r="E44" s="143"/>
-      <c r="F44" s="143"/>
-      <c r="G44" s="144"/>
+      <c r="D44" s="130"/>
+      <c r="E44" s="130"/>
+      <c r="F44" s="130"/>
+      <c r="G44" s="131"/>
       <c r="H44" s="33"/>
       <c r="I44" s="53"/>
       <c r="J44" s="57"/>
       <c r="K44" s="57"/>
       <c r="L44" s="57"/>
       <c r="M44" s="75"/>
-      <c r="N44" s="171"/>
+      <c r="N44" s="118"/>
       <c r="O44" s="104"/>
       <c r="P44" s="103"/>
       <c r="Q44" s="103"/>
@@ -7503,10 +7463,10 @@
       <c r="AC44" s="66"/>
       <c r="AD44" s="91"/>
       <c r="AE44" s="41"/>
-      <c r="AF44" s="179"/>
-      <c r="AG44" s="178"/>
-      <c r="AH44" s="175"/>
-      <c r="AI44" s="176"/>
+      <c r="AF44" s="125"/>
+      <c r="AG44" s="124"/>
+      <c r="AH44" s="121"/>
+      <c r="AI44" s="122"/>
       <c r="AJ44" s="42"/>
       <c r="AK44" s="43"/>
       <c r="AL44" s="44"/>
@@ -7528,7 +7488,7 @@
       <c r="K45" s="35"/>
       <c r="L45" s="35"/>
       <c r="M45" s="76"/>
-      <c r="N45" s="171">
+      <c r="N45" s="118">
         <f>SUM(I45:M45)</f>
         <v>0</v>
       </c>
@@ -7566,22 +7526,20 @@
         <f>T46</f>
         <v>0</v>
       </c>
-      <c r="AE45" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF45" s="174">
+      <c r="AE45" s="41"/>
+      <c r="AF45" s="120">
         <f>10+4+ROUND(1*I45+1*J45+1*K45+1*L45+1*M45,3)+ROUND(2*I45+2*J45+2*K45+2*L45+2*M45,3)</f>
         <v>14</v>
       </c>
-      <c r="AG45" s="166" t="e">
+      <c r="AG45" s="115" t="e">
         <f>U45+AC45+AD45+AF45</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH45" s="175" t="e">
+      <c r="AH45" s="121" t="e">
         <f>AG45+AE45</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI45" s="176" t="e">
+      <c r="AI45" s="122" t="e">
         <f>IF(AH45&gt;=40,40,AH45)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7601,20 +7559,20 @@
     <row r="46" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="80"/>
       <c r="B46" s="78"/>
-      <c r="C46" s="142" t="s">
+      <c r="C46" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D46" s="143"/>
-      <c r="E46" s="143"/>
-      <c r="F46" s="143"/>
-      <c r="G46" s="144"/>
+      <c r="D46" s="130"/>
+      <c r="E46" s="130"/>
+      <c r="F46" s="130"/>
+      <c r="G46" s="131"/>
       <c r="H46" s="33"/>
       <c r="I46" s="53"/>
       <c r="J46" s="57"/>
       <c r="K46" s="57"/>
       <c r="L46" s="57"/>
       <c r="M46" s="75"/>
-      <c r="N46" s="171"/>
+      <c r="N46" s="118"/>
       <c r="O46" s="104"/>
       <c r="P46" s="105"/>
       <c r="Q46" s="105"/>
@@ -7635,10 +7593,10 @@
       <c r="AC46" s="66"/>
       <c r="AD46" s="91"/>
       <c r="AE46" s="41"/>
-      <c r="AF46" s="179"/>
-      <c r="AG46" s="178"/>
-      <c r="AH46" s="175"/>
-      <c r="AI46" s="176"/>
+      <c r="AF46" s="125"/>
+      <c r="AG46" s="124"/>
+      <c r="AH46" s="121"/>
+      <c r="AI46" s="122"/>
       <c r="AJ46" s="42"/>
       <c r="AK46" s="43"/>
       <c r="AL46" s="44"/>
@@ -7660,7 +7618,7 @@
       <c r="K47" s="35"/>
       <c r="L47" s="57"/>
       <c r="M47" s="76"/>
-      <c r="N47" s="171">
+      <c r="N47" s="118">
         <f>SUM(I47:M47)</f>
         <v>0</v>
       </c>
@@ -7698,22 +7656,20 @@
         <f>T48</f>
         <v>0</v>
       </c>
-      <c r="AE47" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF47" s="174">
+      <c r="AE47" s="41"/>
+      <c r="AF47" s="120">
         <f>10+4+ROUND(1*I47+1*J47+1*K47+1*L47+1*M47,3)+ROUND(2*I47+2*J47+2*K47+2*L47+2*M47,3)</f>
         <v>14</v>
       </c>
-      <c r="AG47" s="166" t="e">
+      <c r="AG47" s="115" t="e">
         <f>U47+AC47+AD47+AF47</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH47" s="175" t="e">
+      <c r="AH47" s="121" t="e">
         <f>AG47+AE47</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI47" s="176" t="e">
+      <c r="AI47" s="122" t="e">
         <f>IF(AH47&gt;=40,40,AH47)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7733,20 +7689,20 @@
     <row r="48" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="80"/>
       <c r="B48" s="78"/>
-      <c r="C48" s="142" t="s">
+      <c r="C48" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D48" s="143"/>
-      <c r="E48" s="143"/>
-      <c r="F48" s="143"/>
-      <c r="G48" s="144"/>
+      <c r="D48" s="130"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="131"/>
       <c r="H48" s="33"/>
       <c r="I48" s="53"/>
       <c r="J48" s="57"/>
       <c r="K48" s="57"/>
       <c r="L48" s="57"/>
       <c r="M48" s="75"/>
-      <c r="N48" s="171"/>
+      <c r="N48" s="118"/>
       <c r="O48" s="104"/>
       <c r="P48" s="103"/>
       <c r="Q48" s="103"/>
@@ -7767,10 +7723,10 @@
       <c r="AC48" s="66"/>
       <c r="AD48" s="91"/>
       <c r="AE48" s="41"/>
-      <c r="AF48" s="179"/>
-      <c r="AG48" s="178"/>
-      <c r="AH48" s="175"/>
-      <c r="AI48" s="176"/>
+      <c r="AF48" s="125"/>
+      <c r="AG48" s="124"/>
+      <c r="AH48" s="121"/>
+      <c r="AI48" s="122"/>
       <c r="AJ48" s="42"/>
       <c r="AK48" s="43"/>
       <c r="AL48" s="44"/>
@@ -7792,7 +7748,7 @@
       <c r="K49" s="35"/>
       <c r="L49" s="35"/>
       <c r="M49" s="76"/>
-      <c r="N49" s="171">
+      <c r="N49" s="118">
         <f>SUM(I49:M49)</f>
         <v>0</v>
       </c>
@@ -7830,22 +7786,20 @@
         <f>T50</f>
         <v>0</v>
       </c>
-      <c r="AE49" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF49" s="174">
+      <c r="AE49" s="41"/>
+      <c r="AF49" s="120">
         <f>10+4+ROUND(1*I49+1*J49+1*K49+1*L49+1*M49,3)+ROUND(2*I49+2*J49+2*K49+2*L49+2*M49,3)</f>
         <v>14</v>
       </c>
-      <c r="AG49" s="166" t="e">
+      <c r="AG49" s="115" t="e">
         <f>U49+AC49+AD49+AF49</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH49" s="175" t="e">
+      <c r="AH49" s="121" t="e">
         <f>AG49+AE49</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI49" s="176" t="e">
+      <c r="AI49" s="122" t="e">
         <f>IF(AH49&gt;=40,40,AH49)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7865,20 +7819,20 @@
     <row r="50" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="80"/>
       <c r="B50" s="78"/>
-      <c r="C50" s="142" t="s">
+      <c r="C50" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D50" s="143"/>
-      <c r="E50" s="143"/>
-      <c r="F50" s="143"/>
-      <c r="G50" s="144"/>
+      <c r="D50" s="130"/>
+      <c r="E50" s="130"/>
+      <c r="F50" s="130"/>
+      <c r="G50" s="131"/>
       <c r="H50" s="33"/>
       <c r="I50" s="53"/>
       <c r="J50" s="57"/>
       <c r="K50" s="57"/>
       <c r="L50" s="57"/>
       <c r="M50" s="75"/>
-      <c r="N50" s="171"/>
+      <c r="N50" s="118"/>
       <c r="O50" s="104"/>
       <c r="P50" s="105"/>
       <c r="Q50" s="105"/>
@@ -7899,10 +7853,10 @@
       <c r="AC50" s="66"/>
       <c r="AD50" s="91"/>
       <c r="AE50" s="41"/>
-      <c r="AF50" s="179"/>
-      <c r="AG50" s="178"/>
-      <c r="AH50" s="175"/>
-      <c r="AI50" s="176"/>
+      <c r="AF50" s="125"/>
+      <c r="AG50" s="124"/>
+      <c r="AH50" s="121"/>
+      <c r="AI50" s="122"/>
       <c r="AJ50" s="42"/>
       <c r="AK50" s="43"/>
       <c r="AL50" s="44"/>
@@ -7924,7 +7878,7 @@
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
       <c r="M51" s="76"/>
-      <c r="N51" s="171">
+      <c r="N51" s="118">
         <f>SUM(I51:M51)</f>
         <v>0</v>
       </c>
@@ -7962,22 +7916,20 @@
         <f>T52</f>
         <v>0</v>
       </c>
-      <c r="AE51" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF51" s="174">
+      <c r="AE51" s="41"/>
+      <c r="AF51" s="120">
         <f>10+4+ROUND(1*I51+1*J51+1*K51+1*L51+1*M51,3)+ROUND(2*I51+2*J51+2*K51+2*L51+2*M51,3)</f>
         <v>14</v>
       </c>
-      <c r="AG51" s="166" t="e">
+      <c r="AG51" s="115" t="e">
         <f>U51+AC51+AD51+AF51</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH51" s="175" t="e">
+      <c r="AH51" s="121" t="e">
         <f>AG51+AE51</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI51" s="176" t="e">
+      <c r="AI51" s="122" t="e">
         <f>IF(AH51&gt;=40,40,AH51)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7997,20 +7949,20 @@
     <row r="52" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="80"/>
       <c r="B52" s="78"/>
-      <c r="C52" s="142" t="s">
+      <c r="C52" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="143"/>
-      <c r="E52" s="143"/>
-      <c r="F52" s="143"/>
-      <c r="G52" s="144"/>
+      <c r="D52" s="130"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="131"/>
       <c r="H52" s="33"/>
       <c r="I52" s="53"/>
       <c r="J52" s="57"/>
       <c r="K52" s="57"/>
       <c r="L52" s="57"/>
       <c r="M52" s="75"/>
-      <c r="N52" s="171"/>
+      <c r="N52" s="118"/>
       <c r="O52" s="104"/>
       <c r="P52" s="103"/>
       <c r="Q52" s="105"/>
@@ -8031,10 +7983,10 @@
       <c r="AC52" s="66"/>
       <c r="AD52" s="91"/>
       <c r="AE52" s="41"/>
-      <c r="AF52" s="179"/>
-      <c r="AG52" s="178"/>
-      <c r="AH52" s="175"/>
-      <c r="AI52" s="176"/>
+      <c r="AF52" s="125"/>
+      <c r="AG52" s="124"/>
+      <c r="AH52" s="121"/>
+      <c r="AI52" s="122"/>
       <c r="AJ52" s="42"/>
       <c r="AK52" s="43"/>
       <c r="AL52" s="44"/>
@@ -8056,7 +8008,7 @@
       <c r="K53" s="35"/>
       <c r="L53" s="35"/>
       <c r="M53" s="76"/>
-      <c r="N53" s="171">
+      <c r="N53" s="118">
         <f>SUM(I53:M53)</f>
         <v>0</v>
       </c>
@@ -8094,22 +8046,20 @@
         <f>T54</f>
         <v>0</v>
       </c>
-      <c r="AE53" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF53" s="174">
+      <c r="AE53" s="41"/>
+      <c r="AF53" s="120">
         <f>10+4+ROUND(1*I53+1*J53+1*K53+1*L53+1*M53,3)+ROUND(2*I53+2*J53+2*K53+2*L53+2*M53,3)</f>
         <v>14</v>
       </c>
-      <c r="AG53" s="166" t="e">
+      <c r="AG53" s="115" t="e">
         <f>U53+AC53+AD53+AF53</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH53" s="175" t="e">
+      <c r="AH53" s="121" t="e">
         <f>AG53+AE53</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI53" s="176" t="e">
+      <c r="AI53" s="122" t="e">
         <f>IF(AH53&gt;=40,40,AH53)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8129,20 +8079,20 @@
     <row r="54" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="80"/>
       <c r="B54" s="78"/>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="143"/>
-      <c r="E54" s="143"/>
-      <c r="F54" s="143"/>
-      <c r="G54" s="144"/>
+      <c r="D54" s="130"/>
+      <c r="E54" s="130"/>
+      <c r="F54" s="130"/>
+      <c r="G54" s="131"/>
       <c r="H54" s="33"/>
       <c r="I54" s="53"/>
       <c r="J54" s="57"/>
       <c r="K54" s="57"/>
       <c r="L54" s="57"/>
       <c r="M54" s="75"/>
-      <c r="N54" s="171"/>
+      <c r="N54" s="118"/>
       <c r="O54" s="104"/>
       <c r="P54" s="104"/>
       <c r="Q54" s="105"/>
@@ -8163,10 +8113,10 @@
       <c r="AC54" s="66"/>
       <c r="AD54" s="91"/>
       <c r="AE54" s="41"/>
-      <c r="AF54" s="179"/>
-      <c r="AG54" s="178"/>
-      <c r="AH54" s="175"/>
-      <c r="AI54" s="176"/>
+      <c r="AF54" s="125"/>
+      <c r="AG54" s="124"/>
+      <c r="AH54" s="121"/>
+      <c r="AI54" s="122"/>
       <c r="AJ54" s="42"/>
       <c r="AK54" s="43"/>
       <c r="AL54" s="44"/>
@@ -8188,7 +8138,7 @@
       <c r="K55" s="35"/>
       <c r="L55" s="57"/>
       <c r="M55" s="76"/>
-      <c r="N55" s="171">
+      <c r="N55" s="118">
         <f>SUM(I55:M55)</f>
         <v>0</v>
       </c>
@@ -8226,22 +8176,20 @@
         <f>T56</f>
         <v>0</v>
       </c>
-      <c r="AE55" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF55" s="174">
+      <c r="AE55" s="41"/>
+      <c r="AF55" s="120">
         <f>10+4+ROUND(1*I55+1*J55+1*K55+1*L55+1*M55,3)+ROUND(2*I55+2*J55+2*K55+2*L55+2*M55,3)</f>
         <v>14</v>
       </c>
-      <c r="AG55" s="166" t="e">
+      <c r="AG55" s="115" t="e">
         <f>U55+AC55+AD55+AF55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH55" s="175" t="e">
+      <c r="AH55" s="121" t="e">
         <f>AG55+AE55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI55" s="176" t="e">
+      <c r="AI55" s="122" t="e">
         <f>IF(AH55&gt;=40,40,AH55)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8261,20 +8209,20 @@
     <row r="56" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="80"/>
       <c r="B56" s="78"/>
-      <c r="C56" s="142" t="s">
+      <c r="C56" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D56" s="143"/>
-      <c r="E56" s="143"/>
-      <c r="F56" s="143"/>
-      <c r="G56" s="144"/>
+      <c r="D56" s="130"/>
+      <c r="E56" s="130"/>
+      <c r="F56" s="130"/>
+      <c r="G56" s="131"/>
       <c r="H56" s="33"/>
       <c r="I56" s="53"/>
       <c r="J56" s="57"/>
       <c r="K56" s="57"/>
       <c r="L56" s="57"/>
       <c r="M56" s="75"/>
-      <c r="N56" s="171"/>
+      <c r="N56" s="118"/>
       <c r="O56" s="104"/>
       <c r="P56" s="104"/>
       <c r="Q56" s="104"/>
@@ -8295,10 +8243,10 @@
       <c r="AC56" s="66"/>
       <c r="AD56" s="91"/>
       <c r="AE56" s="41"/>
-      <c r="AF56" s="179"/>
-      <c r="AG56" s="178"/>
-      <c r="AH56" s="175"/>
-      <c r="AI56" s="176"/>
+      <c r="AF56" s="125"/>
+      <c r="AG56" s="124"/>
+      <c r="AH56" s="121"/>
+      <c r="AI56" s="122"/>
       <c r="AJ56" s="42"/>
       <c r="AK56" s="43"/>
       <c r="AL56" s="44"/>
@@ -8320,7 +8268,7 @@
       <c r="K57" s="81"/>
       <c r="L57" s="81"/>
       <c r="M57" s="94"/>
-      <c r="N57" s="171">
+      <c r="N57" s="118">
         <f>SUM(I57:M57)</f>
         <v>0</v>
       </c>
@@ -8358,22 +8306,20 @@
         <f>T58</f>
         <v>0</v>
       </c>
-      <c r="AE57" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF57" s="174">
+      <c r="AE57" s="41"/>
+      <c r="AF57" s="120">
         <f>10+4+ROUND(1*I57+1*J57+1*K57+1*L57+1*M57,3)+ROUND(2*I57+2*J57+2*K57+2*L57+2*M57,3)</f>
         <v>14</v>
       </c>
-      <c r="AG57" s="166" t="e">
+      <c r="AG57" s="115" t="e">
         <f>U57+AC57+AD57+AF57</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH57" s="175" t="e">
+      <c r="AH57" s="121" t="e">
         <f>AG57+AE57</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI57" s="176" t="e">
+      <c r="AI57" s="122" t="e">
         <f>IF(AH57&gt;=40,40,AH57)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8387,20 +8333,20 @@
     <row r="58" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="80"/>
       <c r="B58" s="78"/>
-      <c r="C58" s="142" t="s">
+      <c r="C58" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D58" s="143"/>
-      <c r="E58" s="143"/>
-      <c r="F58" s="143"/>
-      <c r="G58" s="144"/>
+      <c r="D58" s="130"/>
+      <c r="E58" s="130"/>
+      <c r="F58" s="130"/>
+      <c r="G58" s="131"/>
       <c r="H58" s="82"/>
       <c r="I58" s="83"/>
       <c r="J58" s="84"/>
       <c r="K58" s="84"/>
       <c r="L58" s="84"/>
       <c r="M58" s="95"/>
-      <c r="N58" s="171"/>
+      <c r="N58" s="118"/>
       <c r="O58" s="105"/>
       <c r="P58" s="105"/>
       <c r="Q58" s="105"/>
@@ -8421,10 +8367,10 @@
       <c r="AC58" s="66"/>
       <c r="AD58" s="91"/>
       <c r="AE58" s="41"/>
-      <c r="AF58" s="179"/>
-      <c r="AG58" s="178"/>
-      <c r="AH58" s="175"/>
-      <c r="AI58" s="176"/>
+      <c r="AF58" s="125"/>
+      <c r="AG58" s="124"/>
+      <c r="AH58" s="121"/>
+      <c r="AI58" s="122"/>
       <c r="AJ58" s="42"/>
       <c r="AK58" s="43"/>
       <c r="AL58" s="44"/>
@@ -8446,7 +8392,7 @@
       <c r="K59" s="35"/>
       <c r="L59" s="35"/>
       <c r="M59" s="76"/>
-      <c r="N59" s="171">
+      <c r="N59" s="118">
         <f>SUM(I59:M59)</f>
         <v>0</v>
       </c>
@@ -8484,22 +8430,20 @@
         <f>T60</f>
         <v>0</v>
       </c>
-      <c r="AE59" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="AF59" s="174">
+      <c r="AE59" s="41"/>
+      <c r="AF59" s="120">
         <f>10+4+ROUND(1*I59+1*J59+1*K59+1*L59+1*M59,3)+ROUND(2*I59+2*J59+2*K59+2*L59+2*M59,3)</f>
         <v>14</v>
       </c>
-      <c r="AG59" s="166" t="e">
+      <c r="AG59" s="115" t="e">
         <f>U59+AC59+AD59+AF59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH59" s="175" t="e">
+      <c r="AH59" s="121" t="e">
         <f>AG59+AE59</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI59" s="176" t="e">
+      <c r="AI59" s="122" t="e">
         <f>IF(AH59&gt;=40,40,AH59)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8519,20 +8463,20 @@
     <row r="60" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="80"/>
       <c r="B60" s="78"/>
-      <c r="C60" s="142" t="s">
+      <c r="C60" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D60" s="143"/>
-      <c r="E60" s="143"/>
-      <c r="F60" s="143"/>
-      <c r="G60" s="144"/>
+      <c r="D60" s="130"/>
+      <c r="E60" s="130"/>
+      <c r="F60" s="130"/>
+      <c r="G60" s="131"/>
       <c r="H60" s="33"/>
       <c r="I60" s="53"/>
       <c r="J60" s="57"/>
       <c r="K60" s="57"/>
       <c r="L60" s="57"/>
       <c r="M60" s="75"/>
-      <c r="N60" s="171"/>
+      <c r="N60" s="118"/>
       <c r="O60" s="104"/>
       <c r="P60" s="105"/>
       <c r="Q60" s="105"/>
@@ -8553,10 +8497,10 @@
       <c r="AC60" s="66"/>
       <c r="AD60" s="91"/>
       <c r="AE60" s="41"/>
-      <c r="AF60" s="179"/>
-      <c r="AG60" s="178"/>
-      <c r="AH60" s="175"/>
-      <c r="AI60" s="176"/>
+      <c r="AF60" s="125"/>
+      <c r="AG60" s="124"/>
+      <c r="AH60" s="121"/>
+      <c r="AI60" s="122"/>
       <c r="AJ60" s="42"/>
       <c r="AK60" s="43"/>
       <c r="AL60" s="44"/>
@@ -8578,7 +8522,7 @@
       <c r="K61" s="35"/>
       <c r="L61" s="35"/>
       <c r="M61" s="76"/>
-      <c r="N61" s="171">
+      <c r="N61" s="118">
         <f>SUM(I61:M61)</f>
         <v>0</v>
       </c>
@@ -8616,22 +8560,20 @@
         <f>T62</f>
         <v>0</v>
       </c>
-      <c r="AE61" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="AF61" s="174">
+      <c r="AE61" s="41"/>
+      <c r="AF61" s="120">
         <f>10+4+ROUND(1*I61+1*J61+1*K61+1*L61+1*M61,3)+ROUND(2*I61+2*J61+2*K61+2*L61+2*M61,3)</f>
         <v>14</v>
       </c>
-      <c r="AG61" s="166" t="e">
+      <c r="AG61" s="115" t="e">
         <f>U61+AC61+AD61+AF61</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH61" s="175" t="e">
+      <c r="AH61" s="121" t="e">
         <f>AG61+AE61</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI61" s="176" t="e">
+      <c r="AI61" s="122" t="e">
         <f>IF(AH61&gt;=40,40,AH61)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8651,20 +8593,20 @@
     <row r="62" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="80"/>
       <c r="B62" s="78"/>
-      <c r="C62" s="142" t="s">
+      <c r="C62" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D62" s="143"/>
-      <c r="E62" s="143"/>
-      <c r="F62" s="143"/>
-      <c r="G62" s="144"/>
+      <c r="D62" s="130"/>
+      <c r="E62" s="130"/>
+      <c r="F62" s="130"/>
+      <c r="G62" s="131"/>
       <c r="H62" s="33"/>
       <c r="I62" s="53"/>
       <c r="J62" s="57"/>
       <c r="K62" s="57"/>
       <c r="L62" s="57"/>
       <c r="M62" s="75"/>
-      <c r="N62" s="171"/>
+      <c r="N62" s="118"/>
       <c r="O62" s="105"/>
       <c r="P62" s="105"/>
       <c r="Q62" s="105"/>
@@ -8685,10 +8627,10 @@
       <c r="AC62" s="66"/>
       <c r="AD62" s="91"/>
       <c r="AE62" s="41"/>
-      <c r="AF62" s="179"/>
-      <c r="AG62" s="178"/>
-      <c r="AH62" s="175"/>
-      <c r="AI62" s="176"/>
+      <c r="AF62" s="125"/>
+      <c r="AG62" s="124"/>
+      <c r="AH62" s="121"/>
+      <c r="AI62" s="122"/>
       <c r="AJ62" s="42"/>
       <c r="AK62" s="43"/>
       <c r="AL62" s="44"/>
@@ -8710,7 +8652,7 @@
       <c r="K63" s="35"/>
       <c r="L63" s="35"/>
       <c r="M63" s="76"/>
-      <c r="N63" s="171">
+      <c r="N63" s="118">
         <f>SUM(I63:M63)</f>
         <v>0</v>
       </c>
@@ -8748,22 +8690,20 @@
         <f>T64</f>
         <v>0</v>
       </c>
-      <c r="AE63" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF63" s="174">
+      <c r="AE63" s="41"/>
+      <c r="AF63" s="120">
         <f>10+4+ROUND(1*I63+1*J63+1*K63+1*L63+1*M63,3)+ROUND(2*I63+2*J63+2*K63+2*L63+2*M63,3)</f>
         <v>14</v>
       </c>
-      <c r="AG63" s="166" t="e">
+      <c r="AG63" s="115" t="e">
         <f>U63+AC63+AD63+AF63</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH63" s="175" t="e">
+      <c r="AH63" s="121" t="e">
         <f>AG63+AE63</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI63" s="176" t="e">
+      <c r="AI63" s="122" t="e">
         <f>IF(AH63&gt;=40,40,AH63)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8783,20 +8723,20 @@
     <row r="64" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="80"/>
       <c r="B64" s="78"/>
-      <c r="C64" s="142" t="s">
+      <c r="C64" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D64" s="143"/>
-      <c r="E64" s="143"/>
-      <c r="F64" s="143"/>
-      <c r="G64" s="144"/>
+      <c r="D64" s="130"/>
+      <c r="E64" s="130"/>
+      <c r="F64" s="130"/>
+      <c r="G64" s="131"/>
       <c r="H64" s="33"/>
       <c r="I64" s="53"/>
       <c r="J64" s="57"/>
       <c r="K64" s="57"/>
       <c r="L64" s="57"/>
       <c r="M64" s="75"/>
-      <c r="N64" s="171"/>
+      <c r="N64" s="118"/>
       <c r="O64" s="105"/>
       <c r="P64" s="105"/>
       <c r="Q64" s="105"/>
@@ -8817,10 +8757,10 @@
       <c r="AC64" s="66"/>
       <c r="AD64" s="91"/>
       <c r="AE64" s="41"/>
-      <c r="AF64" s="179"/>
-      <c r="AG64" s="178"/>
-      <c r="AH64" s="175"/>
-      <c r="AI64" s="176"/>
+      <c r="AF64" s="125"/>
+      <c r="AG64" s="124"/>
+      <c r="AH64" s="121"/>
+      <c r="AI64" s="122"/>
       <c r="AJ64" s="42"/>
       <c r="AK64" s="43"/>
       <c r="AL64" s="44"/>
@@ -8842,7 +8782,7 @@
       <c r="K65" s="35"/>
       <c r="L65" s="35"/>
       <c r="M65" s="76"/>
-      <c r="N65" s="171">
+      <c r="N65" s="118">
         <f>SUM(I65:M65)</f>
         <v>0</v>
       </c>
@@ -8880,22 +8820,20 @@
         <f>T66</f>
         <v>0</v>
       </c>
-      <c r="AE65" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF65" s="174">
+      <c r="AE65" s="41"/>
+      <c r="AF65" s="120">
         <f>10+4+ROUND(1*I65+1*J65+1*K65+1*L65+1*M65,3)+ROUND(2*I65+2*J65+2*K65+2*L65+2*M65,3)</f>
         <v>14</v>
       </c>
-      <c r="AG65" s="166" t="e">
+      <c r="AG65" s="115" t="e">
         <f>U65+AC65+AD65+AF65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH65" s="175" t="e">
+      <c r="AH65" s="121" t="e">
         <f>AG65+AE65</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI65" s="176" t="e">
+      <c r="AI65" s="122" t="e">
         <f>IF(AH65&gt;=40,40,AH65)</f>
         <v>#DIV/0!</v>
       </c>
@@ -8915,20 +8853,20 @@
     <row r="66" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="80"/>
       <c r="B66" s="78"/>
-      <c r="C66" s="142" t="s">
+      <c r="C66" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D66" s="143"/>
-      <c r="E66" s="143"/>
-      <c r="F66" s="143"/>
-      <c r="G66" s="144"/>
+      <c r="D66" s="130"/>
+      <c r="E66" s="130"/>
+      <c r="F66" s="130"/>
+      <c r="G66" s="131"/>
       <c r="H66" s="33"/>
       <c r="I66" s="53"/>
       <c r="J66" s="57"/>
       <c r="K66" s="57"/>
       <c r="L66" s="57"/>
       <c r="M66" s="75"/>
-      <c r="N66" s="171"/>
+      <c r="N66" s="118"/>
       <c r="O66" s="104"/>
       <c r="P66" s="105"/>
       <c r="Q66" s="105"/>
@@ -8949,10 +8887,10 @@
       <c r="AC66" s="66"/>
       <c r="AD66" s="91"/>
       <c r="AE66" s="41"/>
-      <c r="AF66" s="179"/>
-      <c r="AG66" s="178"/>
-      <c r="AH66" s="175"/>
-      <c r="AI66" s="176"/>
+      <c r="AF66" s="125"/>
+      <c r="AG66" s="124"/>
+      <c r="AH66" s="121"/>
+      <c r="AI66" s="122"/>
       <c r="AJ66" s="42"/>
       <c r="AK66" s="43"/>
       <c r="AL66" s="44"/>
@@ -8974,7 +8912,7 @@
       <c r="K67" s="35"/>
       <c r="L67" s="57"/>
       <c r="M67" s="76"/>
-      <c r="N67" s="171">
+      <c r="N67" s="118">
         <f>SUM(I67:M67)</f>
         <v>0</v>
       </c>
@@ -9012,22 +8950,20 @@
         <f>T68</f>
         <v>0</v>
       </c>
-      <c r="AE67" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF67" s="174">
+      <c r="AE67" s="41"/>
+      <c r="AF67" s="120">
         <f>10+4+ROUND(1*I67+1*J67+1*K67+1*L67+1*M67,3)+ROUND(2*I67+2*J67+2*K67+2*L67+2*M67,3)</f>
         <v>14</v>
       </c>
-      <c r="AG67" s="166" t="e">
+      <c r="AG67" s="115" t="e">
         <f>U67+AC67+AD67+AF67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH67" s="175" t="e">
+      <c r="AH67" s="121" t="e">
         <f>AG67+AE67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI67" s="176" t="e">
+      <c r="AI67" s="122" t="e">
         <f>IF(AH67&gt;=40,40,AH67)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9047,20 +8983,20 @@
     <row r="68" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="80"/>
       <c r="B68" s="78"/>
-      <c r="C68" s="142" t="s">
+      <c r="C68" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D68" s="143"/>
-      <c r="E68" s="143"/>
-      <c r="F68" s="143"/>
-      <c r="G68" s="144"/>
+      <c r="D68" s="130"/>
+      <c r="E68" s="130"/>
+      <c r="F68" s="130"/>
+      <c r="G68" s="131"/>
       <c r="H68" s="33"/>
       <c r="I68" s="53"/>
       <c r="J68" s="57"/>
       <c r="K68" s="57"/>
       <c r="L68" s="57"/>
       <c r="M68" s="75"/>
-      <c r="N68" s="171"/>
+      <c r="N68" s="118"/>
       <c r="O68" s="104"/>
       <c r="P68" s="103"/>
       <c r="Q68" s="103"/>
@@ -9081,10 +9017,10 @@
       <c r="AC68" s="66"/>
       <c r="AD68" s="91"/>
       <c r="AE68" s="41"/>
-      <c r="AF68" s="179"/>
-      <c r="AG68" s="178"/>
-      <c r="AH68" s="175"/>
-      <c r="AI68" s="176"/>
+      <c r="AF68" s="125"/>
+      <c r="AG68" s="124"/>
+      <c r="AH68" s="121"/>
+      <c r="AI68" s="122"/>
       <c r="AJ68" s="42"/>
       <c r="AK68" s="43"/>
       <c r="AL68" s="44"/>
@@ -9106,7 +9042,7 @@
       <c r="K69" s="35"/>
       <c r="L69" s="35"/>
       <c r="M69" s="76"/>
-      <c r="N69" s="171">
+      <c r="N69" s="118">
         <f>SUM(I69:M69)</f>
         <v>0</v>
       </c>
@@ -9144,22 +9080,20 @@
         <f>T70</f>
         <v>0</v>
       </c>
-      <c r="AE69" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF69" s="174">
+      <c r="AE69" s="41"/>
+      <c r="AF69" s="120">
         <f>10+4+ROUND(1*I69+1*J69+1*K69+1*L69+1*M69,3)+ROUND(2*I69+2*J69+2*K69+2*L69+2*M69,3)</f>
         <v>14</v>
       </c>
-      <c r="AG69" s="166" t="e">
+      <c r="AG69" s="115" t="e">
         <f>U69+AC69+AD69+AF69</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH69" s="175" t="e">
+      <c r="AH69" s="121" t="e">
         <f>AG69+AE69</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI69" s="176" t="e">
+      <c r="AI69" s="122" t="e">
         <f>IF(AH69&gt;=40,40,AH69)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9179,20 +9113,20 @@
     <row r="70" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="80"/>
       <c r="B70" s="78"/>
-      <c r="C70" s="153" t="s">
+      <c r="C70" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D70" s="154"/>
-      <c r="E70" s="154"/>
-      <c r="F70" s="154"/>
-      <c r="G70" s="155"/>
+      <c r="D70" s="127"/>
+      <c r="E70" s="127"/>
+      <c r="F70" s="127"/>
+      <c r="G70" s="128"/>
       <c r="H70" s="33"/>
       <c r="I70" s="53"/>
       <c r="J70" s="57"/>
       <c r="K70" s="57"/>
       <c r="L70" s="57"/>
       <c r="M70" s="75"/>
-      <c r="N70" s="171"/>
+      <c r="N70" s="118"/>
       <c r="O70" s="104"/>
       <c r="P70" s="104"/>
       <c r="Q70" s="104"/>
@@ -9213,10 +9147,10 @@
       <c r="AC70" s="66"/>
       <c r="AD70" s="91"/>
       <c r="AE70" s="41"/>
-      <c r="AF70" s="179"/>
-      <c r="AG70" s="178"/>
-      <c r="AH70" s="175"/>
-      <c r="AI70" s="176"/>
+      <c r="AF70" s="125"/>
+      <c r="AG70" s="124"/>
+      <c r="AH70" s="121"/>
+      <c r="AI70" s="122"/>
       <c r="AJ70" s="42"/>
       <c r="AK70" s="43"/>
       <c r="AL70" s="44"/>
@@ -9238,7 +9172,7 @@
       <c r="K71" s="35"/>
       <c r="L71" s="35"/>
       <c r="M71" s="76"/>
-      <c r="N71" s="171">
+      <c r="N71" s="118">
         <f>SUM(I71:M71)</f>
         <v>0</v>
       </c>
@@ -9276,22 +9210,20 @@
         <f>T72</f>
         <v>0</v>
       </c>
-      <c r="AE71" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF71" s="174">
+      <c r="AE71" s="41"/>
+      <c r="AF71" s="120">
         <f>10+4+ROUND(1*I71+1*J71+1*K71+1*L71+1*M71,3)+ROUND(2*I71+2*J71+2*K71+2*L71+2*M71,3)</f>
         <v>14</v>
       </c>
-      <c r="AG71" s="166" t="e">
+      <c r="AG71" s="115" t="e">
         <f>U71+AC71+AD71+AF71</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH71" s="175" t="e">
+      <c r="AH71" s="121" t="e">
         <f>AG71+AE71</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI71" s="176" t="e">
+      <c r="AI71" s="122" t="e">
         <f>IF(AH71&gt;=40,40,AH71)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9305,20 +9237,20 @@
     <row r="72" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="80"/>
       <c r="B72" s="78"/>
-      <c r="C72" s="153" t="s">
+      <c r="C72" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D72" s="154"/>
-      <c r="E72" s="154"/>
-      <c r="F72" s="154"/>
-      <c r="G72" s="155"/>
+      <c r="D72" s="127"/>
+      <c r="E72" s="127"/>
+      <c r="F72" s="127"/>
+      <c r="G72" s="128"/>
       <c r="H72" s="33"/>
       <c r="I72" s="53"/>
       <c r="J72" s="57"/>
       <c r="K72" s="57"/>
       <c r="L72" s="57"/>
       <c r="M72" s="75"/>
-      <c r="N72" s="171"/>
+      <c r="N72" s="118"/>
       <c r="O72" s="105"/>
       <c r="P72" s="105"/>
       <c r="Q72" s="105"/>
@@ -9339,10 +9271,10 @@
       <c r="AC72" s="66"/>
       <c r="AD72" s="91"/>
       <c r="AE72" s="41"/>
-      <c r="AF72" s="179"/>
-      <c r="AG72" s="178"/>
-      <c r="AH72" s="175"/>
-      <c r="AI72" s="176"/>
+      <c r="AF72" s="125"/>
+      <c r="AG72" s="124"/>
+      <c r="AH72" s="121"/>
+      <c r="AI72" s="122"/>
       <c r="AJ72" s="42"/>
       <c r="AK72" s="43"/>
       <c r="AL72" s="44"/>
@@ -9364,7 +9296,7 @@
       <c r="K73" s="35"/>
       <c r="L73" s="35"/>
       <c r="M73" s="76"/>
-      <c r="N73" s="171">
+      <c r="N73" s="118">
         <f>SUM(I73:M73)</f>
         <v>0</v>
       </c>
@@ -9402,22 +9334,20 @@
         <f>T74</f>
         <v>0</v>
       </c>
-      <c r="AE73" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF73" s="174">
+      <c r="AE73" s="41"/>
+      <c r="AF73" s="120">
         <f>10+4+ROUND(1*I73+1*J73+1*K73+1*L73+1*M73,3)+ROUND(2*I73+2*J73+2*K73+2*L73+2*M73,3)</f>
         <v>14</v>
       </c>
-      <c r="AG73" s="166" t="e">
+      <c r="AG73" s="115" t="e">
         <f>U73+AC73+AD73+AF73</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH73" s="175" t="e">
+      <c r="AH73" s="121" t="e">
         <f>AG73+AE73</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI73" s="176" t="e">
+      <c r="AI73" s="122" t="e">
         <f>IF(AH73&gt;=40,40,AH73)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9437,20 +9367,20 @@
     <row r="74" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="80"/>
       <c r="B74" s="78"/>
-      <c r="C74" s="153" t="s">
+      <c r="C74" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D74" s="154"/>
-      <c r="E74" s="154"/>
-      <c r="F74" s="154"/>
-      <c r="G74" s="155"/>
+      <c r="D74" s="127"/>
+      <c r="E74" s="127"/>
+      <c r="F74" s="127"/>
+      <c r="G74" s="128"/>
       <c r="H74" s="33"/>
       <c r="I74" s="53"/>
       <c r="J74" s="57"/>
       <c r="K74" s="57"/>
       <c r="L74" s="57"/>
       <c r="M74" s="75"/>
-      <c r="N74" s="171"/>
+      <c r="N74" s="118"/>
       <c r="O74" s="104"/>
       <c r="P74" s="105"/>
       <c r="Q74" s="105"/>
@@ -9471,10 +9401,10 @@
       <c r="AC74" s="66"/>
       <c r="AD74" s="91"/>
       <c r="AE74" s="41"/>
-      <c r="AF74" s="179"/>
-      <c r="AG74" s="178"/>
-      <c r="AH74" s="175"/>
-      <c r="AI74" s="176"/>
+      <c r="AF74" s="125"/>
+      <c r="AG74" s="124"/>
+      <c r="AH74" s="121"/>
+      <c r="AI74" s="122"/>
       <c r="AJ74" s="42"/>
       <c r="AK74" s="43"/>
       <c r="AL74" s="44"/>
@@ -9496,7 +9426,7 @@
       <c r="K75" s="35"/>
       <c r="L75" s="35"/>
       <c r="M75" s="76"/>
-      <c r="N75" s="171">
+      <c r="N75" s="118">
         <f>SUM(I75:M75)</f>
         <v>0</v>
       </c>
@@ -9534,22 +9464,20 @@
         <f>T76</f>
         <v>0</v>
       </c>
-      <c r="AE75" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF75" s="174">
+      <c r="AE75" s="41"/>
+      <c r="AF75" s="120">
         <f>10+4+ROUND(1*I75+1*J75+1*K75+1*L75+1*M75,3)+ROUND(2*I75+2*J75+2*K75+2*L75+2*M75,3)</f>
         <v>14</v>
       </c>
-      <c r="AG75" s="166" t="e">
+      <c r="AG75" s="115" t="e">
         <f>U75+AC75+AD75+AF75</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH75" s="175" t="e">
+      <c r="AH75" s="121" t="e">
         <f>AG75+AE75</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI75" s="176" t="e">
+      <c r="AI75" s="122" t="e">
         <f>IF(AH75&gt;=40,40,AH75)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9569,20 +9497,20 @@
     <row r="76" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="80"/>
       <c r="B76" s="78"/>
-      <c r="C76" s="153" t="s">
+      <c r="C76" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="154"/>
-      <c r="E76" s="154"/>
-      <c r="F76" s="154"/>
-      <c r="G76" s="155"/>
+      <c r="D76" s="127"/>
+      <c r="E76" s="127"/>
+      <c r="F76" s="127"/>
+      <c r="G76" s="128"/>
       <c r="H76" s="33"/>
       <c r="I76" s="53"/>
       <c r="J76" s="57"/>
       <c r="K76" s="57"/>
       <c r="L76" s="57"/>
       <c r="M76" s="75"/>
-      <c r="N76" s="171"/>
+      <c r="N76" s="118"/>
       <c r="O76" s="104"/>
       <c r="P76" s="105"/>
       <c r="Q76" s="105"/>
@@ -9603,10 +9531,10 @@
       <c r="AC76" s="66"/>
       <c r="AD76" s="91"/>
       <c r="AE76" s="41"/>
-      <c r="AF76" s="179"/>
-      <c r="AG76" s="178"/>
-      <c r="AH76" s="175"/>
-      <c r="AI76" s="176"/>
+      <c r="AF76" s="125"/>
+      <c r="AG76" s="124"/>
+      <c r="AH76" s="121"/>
+      <c r="AI76" s="122"/>
       <c r="AJ76" s="42"/>
       <c r="AK76" s="43"/>
       <c r="AL76" s="44"/>
@@ -9628,7 +9556,7 @@
       <c r="K77" s="35"/>
       <c r="L77" s="35"/>
       <c r="M77" s="76"/>
-      <c r="N77" s="171">
+      <c r="N77" s="118">
         <f>SUM(I77:M77)</f>
         <v>0</v>
       </c>
@@ -9666,22 +9594,20 @@
         <f>T78</f>
         <v>0</v>
       </c>
-      <c r="AE77" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF77" s="174">
+      <c r="AE77" s="41"/>
+      <c r="AF77" s="120">
         <f>10+4+ROUND(1*I77+1*J77+1*K77+1*L77+1*M77,3)+ROUND(2*I77+2*J77+2*K77+2*L77+2*M77,3)</f>
         <v>14</v>
       </c>
-      <c r="AG77" s="166" t="e">
+      <c r="AG77" s="115" t="e">
         <f>U77+AC77+AD77+AF77</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH77" s="175" t="e">
+      <c r="AH77" s="121" t="e">
         <f>AG77+AE77</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI77" s="176" t="e">
+      <c r="AI77" s="122" t="e">
         <f>IF(AH77&gt;=40,40,AH77)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9701,20 +9627,20 @@
     <row r="78" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="80"/>
       <c r="B78" s="78"/>
-      <c r="C78" s="153" t="s">
+      <c r="C78" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D78" s="154"/>
-      <c r="E78" s="154"/>
-      <c r="F78" s="154"/>
-      <c r="G78" s="155"/>
+      <c r="D78" s="127"/>
+      <c r="E78" s="127"/>
+      <c r="F78" s="127"/>
+      <c r="G78" s="128"/>
       <c r="H78" s="33"/>
       <c r="I78" s="53"/>
       <c r="J78" s="57"/>
       <c r="K78" s="57"/>
       <c r="L78" s="57"/>
       <c r="M78" s="75"/>
-      <c r="N78" s="171"/>
+      <c r="N78" s="118"/>
       <c r="O78" s="104"/>
       <c r="P78" s="105"/>
       <c r="Q78" s="105"/>
@@ -9735,10 +9661,10 @@
       <c r="AC78" s="66"/>
       <c r="AD78" s="91"/>
       <c r="AE78" s="41"/>
-      <c r="AF78" s="179"/>
-      <c r="AG78" s="178"/>
-      <c r="AH78" s="175"/>
-      <c r="AI78" s="176"/>
+      <c r="AF78" s="125"/>
+      <c r="AG78" s="124"/>
+      <c r="AH78" s="121"/>
+      <c r="AI78" s="122"/>
       <c r="AJ78" s="42"/>
       <c r="AK78" s="43"/>
       <c r="AL78" s="44"/>
@@ -9760,7 +9686,7 @@
       <c r="K79" s="35"/>
       <c r="L79" s="35"/>
       <c r="M79" s="76"/>
-      <c r="N79" s="171">
+      <c r="N79" s="118">
         <f>SUM(I79:M79)</f>
         <v>0</v>
       </c>
@@ -9798,22 +9724,20 @@
         <f>T80</f>
         <v>0</v>
       </c>
-      <c r="AE79" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF79" s="174">
+      <c r="AE79" s="41"/>
+      <c r="AF79" s="120">
         <f>10+4+ROUND(1*I79+1*J79+1*K79+1*L79+1*M79,3)+ROUND(2*I79+2*J79+2*K79+2*L79+2*M79,3)</f>
         <v>14</v>
       </c>
-      <c r="AG79" s="166" t="e">
+      <c r="AG79" s="115" t="e">
         <f>U79+AC79+AD79+AF79</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH79" s="175" t="e">
+      <c r="AH79" s="121" t="e">
         <f>AG79+AE79</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI79" s="176" t="e">
+      <c r="AI79" s="122" t="e">
         <f>IF(AH79&gt;=40,40,AH79)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9833,20 +9757,20 @@
     <row r="80" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="80"/>
       <c r="B80" s="78"/>
-      <c r="C80" s="153" t="s">
+      <c r="C80" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D80" s="154"/>
-      <c r="E80" s="154"/>
-      <c r="F80" s="154"/>
-      <c r="G80" s="155"/>
+      <c r="D80" s="127"/>
+      <c r="E80" s="127"/>
+      <c r="F80" s="127"/>
+      <c r="G80" s="128"/>
       <c r="H80" s="33"/>
       <c r="I80" s="53"/>
       <c r="J80" s="57"/>
       <c r="K80" s="57"/>
       <c r="L80" s="57"/>
       <c r="M80" s="75"/>
-      <c r="N80" s="171"/>
+      <c r="N80" s="118"/>
       <c r="O80" s="105"/>
       <c r="P80" s="105"/>
       <c r="Q80" s="103"/>
@@ -9867,10 +9791,10 @@
       <c r="AC80" s="66"/>
       <c r="AD80" s="91"/>
       <c r="AE80" s="41"/>
-      <c r="AF80" s="179"/>
-      <c r="AG80" s="178"/>
-      <c r="AH80" s="175"/>
-      <c r="AI80" s="176"/>
+      <c r="AF80" s="125"/>
+      <c r="AG80" s="124"/>
+      <c r="AH80" s="121"/>
+      <c r="AI80" s="122"/>
       <c r="AJ80" s="42"/>
       <c r="AK80" s="43"/>
       <c r="AL80" s="44"/>
@@ -9892,7 +9816,7 @@
       <c r="K81" s="35"/>
       <c r="L81" s="35"/>
       <c r="M81" s="76"/>
-      <c r="N81" s="171">
+      <c r="N81" s="118">
         <f>SUM(I81:M81)</f>
         <v>0</v>
       </c>
@@ -9930,22 +9854,20 @@
         <f>T82</f>
         <v>0</v>
       </c>
-      <c r="AE81" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="AF81" s="174">
+      <c r="AE81" s="41"/>
+      <c r="AF81" s="120">
         <f>10+4+ROUND(1*I81+1*J81+1*K81+1*L81+1*M81,3)+ROUND(2*I81+2*J81+2*K81+2*L81+2*M81,3)</f>
         <v>14</v>
       </c>
-      <c r="AG81" s="166" t="e">
+      <c r="AG81" s="115" t="e">
         <f>U81+AC81+AD81+AF81</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH81" s="175" t="e">
+      <c r="AH81" s="121" t="e">
         <f>AG81+AE81</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI81" s="176" t="e">
+      <c r="AI81" s="122" t="e">
         <f>IF(AH81&gt;=40,40,AH81)</f>
         <v>#DIV/0!</v>
       </c>
@@ -9965,20 +9887,20 @@
     <row r="82" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="80"/>
       <c r="B82" s="78"/>
-      <c r="C82" s="153" t="s">
+      <c r="C82" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D82" s="154"/>
-      <c r="E82" s="154"/>
-      <c r="F82" s="154"/>
-      <c r="G82" s="155"/>
+      <c r="D82" s="127"/>
+      <c r="E82" s="127"/>
+      <c r="F82" s="127"/>
+      <c r="G82" s="128"/>
       <c r="H82" s="33"/>
       <c r="I82" s="53"/>
       <c r="J82" s="57"/>
       <c r="K82" s="57"/>
       <c r="L82" s="57"/>
       <c r="M82" s="75"/>
-      <c r="N82" s="171"/>
+      <c r="N82" s="118"/>
       <c r="O82" s="104"/>
       <c r="P82" s="105"/>
       <c r="Q82" s="105"/>
@@ -9999,10 +9921,10 @@
       <c r="AC82" s="66"/>
       <c r="AD82" s="91"/>
       <c r="AE82" s="41"/>
-      <c r="AF82" s="179"/>
-      <c r="AG82" s="178"/>
-      <c r="AH82" s="175"/>
-      <c r="AI82" s="176"/>
+      <c r="AF82" s="125"/>
+      <c r="AG82" s="124"/>
+      <c r="AH82" s="121"/>
+      <c r="AI82" s="122"/>
       <c r="AJ82" s="42"/>
       <c r="AK82" s="43"/>
       <c r="AL82" s="44"/>
@@ -10024,7 +9946,7 @@
       <c r="K83" s="35"/>
       <c r="L83" s="35"/>
       <c r="M83" s="76"/>
-      <c r="N83" s="171">
+      <c r="N83" s="118">
         <f>SUM(I83:M83)</f>
         <v>0</v>
       </c>
@@ -10062,22 +9984,20 @@
         <f>T84</f>
         <v>0</v>
       </c>
-      <c r="AE83" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF83" s="174">
+      <c r="AE83" s="41"/>
+      <c r="AF83" s="120">
         <f>10+4+ROUND(1*I83+1*J83+1*K83+1*L83+1*M83,3)+ROUND(2*I83+2*J83+2*K83+2*L83+2*M83,3)</f>
         <v>14</v>
       </c>
-      <c r="AG83" s="166" t="e">
+      <c r="AG83" s="115" t="e">
         <f>U83+AC83+AD83+AF83</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH83" s="175" t="e">
+      <c r="AH83" s="121" t="e">
         <f>AG83+AE83</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI83" s="176" t="e">
+      <c r="AI83" s="122" t="e">
         <f>IF(AH83&gt;=40,40,AH83)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10097,20 +10017,20 @@
     <row r="84" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="80"/>
       <c r="B84" s="77"/>
-      <c r="C84" s="153" t="s">
+      <c r="C84" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D84" s="154"/>
-      <c r="E84" s="154"/>
-      <c r="F84" s="154"/>
-      <c r="G84" s="155"/>
+      <c r="D84" s="127"/>
+      <c r="E84" s="127"/>
+      <c r="F84" s="127"/>
+      <c r="G84" s="128"/>
       <c r="H84" s="33"/>
       <c r="I84" s="53"/>
       <c r="J84" s="57"/>
       <c r="K84" s="57"/>
       <c r="L84" s="57"/>
       <c r="M84" s="75"/>
-      <c r="N84" s="171"/>
+      <c r="N84" s="118"/>
       <c r="O84" s="104"/>
       <c r="P84" s="105"/>
       <c r="Q84" s="105"/>
@@ -10131,10 +10051,10 @@
       <c r="AC84" s="66"/>
       <c r="AD84" s="91"/>
       <c r="AE84" s="41"/>
-      <c r="AF84" s="179"/>
-      <c r="AG84" s="178"/>
-      <c r="AH84" s="175"/>
-      <c r="AI84" s="176"/>
+      <c r="AF84" s="125"/>
+      <c r="AG84" s="124"/>
+      <c r="AH84" s="121"/>
+      <c r="AI84" s="122"/>
       <c r="AJ84" s="42"/>
       <c r="AK84" s="43"/>
       <c r="AL84" s="44"/>
@@ -10156,7 +10076,7 @@
       <c r="K85" s="57"/>
       <c r="L85" s="35"/>
       <c r="M85" s="76"/>
-      <c r="N85" s="171">
+      <c r="N85" s="118">
         <f>SUM(I85:M85)</f>
         <v>0</v>
       </c>
@@ -10194,22 +10114,20 @@
         <f>T86</f>
         <v>0</v>
       </c>
-      <c r="AE85" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF85" s="174">
+      <c r="AE85" s="41"/>
+      <c r="AF85" s="120">
         <f>10+4+ROUND(1*I85+1*J85+1*K85+1*L85+1*M85,3)+ROUND(2*I85+2*J85+2*K85+2*L85+2*M85,3)</f>
         <v>14</v>
       </c>
-      <c r="AG85" s="166" t="e">
+      <c r="AG85" s="115" t="e">
         <f>U85+AC85+AD85+AF85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH85" s="175" t="e">
+      <c r="AH85" s="121" t="e">
         <f>AG85+AE85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI85" s="176" t="e">
+      <c r="AI85" s="122" t="e">
         <f>IF(AH85&gt;=40,40,AH85)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10223,20 +10141,20 @@
     <row r="86" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="80"/>
       <c r="B86" s="78"/>
-      <c r="C86" s="153" t="s">
+      <c r="C86" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D86" s="154"/>
-      <c r="E86" s="154"/>
-      <c r="F86" s="154"/>
-      <c r="G86" s="155"/>
+      <c r="D86" s="127"/>
+      <c r="E86" s="127"/>
+      <c r="F86" s="127"/>
+      <c r="G86" s="128"/>
       <c r="H86" s="33"/>
       <c r="I86" s="53"/>
       <c r="J86" s="57"/>
       <c r="K86" s="57"/>
       <c r="L86" s="57"/>
       <c r="M86" s="75"/>
-      <c r="N86" s="171"/>
+      <c r="N86" s="118"/>
       <c r="O86" s="104"/>
       <c r="P86" s="103"/>
       <c r="Q86" s="103"/>
@@ -10257,10 +10175,10 @@
       <c r="AC86" s="66"/>
       <c r="AD86" s="91"/>
       <c r="AE86" s="41"/>
-      <c r="AF86" s="179"/>
-      <c r="AG86" s="178"/>
-      <c r="AH86" s="175"/>
-      <c r="AI86" s="176"/>
+      <c r="AF86" s="125"/>
+      <c r="AG86" s="124"/>
+      <c r="AH86" s="121"/>
+      <c r="AI86" s="122"/>
       <c r="AJ86" s="42"/>
       <c r="AK86" s="43"/>
       <c r="AL86" s="44"/>
@@ -10282,7 +10200,7 @@
       <c r="K87" s="35"/>
       <c r="L87" s="35"/>
       <c r="M87" s="76"/>
-      <c r="N87" s="171">
+      <c r="N87" s="118">
         <f>SUM(I87:M87)</f>
         <v>0</v>
       </c>
@@ -10320,22 +10238,20 @@
         <f>T88</f>
         <v>0</v>
       </c>
-      <c r="AE87" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF87" s="174">
+      <c r="AE87" s="41"/>
+      <c r="AF87" s="120">
         <f>10+4+ROUND(1*I87+1*J87+1*K87+1*L87+1*M87,3)+ROUND(2*I87+2*J87+2*K87+2*L87+2*M87,3)</f>
         <v>14</v>
       </c>
-      <c r="AG87" s="166" t="e">
+      <c r="AG87" s="115" t="e">
         <f>U87+AC87+AD87+AF87</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH87" s="175" t="e">
+      <c r="AH87" s="121" t="e">
         <f>AG87+AE87</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI87" s="176" t="e">
+      <c r="AI87" s="122" t="e">
         <f>IF(AH87&gt;=40,40,AH87)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10355,20 +10271,20 @@
     <row r="88" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="80"/>
       <c r="B88" s="78"/>
-      <c r="C88" s="153" t="s">
+      <c r="C88" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D88" s="154"/>
-      <c r="E88" s="154"/>
-      <c r="F88" s="154"/>
-      <c r="G88" s="155"/>
+      <c r="D88" s="127"/>
+      <c r="E88" s="127"/>
+      <c r="F88" s="127"/>
+      <c r="G88" s="128"/>
       <c r="H88" s="33"/>
       <c r="I88" s="53"/>
       <c r="J88" s="57"/>
       <c r="K88" s="57"/>
       <c r="L88" s="57"/>
       <c r="M88" s="75"/>
-      <c r="N88" s="171"/>
+      <c r="N88" s="118"/>
       <c r="O88" s="104"/>
       <c r="P88" s="105"/>
       <c r="Q88" s="105"/>
@@ -10389,10 +10305,10 @@
       <c r="AC88" s="66"/>
       <c r="AD88" s="91"/>
       <c r="AE88" s="41"/>
-      <c r="AF88" s="179"/>
-      <c r="AG88" s="178"/>
-      <c r="AH88" s="175"/>
-      <c r="AI88" s="176"/>
+      <c r="AF88" s="125"/>
+      <c r="AG88" s="124"/>
+      <c r="AH88" s="121"/>
+      <c r="AI88" s="122"/>
       <c r="AJ88" s="42"/>
       <c r="AK88" s="43"/>
       <c r="AL88" s="44"/>
@@ -10414,7 +10330,7 @@
       <c r="K89" s="35"/>
       <c r="L89" s="35"/>
       <c r="M89" s="76"/>
-      <c r="N89" s="171">
+      <c r="N89" s="118">
         <f>SUM(I89:M89)</f>
         <v>0</v>
       </c>
@@ -10452,22 +10368,20 @@
         <f>T90</f>
         <v>0</v>
       </c>
-      <c r="AE89" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="AF89" s="174">
+      <c r="AE89" s="41"/>
+      <c r="AF89" s="120">
         <f>10+4+ROUND(1*I89+1*J89+1*K89+1*L89+1*M89,3)+ROUND(2*I89+2*J89+2*K89+2*L89+2*M89,3)</f>
         <v>14</v>
       </c>
-      <c r="AG89" s="166" t="e">
+      <c r="AG89" s="115" t="e">
         <f>U89+AC89+AD89+AF89</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH89" s="175" t="e">
+      <c r="AH89" s="121" t="e">
         <f>AG89+AE89</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI89" s="176" t="e">
+      <c r="AI89" s="122" t="e">
         <f>IF(AH89&gt;=40,40,AH89)</f>
         <v>#DIV/0!</v>
       </c>
@@ -10487,20 +10401,20 @@
     <row r="90" spans="1:41" s="21" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="55"/>
       <c r="B90" s="59"/>
-      <c r="C90" s="153" t="s">
+      <c r="C90" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="D90" s="154"/>
-      <c r="E90" s="154"/>
-      <c r="F90" s="154"/>
-      <c r="G90" s="155"/>
+      <c r="D90" s="127"/>
+      <c r="E90" s="127"/>
+      <c r="F90" s="127"/>
+      <c r="G90" s="128"/>
       <c r="H90" s="33"/>
       <c r="I90" s="53"/>
       <c r="J90" s="57"/>
       <c r="K90" s="57"/>
       <c r="L90" s="57"/>
       <c r="M90" s="75"/>
-      <c r="N90" s="171"/>
+      <c r="N90" s="118"/>
       <c r="O90" s="104"/>
       <c r="P90" s="105"/>
       <c r="Q90" s="105"/>
@@ -10521,10 +10435,10 @@
       <c r="AC90" s="66"/>
       <c r="AD90" s="91"/>
       <c r="AE90" s="41"/>
-      <c r="AF90" s="179"/>
-      <c r="AG90" s="178"/>
-      <c r="AH90" s="175"/>
-      <c r="AI90" s="176"/>
+      <c r="AF90" s="125"/>
+      <c r="AG90" s="124"/>
+      <c r="AH90" s="121"/>
+      <c r="AI90" s="122"/>
       <c r="AJ90" s="42"/>
       <c r="AK90" s="43"/>
       <c r="AL90" s="44"/>
@@ -10534,14 +10448,52 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="T3:AH3"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C36:G36"/>
     <mergeCell ref="C42:G42"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C86:G86"/>
@@ -10558,52 +10510,14 @@
     <mergeCell ref="C64:G64"/>
     <mergeCell ref="C66:G66"/>
     <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="T3:AH3"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C84:G84"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
